--- a/src/assets/downloads/LZK-Rechner_Pkw_V1.3_Beispiel.xlsx
+++ b/src/assets/downloads/LZK-Rechner_Pkw_V1.3_Beispiel.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20414"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20415"/>
   <workbookPr updateLinks="never"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ifeu2.sharepoint.com/sites/DBUBeschaffungBerlin/Freigegebene Dokumente/General/Folgeprojekt/03_Arbeitsdokumente/A4 - Aktualisierung der Instrumente aus Basisprojekt/LZK-Rechner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="8_{F8E3439C-4500-4DCC-A4D0-17CF3516801A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{3DD1DB26-AF9C-4DCD-A403-1CECB4152EE4}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{F8E3439C-4500-4DCC-A4D0-17CF3516801A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{5282CB64-9BD1-4F78-BEE1-30AEB72C1434}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="887" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1161,9 +1161,6 @@
     </r>
   </si>
   <si>
-    <t>Ladeverhalten Elektroauto</t>
-  </si>
-  <si>
     <t>Ergänzende Angaben für Elektrofahrzeuge:</t>
   </si>
   <si>
@@ -3364,6 +3361,9 @@
   </si>
   <si>
     <t>https://www.nachhaltige-oeffentliche-pkw-beschaffung.de/assets/downloads/LZK-Rechner_Fahrzeuge_Dokumentation.pdf</t>
+  </si>
+  <si>
+    <t>Ladeverhalten Elektrofahrzeug</t>
   </si>
 </sst>
 </file>
@@ -5566,6 +5566,15 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
@@ -5600,15 +5609,6 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="13" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
@@ -12437,8 +12437,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9067589" y="2569845"/>
-          <a:ext cx="1630074" cy="963295"/>
+          <a:off x="9090449" y="2604135"/>
+          <a:ext cx="1631979" cy="976630"/>
           <a:chOff x="8390255" y="2565400"/>
           <a:chExt cx="1643409" cy="965200"/>
         </a:xfrm>
@@ -14042,7 +14042,7 @@
       <c r="H2" s="16"/>
       <c r="I2" s="16"/>
       <c r="J2" s="268" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.25">
@@ -14064,17 +14064,17 @@
       <c r="J4" s="115"/>
     </row>
     <row r="5" spans="2:10" ht="149.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="370" t="s">
-        <v>490</v>
-      </c>
-      <c r="C5" s="370"/>
-      <c r="D5" s="370"/>
-      <c r="E5" s="370"/>
-      <c r="F5" s="370"/>
-      <c r="G5" s="370"/>
-      <c r="H5" s="370"/>
-      <c r="I5" s="370"/>
-      <c r="J5" s="370"/>
+      <c r="B5" s="373" t="s">
+        <v>489</v>
+      </c>
+      <c r="C5" s="373"/>
+      <c r="D5" s="373"/>
+      <c r="E5" s="373"/>
+      <c r="F5" s="373"/>
+      <c r="G5" s="373"/>
+      <c r="H5" s="373"/>
+      <c r="I5" s="373"/>
+      <c r="J5" s="373"/>
     </row>
     <row r="6" spans="2:10" ht="11.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="245"/>
@@ -14112,13 +14112,13 @@
     <row r="9" spans="2:10" ht="52.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D9" s="245"/>
       <c r="E9" s="245"/>
-      <c r="F9" s="371" t="s">
-        <v>442</v>
-      </c>
-      <c r="G9" s="371"/>
-      <c r="H9" s="371"/>
-      <c r="I9" s="371"/>
-      <c r="J9" s="371"/>
+      <c r="F9" s="374" t="s">
+        <v>441</v>
+      </c>
+      <c r="G9" s="374"/>
+      <c r="H9" s="374"/>
+      <c r="I9" s="374"/>
+      <c r="J9" s="374"/>
     </row>
     <row r="10" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D10" s="245"/>
@@ -14132,31 +14132,31 @@
     <row r="11" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D11" s="245"/>
       <c r="E11" s="245"/>
-      <c r="F11" s="372" t="s">
-        <v>463</v>
-      </c>
-      <c r="G11" s="373"/>
-      <c r="H11" s="373"/>
-      <c r="I11" s="373"/>
-      <c r="J11" s="373"/>
+      <c r="F11" s="375" t="s">
+        <v>462</v>
+      </c>
+      <c r="G11" s="376"/>
+      <c r="H11" s="376"/>
+      <c r="I11" s="376"/>
+      <c r="J11" s="376"/>
     </row>
     <row r="12" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D12" s="245"/>
       <c r="E12" s="245"/>
-      <c r="F12" s="373"/>
-      <c r="G12" s="373"/>
-      <c r="H12" s="373"/>
-      <c r="I12" s="373"/>
-      <c r="J12" s="373"/>
+      <c r="F12" s="376"/>
+      <c r="G12" s="376"/>
+      <c r="H12" s="376"/>
+      <c r="I12" s="376"/>
+      <c r="J12" s="376"/>
     </row>
     <row r="13" spans="2:10" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D13" s="245"/>
       <c r="E13" s="245"/>
-      <c r="F13" s="373"/>
-      <c r="G13" s="373"/>
-      <c r="H13" s="373"/>
-      <c r="I13" s="373"/>
-      <c r="J13" s="373"/>
+      <c r="F13" s="376"/>
+      <c r="G13" s="376"/>
+      <c r="H13" s="376"/>
+      <c r="I13" s="376"/>
+      <c r="J13" s="376"/>
     </row>
     <row r="14" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D14" s="245"/>
@@ -14170,22 +14170,22 @@
     <row r="15" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D15" s="245"/>
       <c r="E15" s="245"/>
-      <c r="F15" s="374" t="s">
+      <c r="F15" s="377" t="s">
         <v>2</v>
       </c>
-      <c r="G15" s="375"/>
-      <c r="H15" s="375"/>
-      <c r="I15" s="375"/>
-      <c r="J15" s="375"/>
+      <c r="G15" s="378"/>
+      <c r="H15" s="378"/>
+      <c r="I15" s="378"/>
+      <c r="J15" s="378"/>
     </row>
     <row r="16" spans="2:10" ht="73.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D16" s="245"/>
       <c r="E16" s="245"/>
-      <c r="F16" s="375"/>
-      <c r="G16" s="375"/>
-      <c r="H16" s="375"/>
-      <c r="I16" s="375"/>
-      <c r="J16" s="375"/>
+      <c r="F16" s="378"/>
+      <c r="G16" s="378"/>
+      <c r="H16" s="378"/>
+      <c r="I16" s="378"/>
+      <c r="J16" s="378"/>
     </row>
     <row r="17" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D17" s="245"/>
@@ -14199,13 +14199,13 @@
     <row r="18" spans="2:10" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D18" s="245"/>
       <c r="E18" s="245"/>
-      <c r="F18" s="376" t="s">
+      <c r="F18" s="379" t="s">
         <v>3</v>
       </c>
-      <c r="G18" s="377"/>
-      <c r="H18" s="377"/>
-      <c r="I18" s="377"/>
-      <c r="J18" s="377"/>
+      <c r="G18" s="380"/>
+      <c r="H18" s="380"/>
+      <c r="I18" s="380"/>
+      <c r="J18" s="380"/>
     </row>
     <row r="19" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D19" s="245"/>
@@ -14219,31 +14219,31 @@
     <row r="20" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D20" s="245"/>
       <c r="E20" s="245"/>
-      <c r="F20" s="378" t="s">
+      <c r="F20" s="381" t="s">
         <v>4</v>
       </c>
-      <c r="G20" s="378"/>
-      <c r="H20" s="378"/>
-      <c r="I20" s="378"/>
-      <c r="J20" s="378"/>
+      <c r="G20" s="381"/>
+      <c r="H20" s="381"/>
+      <c r="I20" s="381"/>
+      <c r="J20" s="381"/>
     </row>
     <row r="21" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D21" s="245"/>
       <c r="E21" s="245"/>
-      <c r="F21" s="378"/>
-      <c r="G21" s="378"/>
-      <c r="H21" s="378"/>
-      <c r="I21" s="378"/>
-      <c r="J21" s="378"/>
+      <c r="F21" s="381"/>
+      <c r="G21" s="381"/>
+      <c r="H21" s="381"/>
+      <c r="I21" s="381"/>
+      <c r="J21" s="381"/>
     </row>
     <row r="22" spans="2:10" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D22" s="245"/>
       <c r="E22" s="245"/>
-      <c r="F22" s="378"/>
-      <c r="G22" s="378"/>
-      <c r="H22" s="378"/>
-      <c r="I22" s="378"/>
-      <c r="J22" s="378"/>
+      <c r="F22" s="381"/>
+      <c r="G22" s="381"/>
+      <c r="H22" s="381"/>
+      <c r="I22" s="381"/>
+      <c r="J22" s="381"/>
     </row>
     <row r="23" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D23" s="245"/>
@@ -14257,22 +14257,22 @@
     <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="D24" s="245"/>
       <c r="E24" s="245"/>
-      <c r="F24" s="379" t="s">
+      <c r="F24" s="382" t="s">
         <v>5</v>
       </c>
-      <c r="G24" s="379"/>
-      <c r="H24" s="379"/>
-      <c r="I24" s="379"/>
-      <c r="J24" s="379"/>
+      <c r="G24" s="382"/>
+      <c r="H24" s="382"/>
+      <c r="I24" s="382"/>
+      <c r="J24" s="382"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="D25" s="245"/>
       <c r="E25" s="245"/>
-      <c r="F25" s="379"/>
-      <c r="G25" s="379"/>
-      <c r="H25" s="379"/>
-      <c r="I25" s="379"/>
-      <c r="J25" s="379"/>
+      <c r="F25" s="382"/>
+      <c r="G25" s="382"/>
+      <c r="H25" s="382"/>
+      <c r="I25" s="382"/>
+      <c r="J25" s="382"/>
     </row>
     <row r="26" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D26" s="245"/>
@@ -14286,49 +14286,49 @@
     <row r="27" spans="2:10" ht="7.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D27" s="245"/>
       <c r="E27" s="245"/>
-      <c r="F27" s="369"/>
-      <c r="G27" s="369"/>
-      <c r="H27" s="369"/>
-      <c r="I27" s="369"/>
-      <c r="J27" s="369"/>
+      <c r="F27" s="372"/>
+      <c r="G27" s="372"/>
+      <c r="H27" s="372"/>
+      <c r="I27" s="372"/>
+      <c r="J27" s="372"/>
     </row>
     <row r="28" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D28" s="245"/>
       <c r="E28" s="245"/>
-      <c r="F28" s="380" t="s">
-        <v>464</v>
-      </c>
-      <c r="G28" s="380"/>
-      <c r="H28" s="380"/>
-      <c r="I28" s="380"/>
-      <c r="J28" s="380"/>
+      <c r="F28" s="383" t="s">
+        <v>463</v>
+      </c>
+      <c r="G28" s="383"/>
+      <c r="H28" s="383"/>
+      <c r="I28" s="383"/>
+      <c r="J28" s="383"/>
     </row>
     <row r="29" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D29" s="245"/>
       <c r="E29" s="245"/>
-      <c r="F29" s="380"/>
-      <c r="G29" s="380"/>
-      <c r="H29" s="380"/>
-      <c r="I29" s="380"/>
-      <c r="J29" s="380"/>
+      <c r="F29" s="383"/>
+      <c r="G29" s="383"/>
+      <c r="H29" s="383"/>
+      <c r="I29" s="383"/>
+      <c r="J29" s="383"/>
     </row>
     <row r="30" spans="2:10" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D30" s="245"/>
       <c r="E30" s="245"/>
-      <c r="F30" s="380"/>
-      <c r="G30" s="380"/>
-      <c r="H30" s="380"/>
-      <c r="I30" s="380"/>
-      <c r="J30" s="380"/>
+      <c r="F30" s="383"/>
+      <c r="G30" s="383"/>
+      <c r="H30" s="383"/>
+      <c r="I30" s="383"/>
+      <c r="J30" s="383"/>
     </row>
     <row r="31" spans="2:10" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D31" s="245"/>
       <c r="E31" s="245"/>
-      <c r="F31" s="381"/>
-      <c r="G31" s="381"/>
-      <c r="H31" s="381"/>
-      <c r="I31" s="381"/>
-      <c r="J31" s="381"/>
+      <c r="F31" s="371"/>
+      <c r="G31" s="371"/>
+      <c r="H31" s="371"/>
+      <c r="I31" s="371"/>
+      <c r="J31" s="371"/>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="250" t="s">
@@ -14377,15 +14377,15 @@
     <row r="36" spans="2:11" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="116"/>
       <c r="C36" s="113"/>
-      <c r="D36" s="381" t="s">
+      <c r="D36" s="371" t="s">
         <v>8</v>
       </c>
-      <c r="E36" s="381"/>
-      <c r="F36" s="381"/>
-      <c r="G36" s="381"/>
-      <c r="H36" s="381"/>
-      <c r="I36" s="381"/>
-      <c r="J36" s="381"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
+      <c r="G36" s="371"/>
+      <c r="H36" s="371"/>
+      <c r="I36" s="371"/>
+      <c r="J36" s="371"/>
     </row>
     <row r="37" spans="2:11" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="117"/>
@@ -14401,24 +14401,24 @@
     <row r="38" spans="2:11" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B38" s="241"/>
       <c r="C38" s="113"/>
-      <c r="D38" s="369" t="s">
+      <c r="D38" s="372" t="s">
         <v>9</v>
       </c>
-      <c r="E38" s="369"/>
-      <c r="F38" s="369"/>
-      <c r="G38" s="369"/>
-      <c r="H38" s="369"/>
-      <c r="I38" s="369"/>
-      <c r="J38" s="369"/>
+      <c r="E38" s="372"/>
+      <c r="F38" s="372"/>
+      <c r="G38" s="372"/>
+      <c r="H38" s="372"/>
+      <c r="I38" s="372"/>
+      <c r="J38" s="372"/>
     </row>
     <row r="39" spans="2:11" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D39" s="369"/>
-      <c r="E39" s="369"/>
-      <c r="F39" s="369"/>
-      <c r="G39" s="369"/>
-      <c r="H39" s="369"/>
-      <c r="I39" s="369"/>
-      <c r="J39" s="369"/>
+      <c r="D39" s="372"/>
+      <c r="E39" s="372"/>
+      <c r="F39" s="372"/>
+      <c r="G39" s="372"/>
+      <c r="H39" s="372"/>
+      <c r="I39" s="372"/>
+      <c r="J39" s="372"/>
     </row>
     <row r="40" spans="2:11" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="117"/>
@@ -14436,15 +14436,15 @@
         <v>10</v>
       </c>
       <c r="C41" s="113"/>
-      <c r="D41" s="382" t="s">
+      <c r="D41" s="369" t="s">
         <v>11</v>
       </c>
-      <c r="E41" s="382"/>
-      <c r="F41" s="382"/>
-      <c r="G41" s="382"/>
-      <c r="H41" s="382"/>
-      <c r="I41" s="382"/>
-      <c r="J41" s="382"/>
+      <c r="E41" s="369"/>
+      <c r="F41" s="369"/>
+      <c r="G41" s="369"/>
+      <c r="H41" s="369"/>
+      <c r="I41" s="369"/>
+      <c r="J41" s="369"/>
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" s="113"/>
@@ -14458,30 +14458,30 @@
       <c r="J42" s="245"/>
     </row>
     <row r="43" spans="2:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="383" t="s">
+      <c r="B43" s="370" t="s">
         <v>12</v>
       </c>
       <c r="C43" s="103"/>
-      <c r="D43" s="381" t="s">
+      <c r="D43" s="371" t="s">
         <v>13</v>
       </c>
-      <c r="E43" s="381"/>
-      <c r="F43" s="381"/>
-      <c r="G43" s="381"/>
-      <c r="H43" s="381"/>
-      <c r="I43" s="381"/>
-      <c r="J43" s="381"/>
+      <c r="E43" s="371"/>
+      <c r="F43" s="371"/>
+      <c r="G43" s="371"/>
+      <c r="H43" s="371"/>
+      <c r="I43" s="371"/>
+      <c r="J43" s="371"/>
     </row>
     <row r="44" spans="2:11" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="B44" s="383"/>
+      <c r="B44" s="370"/>
       <c r="C44" s="103"/>
-      <c r="D44" s="381"/>
-      <c r="E44" s="381"/>
-      <c r="F44" s="381"/>
-      <c r="G44" s="381"/>
-      <c r="H44" s="381"/>
-      <c r="I44" s="381"/>
-      <c r="J44" s="381"/>
+      <c r="D44" s="371"/>
+      <c r="E44" s="371"/>
+      <c r="F44" s="371"/>
+      <c r="G44" s="371"/>
+      <c r="H44" s="371"/>
+      <c r="I44" s="371"/>
+      <c r="J44" s="371"/>
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.25">
       <c r="D45" s="112"/>
@@ -14493,17 +14493,17 @@
       <c r="J45" s="114"/>
     </row>
     <row r="46" spans="2:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="381" t="s">
-        <v>433</v>
-      </c>
-      <c r="C46" s="381"/>
-      <c r="D46" s="381"/>
-      <c r="E46" s="381"/>
-      <c r="F46" s="381"/>
-      <c r="G46" s="381"/>
-      <c r="H46" s="381"/>
-      <c r="I46" s="381"/>
-      <c r="J46" s="381"/>
+      <c r="B46" s="371" t="s">
+        <v>432</v>
+      </c>
+      <c r="C46" s="371"/>
+      <c r="D46" s="371"/>
+      <c r="E46" s="371"/>
+      <c r="F46" s="371"/>
+      <c r="G46" s="371"/>
+      <c r="H46" s="371"/>
+      <c r="I46" s="371"/>
+      <c r="J46" s="371"/>
       <c r="K46" s="107"/>
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.25">
@@ -14538,17 +14538,17 @@
       <c r="J49" s="112"/>
     </row>
     <row r="50" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="381" t="s">
+      <c r="B50" s="371" t="s">
         <v>15</v>
       </c>
-      <c r="C50" s="381"/>
-      <c r="D50" s="381"/>
-      <c r="E50" s="381"/>
-      <c r="F50" s="381"/>
-      <c r="G50" s="381"/>
-      <c r="H50" s="381"/>
-      <c r="I50" s="381"/>
-      <c r="J50" s="381"/>
+      <c r="C50" s="371"/>
+      <c r="D50" s="371"/>
+      <c r="E50" s="371"/>
+      <c r="F50" s="371"/>
+      <c r="G50" s="371"/>
+      <c r="H50" s="371"/>
+      <c r="I50" s="371"/>
+      <c r="J50" s="371"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D51" s="114"/>
@@ -14611,11 +14611,6 @@
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="17">
-    <mergeCell ref="D41:J41"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="D43:J44"/>
-    <mergeCell ref="B46:J46"/>
-    <mergeCell ref="B50:J50"/>
     <mergeCell ref="D38:J39"/>
     <mergeCell ref="B5:J5"/>
     <mergeCell ref="F9:J9"/>
@@ -14628,6 +14623,11 @@
     <mergeCell ref="F28:J30"/>
     <mergeCell ref="F31:J31"/>
     <mergeCell ref="D36:J36"/>
+    <mergeCell ref="D41:J41"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="D43:J44"/>
+    <mergeCell ref="B46:J46"/>
+    <mergeCell ref="B50:J50"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F9:J9" location="Input_Beschaffung!A1" display="Geben Sie die übergeordneten Informationen zu Ihrem Beschaffungsfall ein. Hier können Informationen wie die erwartete jährliche Fahrleistung, die Art der Beschaffung (Kauf/Leasing) und weitere Informationen eingegeben werden." xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -14669,7 +14669,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>21</v>
@@ -14682,7 +14682,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B4" s="154" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -14698,7 +14698,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C6" s="54">
         <v>4</v>
@@ -14711,7 +14711,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C7" s="102" t="str">
         <f>IF(Anbieter4=0,"",Anbieter4)</f>
@@ -14733,7 +14733,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C9" s="102"/>
       <c r="E9" s="125"/>
@@ -14741,7 +14741,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C10" s="102" t="str">
         <f>IF(Hersteller4=0,"",Hersteller4)</f>
@@ -14753,7 +14753,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C11" s="102" t="str">
         <f>IF(Modell4=0,"",Modell4)</f>
@@ -14765,7 +14765,7 @@
     </row>
     <row r="12" spans="1:6" ht="43.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="56" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C12" s="102" t="str">
         <f>IF(Zusatzinfo4=0,"",Zusatzinfo4)</f>
@@ -14777,7 +14777,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B13" s="57" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C13" s="102" t="str">
         <f>IF(Antriebsart4=0,"",Antriebsart4)</f>
@@ -14788,7 +14788,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C14" s="102" t="str">
         <f>IF(Energie4=0,"",Energie4)</f>
@@ -14804,7 +14804,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B16" s="154" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -14820,7 +14820,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B18" s="72" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C18" s="288">
         <f>0.0057*(ReichwPHEV4/23)^3-0.0838*(ReichwPHEV4/23)^2+0.4261*(ReichwPHEV4/23)+ 0.1633</f>
@@ -14832,35 +14832,35 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C19" s="289">
         <f>Verbrauch4/(1-0.9*C18)</f>
         <v>0</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E19" s="125"/>
       <c r="F19" s="125"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B20" s="72" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C20" s="290">
         <f>VerbEl_WLTP4/C18</f>
         <v>97.366809552969997</v>
       </c>
       <c r="D20" s="184" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E20" s="125"/>
       <c r="F20" s="125"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B21" s="186" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C21" s="291">
         <f>0.0021*(ReichwPHEV4/23)^3-0.0358*(ReichwPHEV4/23)^2+0.2607*(ReichwPHEV4/23)- 0.0267</f>
@@ -14875,14 +14875,14 @@
         <v>12</v>
       </c>
       <c r="B22" s="439" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C22" s="292">
         <f>C19*(1-0.9*C21)</f>
         <v>0</v>
       </c>
       <c r="D22" s="185" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E22" s="125"/>
       <c r="F22" s="125"/>
@@ -14895,7 +14895,7 @@
         <v>-2.599693815064299</v>
       </c>
       <c r="D23" s="183" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E23" s="125"/>
       <c r="F23" s="125"/>
@@ -14907,7 +14907,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B25" s="154" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
@@ -14920,7 +14920,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B27" s="60" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C27" s="61"/>
       <c r="D27" s="60"/>
@@ -14929,42 +14929,42 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C28" s="279">
         <f>IF(Antriebsart4="Vollelektrisch (BEV)",0,IFERROR(VLOOKUP(Energie4,EnKostList,6,FALSE),0)*IF(Antriebsart4="Plug-In-Hybrid (PHEV)",VerbPHEV4,Verbrauch4)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E28" s="125"/>
       <c r="F28" s="125"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C29" s="279">
         <f>IF(Antriebsart4="Verbrenner",0,VLOOKUP("Strom",EnKostList,6,FALSE)*IF(Antriebsart4="Plug-In-Hybrid (PHEV)",VerbElPHEV4,VerbEl_WLTP4)/100*Fahrleistung)</f>
         <v>1596.36</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E29" s="125"/>
       <c r="F29" s="125"/>
     </row>
     <row r="30" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="64" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C30" s="280">
         <f>SUM(C28:C29)</f>
         <v>1596.36</v>
       </c>
       <c r="D30" s="64" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E30" s="125"/>
       <c r="F30" s="125"/>
@@ -14977,7 +14977,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B32" s="60" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C32" s="145" t="str">
         <f>CONCATENATE("Energieträger: ",Energie4)</f>
@@ -14989,70 +14989,70 @@
     </row>
     <row r="33" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B33" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C33" s="279">
         <f>IF(Antriebsart4="Plug-In-Hybrid (PHEV)",VerbPHEV4*VLOOKUP(Energie4,CO2List,2,FALSE)/100,CO2_4)*Fahrleistung/1000000</f>
         <v>0</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E33" s="125"/>
       <c r="F33" s="125"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C34" s="279">
         <f>C33*Kost_THG</f>
         <v>0</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E34" s="125"/>
       <c r="F34" s="125"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B35" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C35" s="287">
         <f>IF(Energie4="Strom",0,NOX_4*Fahrleistung*Kost_NOX/1000)</f>
         <v>0</v>
       </c>
       <c r="D35" s="65" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E35" s="125"/>
       <c r="F35" s="125"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B36" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C36" s="287">
         <f>IF(Energie4="Strom",0,Partikel4*Fahrleistung*Kost_Partikel/1000)</f>
         <v>0</v>
       </c>
       <c r="D36" s="65" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E36" s="125"/>
       <c r="F36" s="125"/>
     </row>
     <row r="37" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="64" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C37" s="280">
         <f>SUM(C34:C36)</f>
         <v>0</v>
       </c>
       <c r="D37" s="64" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E37" s="125"/>
       <c r="F37" s="125"/>
@@ -15065,7 +15065,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B39" s="60" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C39" s="145" t="str">
         <f>CONCATENATE("Energieträger: ",Energie4,IF(Antriebsart4="Plug-In-Hybrid (PHEV)","+Strom",""))</f>
@@ -15077,28 +15077,28 @@
     </row>
     <row r="40" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B40" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C40" s="279">
         <f>IFERROR(IF(Antriebsart4="Vollelektrisch (BEV)",VLOOKUP("Strom",CO2List,3,FALSE)*VerbEl_WLTP4/100*Fahrleistung/1000000,IF(Antriebsart4="Verbrenner",VLOOKUP(Energie4,CO2List,3,FALSE)*Verbrauch4/100*Fahrleistung/1000000,VLOOKUP(Energie4,CO2List,3,FALSE)*VerbPHEV4/100*Fahrleistung/1000000+VLOOKUP("Strom",CO2List,3,FALSE)*VerbElPHEV4/100*Fahrleistung/1000000)),0)</f>
         <v>0.92537999999999998</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E40" s="125"/>
       <c r="F40" s="125"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B41" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C41" s="279">
         <f>C40*Kost_THG</f>
         <v>795.82679999999993</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E41" s="125"/>
       <c r="F41" s="125"/>
@@ -15109,7 +15109,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B43" s="154" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
@@ -15126,55 +15126,55 @@
     <row r="45" spans="1:6" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="107"/>
       <c r="B45" s="90" t="s">
+        <v>170</v>
+      </c>
+      <c r="C45" s="134" t="s">
         <v>171</v>
-      </c>
-      <c r="C45" s="134" t="s">
-        <v>172</v>
       </c>
       <c r="D45" s="62"/>
       <c r="E45" s="125"/>
       <c r="F45" s="125"/>
     </row>
     <row r="46" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A46" s="383" t="s">
+      <c r="A46" s="370" t="s">
         <v>12</v>
       </c>
       <c r="B46" s="437" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C46" s="281">
         <f>IF(OR(Antriebsart4="Vollelektrisch (BEV)",Antriebsart4="Plug-In-Hybrid (PHEV)"),Batterie4*Batterie_THG/1000,0)</f>
         <v>5.0735999999999999</v>
       </c>
       <c r="D46" s="131" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E46" s="127"/>
       <c r="F46" s="125"/>
     </row>
     <row r="47" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A47" s="383"/>
+      <c r="A47" s="370"/>
       <c r="B47" s="438"/>
       <c r="C47" s="281">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
         <v>23.061818181818182</v>
       </c>
       <c r="D47" s="130" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E47" s="127"/>
       <c r="F47" s="125"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B48" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C48" s="279">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Kost_THG, C46/Haltedauer*Kost_THG)</f>
         <v>396.66327272727273</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E48" s="125"/>
       <c r="F48" s="125"/>
@@ -15198,20 +15198,20 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B52" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="54" spans="1:6" s="70" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="68" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C54" s="282">
         <f>IF(FinArt="Kauf",IF(KaufpreisRech="Kaufpreis",Gesamtpreis4,0),Gesamtpreis4*Haltedauer*12+IF(FinArt="Leasing",LeasSondZahl4,0))</f>
         <v>0</v>
       </c>
       <c r="D54" s="68" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E54" s="69"/>
       <c r="F54" s="58"/>
@@ -15221,72 +15221,72 @@
         <v>12</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C55" s="283">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis4-Gesamtpreis4*(-0.2*LN(Haltedauer)+0.667),0)</f>
         <v>25269.14922308908</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E55" s="125"/>
       <c r="F55" s="73"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B56" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C56" s="283">
         <f>C30*Haltedauer</f>
         <v>11174.519999999999</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F56" s="73"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C57" s="283">
         <f>C37*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F57" s="58"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C58" s="283">
         <f>C41*Haltedauer</f>
         <v>5570.7875999999997</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F58" s="58"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B59" s="333" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C59" s="334">
         <f>C48*Haltedauer</f>
         <v>2776.6429090909091</v>
       </c>
       <c r="D59" s="80" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="383" t="s">
+      <c r="A60" s="370" t="s">
         <v>12</v>
       </c>
       <c r="B60" s="327" t="str">
@@ -15304,7 +15304,7 @@
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="383"/>
+      <c r="A61" s="370"/>
       <c r="B61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
@@ -15320,7 +15320,7 @@
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="383"/>
+      <c r="A62" s="370"/>
       <c r="B62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
@@ -15337,14 +15337,14 @@
     </row>
     <row r="63" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B63" s="64" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C63" s="284">
         <f>SUM(C54:C62)</f>
         <v>44791.09973217998</v>
       </c>
       <c r="D63" s="64" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E63" s="14"/>
       <c r="F63" s="58"/>
@@ -15359,26 +15359,26 @@
     </row>
     <row r="65" spans="2:5" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B65" s="68" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C65" s="285">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Haltedauer, C46)</f>
         <v>3.2286545454545457</v>
       </c>
       <c r="D65" s="68" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="66" spans="2:5" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B66" s="72" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C66" s="286">
         <f>C33*Haltedauer+C40*Haltedauer</f>
         <v>6.4776600000000002</v>
       </c>
       <c r="D66" s="72" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E66" s="71"/>
     </row>
@@ -15429,7 +15429,7 @@
     </row>
     <row r="2" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>21</v>
@@ -15442,7 +15442,7 @@
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="154" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -15458,7 +15458,7 @@
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C6" s="54">
         <v>5</v>
@@ -15471,7 +15471,7 @@
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C7" s="102" t="str">
         <f>IF(Anbieter5=0,"",Anbieter5)</f>
@@ -15493,7 +15493,7 @@
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C9" s="102"/>
       <c r="E9" s="125"/>
@@ -15501,7 +15501,7 @@
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C10" s="102" t="str">
         <f>IF(Hersteller5=0,"",Hersteller5)</f>
@@ -15513,7 +15513,7 @@
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C11" s="102" t="str">
         <f>IF(Modell5=0,"",Modell5)</f>
@@ -15525,7 +15525,7 @@
     </row>
     <row r="12" spans="2:6" ht="43.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="56" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C12" s="102" t="str">
         <f>IF(Zusatzinfo5=0,"",Zusatzinfo5)</f>
@@ -15537,7 +15537,7 @@
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B13" s="57" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C13" s="102" t="str">
         <f>IF(Antriebsart5=0,"",Antriebsart5)</f>
@@ -15548,7 +15548,7 @@
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C14" s="102" t="str">
         <f>IF(Energie5=0,"",Energie5)</f>
@@ -15566,7 +15566,7 @@
     </row>
     <row r="16" spans="2:6" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="154" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -15583,7 +15583,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B18" s="72" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C18" s="288">
         <f>0.0057*(ReichwPHEV5/23)^3-0.0838*(ReichwPHEV5/23)^2+0.4261*(ReichwPHEV5/23)+ 0.1633</f>
@@ -15595,35 +15595,35 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C19" s="289">
         <f>Verbrauch5/(1-0.9*C18)</f>
         <v>3.1271358482255263</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E19" s="125"/>
       <c r="F19" s="125"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B20" s="72" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C20" s="290">
         <f>VerbEl_WLTP5/C18</f>
         <v>15.601172241655869</v>
       </c>
       <c r="D20" s="184" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E20" s="125"/>
       <c r="F20" s="125"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B21" s="186" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C21" s="291">
         <f>0.0021*(ReichwPHEV5/23)^3-0.0358*(ReichwPHEV5/23)^2+0.2607*(ReichwPHEV5/23)- 0.0267</f>
@@ -15638,14 +15638,14 @@
         <v>12</v>
       </c>
       <c r="B22" s="439" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C22" s="292">
         <f>C19*(1-0.9*C21)</f>
         <v>1.8000391534525582</v>
       </c>
       <c r="D22" s="185" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E22" s="125"/>
       <c r="F22" s="125"/>
@@ -15658,7 +15658,7 @@
         <v>7.3564881807932201</v>
       </c>
       <c r="D23" s="183" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E23" s="125"/>
       <c r="F23" s="125"/>
@@ -15670,7 +15670,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B25" s="154" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
@@ -15683,7 +15683,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B27" s="60" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C27" s="61"/>
       <c r="D27" s="60"/>
@@ -15692,42 +15692,42 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C28" s="279">
         <f>IF(Antriebsart5="Vollelektrisch (BEV)",0,IFERROR(VLOOKUP(Energie5,EnKostList,6,FALSE),0)*IF(Antriebsart5="Plug-In-Hybrid (PHEV)",VerbPHEV5,Verbrauch5)/100*Fahrleistung)</f>
         <v>643.69400127463473</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E28" s="125"/>
       <c r="F28" s="125"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C29" s="279">
         <f>IF(Antriebsart5="Verbrenner",0,VLOOKUP("Strom",EnKostList,6,FALSE)*IF(Antriebsart5="Plug-In-Hybrid (PHEV)",VerbElPHEV5,VerbEl_WLTP5)/100*Fahrleistung)</f>
         <v>738.59141335163929</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E29" s="125"/>
       <c r="F29" s="125"/>
     </row>
     <row r="30" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="64" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C30" s="280">
         <f>SUM(C28:C29)</f>
         <v>1382.2854146262739</v>
       </c>
       <c r="D30" s="64" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E30" s="125"/>
       <c r="F30" s="125"/>
@@ -15740,7 +15740,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B32" s="60" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C32" s="145" t="str">
         <f>CONCATENATE("Energieträger: ",Energie5)</f>
@@ -15753,70 +15753,70 @@
     <row r="33" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
       <c r="A33" s="126"/>
       <c r="B33" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C33" s="279">
         <f>IF(Antriebsart5="Plug-In-Hybrid (PHEV)",VerbPHEV5*VLOOKUP(Energie5,CO2List,2,FALSE)/100,CO2_5)*Fahrleistung/1000000</f>
         <v>0.84661901795488459</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E33" s="125"/>
       <c r="F33" s="125"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C34" s="279">
         <f>C33*Kost_THG</f>
         <v>728.09235544120077</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E34" s="125"/>
       <c r="F34" s="125"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B35" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C35" s="287">
         <f>IF(Energie5="Strom",0,NOX_5*Fahrleistung*Kost_NOX/1000)</f>
         <v>2.3199999999999998</v>
       </c>
       <c r="D35" s="65" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E35" s="125"/>
       <c r="F35" s="125"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B36" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C36" s="287">
         <f>IF(Energie5="Strom",0,Partikel5*Fahrleistung*Kost_Partikel/1000)</f>
         <v>0.75</v>
       </c>
       <c r="D36" s="65" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E36" s="125"/>
       <c r="F36" s="125"/>
     </row>
     <row r="37" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="64" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C37" s="280">
         <f>SUM(C34:C36)</f>
         <v>731.16235544120082</v>
       </c>
       <c r="D37" s="64" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E37" s="125"/>
       <c r="F37" s="125"/>
@@ -15829,7 +15829,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B39" s="60" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C39" s="145" t="str">
         <f>CONCATENATE("Energieträger: ",Energie5,IF(Antriebsart5="Plug-In-Hybrid (PHEV)","+Strom",""))</f>
@@ -15841,28 +15841,28 @@
     </row>
     <row r="40" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B40" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C40" s="279">
         <f>IFERROR(IF(Antriebsart5="Vollelektrisch (BEV)",VLOOKUP("Strom",CO2List,3,FALSE)*VerbEl_WLTP5/100*Fahrleistung/1000000,IF(Antriebsart5="Verbrenner",VLOOKUP(Energie5,CO2List,3,FALSE)*Verbrauch5/100*Fahrleistung/1000000,VLOOKUP(Energie5,CO2List,3,FALSE)*VerbPHEV5/100*Fahrleistung/1000000+VLOOKUP("Strom",CO2List,3,FALSE)*VerbElPHEV5/100*Fahrleistung/1000000)),0)</f>
         <v>0.6979974646583782</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E40" s="125"/>
       <c r="F40" s="125"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B41" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C41" s="279">
         <f>C40*Kost_THG</f>
         <v>600.2778196062053</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E41" s="125"/>
       <c r="F41" s="125"/>
@@ -15873,7 +15873,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B43" s="154" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
@@ -15890,55 +15890,55 @@
     <row r="45" spans="1:6" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="107"/>
       <c r="B45" s="90" t="s">
+        <v>170</v>
+      </c>
+      <c r="C45" s="134" t="s">
         <v>171</v>
-      </c>
-      <c r="C45" s="134" t="s">
-        <v>172</v>
       </c>
       <c r="D45" s="62"/>
       <c r="E45" s="125"/>
       <c r="F45" s="125"/>
     </row>
     <row r="46" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A46" s="383" t="s">
+      <c r="A46" s="370" t="s">
         <v>12</v>
       </c>
       <c r="B46" s="437" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C46" s="281">
         <f>IF(OR(Antriebsart5="Vollelektrisch (BEV)",Antriebsart5="Plug-In-Hybrid (PHEV)"),Batterie5*Batterie_THG/1000,0)</f>
         <v>1.008</v>
       </c>
       <c r="D46" s="131" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E46" s="127"/>
       <c r="F46" s="125"/>
     </row>
     <row r="47" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A47" s="383"/>
+      <c r="A47" s="370"/>
       <c r="B47" s="438"/>
       <c r="C47" s="281">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
         <v>4.581818181818182</v>
       </c>
       <c r="D47" s="130" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E47" s="127"/>
       <c r="F47" s="125"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B48" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C48" s="279">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Kost_THG, C46/Haltedauer*Kost_THG)</f>
         <v>78.807272727272732</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E48" s="125"/>
       <c r="F48" s="125"/>
@@ -15962,20 +15962,20 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B52" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="54" spans="1:6" s="70" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="68" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C54" s="282">
         <f>IF(FinArt="Kauf",IF(KaufpreisRech="Kaufpreis",Gesamtpreis5,0),Gesamtpreis5*Haltedauer*12+IF(FinArt="Leasing",LeasSondZahl5,0))</f>
         <v>0</v>
       </c>
       <c r="D54" s="68" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E54" s="69"/>
       <c r="F54" s="58"/>
@@ -15985,72 +15985,72 @@
         <v>12</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C55" s="283">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis5-Gesamtpreis5*(-0.2*LN(Haltedauer)+0.667),0)</f>
         <v>27941.222733390012</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E55" s="125"/>
       <c r="F55" s="73"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B56" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C56" s="283">
         <f>C30*Haltedauer</f>
         <v>9675.9979023839169</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F56" s="73"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C57" s="283">
         <f>C37*Haltedauer</f>
         <v>5118.1364880884057</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F57" s="58"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C58" s="283">
         <f>C41*Haltedauer</f>
         <v>4201.944737243437</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F58" s="58"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B59" s="329" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C59" s="330">
         <f>C48*Haltedauer</f>
         <v>551.65090909090918</v>
       </c>
       <c r="D59" s="329" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="383" t="s">
+      <c r="A60" s="370" t="s">
         <v>12</v>
       </c>
       <c r="B60" s="327" t="str">
@@ -16068,7 +16068,7 @@
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="383"/>
+      <c r="A61" s="370"/>
       <c r="B61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
@@ -16084,7 +16084,7 @@
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="383"/>
+      <c r="A62" s="370"/>
       <c r="B62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
@@ -16101,14 +16101,14 @@
     </row>
     <row r="63" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B63" s="64" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C63" s="284">
         <f>SUM(C54:C62)</f>
         <v>47712.95277019668</v>
       </c>
       <c r="D63" s="64" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E63" s="14"/>
       <c r="F63" s="58"/>
@@ -16123,26 +16123,26 @@
     </row>
     <row r="65" spans="2:5" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B65" s="68" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C65" s="285">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Haltedauer, C46)</f>
         <v>0.6414545454545455</v>
       </c>
       <c r="D65" s="68" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="66" spans="2:5" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B66" s="72" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C66" s="286">
         <f>C33*Haltedauer+C40*Haltedauer</f>
         <v>10.812315378292841</v>
       </c>
       <c r="D66" s="72" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E66" s="71"/>
     </row>
@@ -16188,7 +16188,7 @@
   <sheetData>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H2" s="106" t="s">
         <v>21</v>
@@ -16196,7 +16196,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B4" s="154" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
@@ -16205,18 +16205,18 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="C6" s="63" t="s">
+        <v>181</v>
+      </c>
+      <c r="D6" s="63" t="s">
         <v>182</v>
       </c>
-      <c r="D6" s="63" t="s">
-        <v>183</v>
-      </c>
       <c r="E6" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:9" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B7" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C7" s="302">
         <v>74.027000000000001</v>
@@ -16225,12 +16225,12 @@
         <v>23.4</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B8" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C8" s="302">
         <v>72.787000000000006</v>
@@ -16239,12 +16239,12 @@
         <v>23.2</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="9" spans="1:9" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B9" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C9" s="302">
         <v>56.220999999999997</v>
@@ -16253,12 +16253,12 @@
         <v>20.3</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="92" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C10" s="10"/>
       <c r="D10" s="10"/>
@@ -16268,7 +16268,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B12" s="154" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C12" s="93"/>
       <c r="D12" s="5"/>
@@ -16286,14 +16286,14 @@
     </row>
     <row r="14" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="110" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C14" s="441" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D14" s="441"/>
       <c r="E14" s="442" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F14" s="442"/>
       <c r="G14" s="304"/>
@@ -16301,40 +16301,40 @@
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="66"/>
       <c r="B15" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C15" s="58">
         <v>1</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E15" s="136">
         <f>42.722*0.832</f>
         <v>35.544704000000003</v>
       </c>
       <c r="F15" s="111" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G15" s="111"/>
       <c r="H15" s="136"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B16" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C16" s="58">
         <v>1</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="E16" s="136">
         <f>43.543*0.742</f>
         <v>32.308906</v>
       </c>
       <c r="F16" s="111" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G16" s="111"/>
       <c r="H16" s="136"/>
@@ -16342,54 +16342,54 @@
     <row r="17" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A17" s="66"/>
       <c r="B17" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C17" s="58">
         <v>1</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E17" s="303">
         <v>46.5</v>
       </c>
       <c r="F17" s="111" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="G17" s="111"/>
     </row>
     <row r="18" spans="1:37" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="92" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="D18" s="106"/>
       <c r="E18" s="10"/>
     </row>
     <row r="20" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B20" s="154" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
       <c r="H20" s="2" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="21" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B21" s="66"/>
       <c r="I21" s="58" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J21" s="135" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="K21" s="135"/>
       <c r="L21" s="135"/>
       <c r="M21" s="135"/>
       <c r="O21" s="137" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="P21" s="137"/>
       <c r="Q21" s="137"/>
@@ -16399,13 +16399,13 @@
     <row r="22" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B22" s="66"/>
       <c r="C22" s="63" t="s">
+        <v>181</v>
+      </c>
+      <c r="D22" s="63" t="s">
         <v>182</v>
       </c>
-      <c r="D22" s="63" t="s">
-        <v>183</v>
-      </c>
       <c r="E22" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="23" spans="1:37" ht="16.2" x14ac:dyDescent="0.35">
@@ -16413,7 +16413,7 @@
         <v>12</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C23" s="58">
         <v>0</v>
@@ -16423,12 +16423,12 @@
         <v>290.99999999999994</v>
       </c>
       <c r="E23" s="74" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F23" s="11"/>
       <c r="G23" s="11"/>
       <c r="I23" s="58" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J23" s="2">
         <v>2023</v>
@@ -16517,7 +16517,7 @@
     </row>
     <row r="24" spans="1:37" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B24" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C24" s="96">
         <f>C7*E15</f>
@@ -16528,10 +16528,10 @@
         <v>831.74607360000005</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="I24" s="58" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="J24" s="300">
         <v>445</v>
@@ -16620,7 +16620,7 @@
     </row>
     <row r="25" spans="1:37" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B25" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C25" s="96">
         <f>C8*E16</f>
@@ -16631,12 +16631,12 @@
         <v>749.56661919999999</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="26" spans="1:37" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B26" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C26" s="96">
         <f>C9*E17</f>
@@ -16647,7 +16647,7 @@
         <v>943.95</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="K26" s="136"/>
     </row>
@@ -16702,7 +16702,7 @@
   <sheetData>
     <row r="2" spans="2:17" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Q2" s="106" t="s">
         <v>21</v>
@@ -16710,17 +16710,17 @@
     </row>
     <row r="39" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="234" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="40" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="234" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="41" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="234" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="42" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16731,12 +16731,12 @@
     </row>
     <row r="44" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="2" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="45" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="267" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="I45" s="106"/>
     </row>
@@ -16746,39 +16746,39 @@
     </row>
     <row r="48" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B48" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="50" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B50" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="51" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B51" s="1" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="52" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B52" s="1" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="53" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B53" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.25">
@@ -16786,1111 +16786,1111 @@
         <v>33</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="55" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B55" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="56" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B56" s="1" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="57" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="58" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B59" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="60" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B60" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="61" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B61" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="D61" s="1" t="s">
         <v>222</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="62" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B62" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="D62" s="1" t="s">
         <v>224</v>
-      </c>
-      <c r="D62" s="1" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B63" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D63" s="1" t="s">
         <v>226</v>
-      </c>
-      <c r="D63" s="1" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="64" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B64" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="D64" s="1" t="s">
         <v>228</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="65" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B65" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D65" s="1" t="s">
         <v>230</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="66" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B66" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="D66" s="1" t="s">
         <v>232</v>
-      </c>
-      <c r="D66" s="1" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="67" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B67" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="D67" s="1" t="s">
         <v>234</v>
-      </c>
-      <c r="D67" s="1" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="68" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B68" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="D68" s="1" t="s">
         <v>236</v>
-      </c>
-      <c r="D68" s="1" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="69" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B69" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="D69" s="1" t="s">
         <v>238</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="70" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B70" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="D70" s="1" t="s">
         <v>240</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="71" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B71" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="D71" s="1" t="s">
         <v>242</v>
-      </c>
-      <c r="D71" s="1" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="72" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B72" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="D72" s="1" t="s">
         <v>244</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="73" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B73" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="D73" s="1" t="s">
         <v>246</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="74" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B74" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="D74" s="1" t="s">
         <v>248</v>
-      </c>
-      <c r="D74" s="1" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="75" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B75" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D75" s="1" t="s">
         <v>250</v>
-      </c>
-      <c r="D75" s="1" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="76" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B76" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="D76" s="1" t="s">
         <v>252</v>
-      </c>
-      <c r="D76" s="1" t="s">
-        <v>253</v>
       </c>
     </row>
     <row r="77" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B77" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="D77" s="1" t="s">
         <v>254</v>
-      </c>
-      <c r="D77" s="1" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="78" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B78" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="D78" s="1" t="s">
         <v>256</v>
-      </c>
-      <c r="D78" s="1" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="79" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B79" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="D79" s="1" t="s">
         <v>258</v>
-      </c>
-      <c r="D79" s="1" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="80" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B80" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="D80" s="1" t="s">
         <v>260</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="81" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B81" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="D81" s="1" t="s">
         <v>262</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="82" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B82" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="D82" s="1" t="s">
         <v>264</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="83" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B83" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="D83" s="1" t="s">
         <v>266</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="84" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B84" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="D84" s="1" t="s">
         <v>268</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="85" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B85" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="D85" s="1" t="s">
         <v>270</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="86" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B86" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="D86" s="1" t="s">
         <v>272</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="87" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B87" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="D87" s="1" t="s">
         <v>274</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="88" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B88" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="D88" s="1" t="s">
         <v>276</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="89" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B89" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="D89" s="1" t="s">
         <v>278</v>
-      </c>
-      <c r="D89" s="1" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="90" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B90" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="D90" s="1" t="s">
         <v>280</v>
-      </c>
-      <c r="D90" s="1" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="91" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B91" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="D91" s="1" t="s">
         <v>282</v>
-      </c>
-      <c r="D91" s="1" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="92" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B92" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="D92" s="1" t="s">
         <v>284</v>
-      </c>
-      <c r="D92" s="1" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="93" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B93" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="D93" s="1" t="s">
         <v>286</v>
-      </c>
-      <c r="D93" s="1" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="94" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B94" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="D94" s="1" t="s">
         <v>288</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="95" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B95" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="D95" s="1" t="s">
         <v>290</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="96" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B96" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="D96" s="1" t="s">
         <v>292</v>
-      </c>
-      <c r="D96" s="1" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="97" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B97" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="D97" s="1" t="s">
         <v>294</v>
-      </c>
-      <c r="D97" s="1" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="98" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B98" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="D98" s="1" t="s">
         <v>296</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="99" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B99" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="D99" s="1" t="s">
         <v>298</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="100" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B100" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="D100" s="1" t="s">
         <v>300</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="101" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B101" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="D101" s="1" t="s">
         <v>302</v>
-      </c>
-      <c r="D101" s="1" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="102" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B102" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="D102" s="1" t="s">
         <v>304</v>
-      </c>
-      <c r="D102" s="1" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="103" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B103" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="D103" s="1" t="s">
         <v>306</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="104" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B104" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="D104" s="1" t="s">
         <v>308</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="105" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B105" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="D105" s="1" t="s">
         <v>310</v>
-      </c>
-      <c r="D105" s="1" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="106" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B106" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="D106" s="1" t="s">
         <v>312</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="107" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B107" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="D107" s="1" t="s">
         <v>314</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="108" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B108" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="D108" s="1" t="s">
         <v>316</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="109" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B109" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="D109" s="1" t="s">
         <v>318</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="110" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B110" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="D110" s="1" t="s">
         <v>320</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>321</v>
       </c>
     </row>
     <row r="111" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B111" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="D111" s="1" t="s">
         <v>322</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>323</v>
       </c>
     </row>
     <row r="112" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B112" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="D112" s="1" t="s">
         <v>324</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="113" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B113" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="D113" s="1" t="s">
         <v>326</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="114" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B114" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="D114" s="1" t="s">
         <v>328</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>329</v>
       </c>
     </row>
     <row r="115" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B115" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="D115" s="1" t="s">
         <v>330</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="116" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B116" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="D116" s="1" t="s">
         <v>332</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="117" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B117" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="D117" s="1" t="s">
         <v>334</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="118" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B118" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="D118" s="1" t="s">
         <v>336</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="119" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B119" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="D119" s="1" t="s">
         <v>338</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="120" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B120" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="D120" s="1" t="s">
         <v>340</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>341</v>
       </c>
     </row>
     <row r="121" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B121" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="D121" s="1" t="s">
         <v>342</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="122" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B122" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="D122" s="1" t="s">
         <v>344</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>345</v>
       </c>
     </row>
     <row r="123" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B123" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="D123" s="1" t="s">
         <v>346</v>
-      </c>
-      <c r="D123" s="1" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="124" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B124" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="D124" s="1" t="s">
         <v>348</v>
-      </c>
-      <c r="D124" s="1" t="s">
-        <v>349</v>
       </c>
     </row>
     <row r="125" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B125" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="D125" s="1" t="s">
         <v>350</v>
-      </c>
-      <c r="D125" s="1" t="s">
-        <v>351</v>
       </c>
     </row>
     <row r="126" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B126" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="D126" s="1" t="s">
         <v>352</v>
-      </c>
-      <c r="D126" s="1" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="127" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B127" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="D127" s="1" t="s">
         <v>354</v>
-      </c>
-      <c r="D127" s="1" t="s">
-        <v>355</v>
       </c>
     </row>
     <row r="128" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B128" s="1" t="s">
+        <v>355</v>
+      </c>
+      <c r="D128" s="1" t="s">
         <v>356</v>
-      </c>
-      <c r="D128" s="1" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="129" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B129" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="D129" s="1" t="s">
         <v>358</v>
-      </c>
-      <c r="D129" s="1" t="s">
-        <v>359</v>
       </c>
     </row>
     <row r="130" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B130" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D130" s="1" t="s">
         <v>360</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="131" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B131" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="D131" s="1" t="s">
         <v>531</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>532</v>
       </c>
     </row>
     <row r="132" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B132" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="D132" s="1" t="s">
         <v>533</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>534</v>
       </c>
     </row>
     <row r="133" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B133" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="D133" s="1" t="s">
         <v>535</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="134" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B134" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="D134" s="1" t="s">
         <v>537</v>
-      </c>
-      <c r="D134" s="1" t="s">
-        <v>538</v>
       </c>
     </row>
     <row r="135" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B135" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="D135" s="1" t="s">
         <v>539</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="136" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B136" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="D136" s="1" t="s">
         <v>541</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>542</v>
       </c>
     </row>
     <row r="137" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B137" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="D137" s="1" t="s">
         <v>543</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="138" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B138" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="D138" s="1" t="s">
         <v>545</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="139" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B139" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="D139" s="1" t="s">
         <v>547</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="140" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B140" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="D140" s="1" t="s">
         <v>549</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="141" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B141" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="D141" s="1" t="s">
         <v>551</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="142" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B142" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="D142" s="1" t="s">
         <v>553</v>
-      </c>
-      <c r="D142" s="1" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="143" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B143" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="D143" s="1" t="s">
         <v>555</v>
-      </c>
-      <c r="D143" s="1" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="144" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B144" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="D144" s="1" t="s">
         <v>557</v>
-      </c>
-      <c r="D144" s="1" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="145" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B145" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="D145" s="1" t="s">
         <v>559</v>
-      </c>
-      <c r="D145" s="1" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="146" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B146" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="D146" s="1" t="s">
         <v>561</v>
-      </c>
-      <c r="D146" s="1" t="s">
-        <v>562</v>
       </c>
     </row>
     <row r="147" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B147" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="D147" s="1" t="s">
         <v>563</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="148" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B148" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="D148" s="1" t="s">
         <v>565</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>566</v>
       </c>
     </row>
     <row r="149" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B149" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="D149" s="1" t="s">
         <v>362</v>
-      </c>
-      <c r="D149" s="1" t="s">
-        <v>363</v>
       </c>
     </row>
     <row r="150" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B150" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="D150" s="1" t="s">
         <v>364</v>
-      </c>
-      <c r="D150" s="1" t="s">
-        <v>365</v>
       </c>
     </row>
     <row r="151" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B151" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="D151" s="1" t="s">
         <v>366</v>
-      </c>
-      <c r="D151" s="1" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="152" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B152" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="D152" s="1" t="s">
         <v>368</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>369</v>
       </c>
     </row>
     <row r="153" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B153" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="D153" s="1" t="s">
         <v>370</v>
-      </c>
-      <c r="D153" s="1" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="154" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B154" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="155" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B155" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="156" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B156" s="1" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="157" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B157" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="158" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B158" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="159" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B159" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="D159" s="1" t="s">
         <v>570</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="160" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B160" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="D160" s="1" t="s">
         <v>572</v>
-      </c>
-      <c r="D160" s="1" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="161" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B161" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="D161" s="1" t="s">
         <v>574</v>
-      </c>
-      <c r="D161" s="1" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="162" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B162" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="D162" s="1" t="s">
         <v>377</v>
-      </c>
-      <c r="D162" s="1" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="163" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B163" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="D163" s="1" t="s">
         <v>379</v>
-      </c>
-      <c r="D163" s="1" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="164" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B164" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="D164" s="1" t="s">
         <v>381</v>
-      </c>
-      <c r="D164" s="1" t="s">
-        <v>382</v>
       </c>
     </row>
     <row r="165" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B165" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D165" s="1" t="s">
         <v>383</v>
-      </c>
-      <c r="D165" s="1" t="s">
-        <v>384</v>
       </c>
     </row>
     <row r="166" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B166" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="D166" s="1" t="s">
         <v>385</v>
-      </c>
-      <c r="D166" s="1" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="167" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B167" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D167" s="1" t="s">
         <v>387</v>
-      </c>
-      <c r="D167" s="1" t="s">
-        <v>388</v>
       </c>
     </row>
     <row r="168" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B168" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="D168" s="1" t="s">
         <v>389</v>
-      </c>
-      <c r="D168" s="1" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="169" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B169" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="170" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B170" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="171" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B171" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="172" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B172" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="173" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B173" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="174" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B174" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="175" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B175" s="1" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="176" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B176" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="177" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B177" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="178" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B178" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="179" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B179" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="180" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B180" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="181" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B181" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="182" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B182" s="1" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="183" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B183" s="1" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="184" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B184" s="1" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
     </row>
     <row r="185" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B185" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="186" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B186" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="187" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B187" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="188" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B188" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="189" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B189" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="D189" s="1" t="s">
         <v>407</v>
-      </c>
-      <c r="D189" s="1" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="190" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B190" s="1" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="191" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B191" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="D191" s="1" t="s">
         <v>410</v>
-      </c>
-      <c r="D191" s="1" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="192" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B192" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="D192" s="1" t="s">
         <v>412</v>
-      </c>
-      <c r="D192" s="1" t="s">
-        <v>413</v>
       </c>
     </row>
   </sheetData>
@@ -17920,7 +17920,7 @@
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5"/>
@@ -17932,37 +17932,37 @@
         <v>32</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>198</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>200</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" s="3" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="5"/>
@@ -17971,7 +17971,7 @@
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.25">
@@ -17981,7 +17981,7 @@
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B11" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="5"/>
@@ -17990,22 +17990,22 @@
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B12" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B13" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B14" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
@@ -18014,38 +18014,38 @@
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" s="1" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" s="1" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>204</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" s="1" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B23" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="5"/>
@@ -18054,34 +18054,34 @@
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B26" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B27" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.25">
@@ -18100,12 +18100,12 @@
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B31" s="1" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B33" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="5"/>
@@ -18114,12 +18114,12 @@
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B34" s="12" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B35" s="12" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
   </sheetData>
@@ -18145,7 +18145,7 @@
   <sheetData>
     <row r="2" spans="2:5" ht="13.2" x14ac:dyDescent="0.25">
       <c r="B2" s="3" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C2" s="132"/>
       <c r="E2" s="106" t="s">
@@ -18154,159 +18154,159 @@
     </row>
     <row r="4" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B4" s="275" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C4" s="275" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="5" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C5" s="276" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="6" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B6" s="275" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C6" s="275" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="7" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C7" s="276" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="8" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B8" s="275" t="s">
+        <v>480</v>
+      </c>
+      <c r="C8" s="270" t="s">
         <v>481</v>
-      </c>
-      <c r="C8" s="270" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="9" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C9" s="276" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="10" spans="2:5" s="275" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="277" t="s">
+        <v>417</v>
+      </c>
+      <c r="C10" s="270" t="s">
         <v>418</v>
-      </c>
-      <c r="C10" s="270" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="11" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B11" s="270"/>
       <c r="C11" s="276" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="12" spans="2:5" s="275" customFormat="1" ht="22.8" x14ac:dyDescent="0.2">
       <c r="B12" s="278" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C12" s="275" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="13" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C13" s="276" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="14" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B14" s="275" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C14" s="275" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="15" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C15" s="276" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="16" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B16" s="278" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C16" s="275" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="17" spans="2:3" s="275" customFormat="1" ht="22.8" x14ac:dyDescent="0.2">
       <c r="C17" s="276" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="18" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B18" s="275" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C18" s="275" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="19" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C19" s="276" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="20" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B20" s="275" t="s">
+        <v>424</v>
+      </c>
+      <c r="C20" s="275" t="s">
         <v>425</v>
-      </c>
-      <c r="C20" s="275" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="21" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C21" s="276" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="22" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B22" s="275" t="s">
+        <v>454</v>
+      </c>
+      <c r="C22" s="275" t="s">
         <v>455</v>
-      </c>
-      <c r="C22" s="275" t="s">
-        <v>456</v>
       </c>
     </row>
     <row r="23" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C23" s="276" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="24" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B24" s="275" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C24" s="275" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="25" spans="2:3" s="275" customFormat="1" ht="22.8" x14ac:dyDescent="0.2">
       <c r="C25" s="276" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="26" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B26" s="275" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="C26" s="275" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="27" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C27" s="269" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="28" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -18355,7 +18355,7 @@
   <sheetData>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="I2" s="106" t="s">
         <v>21</v>
@@ -18374,10 +18374,10 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C6" s="388" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D6" s="389"/>
       <c r="E6" s="389"/>
@@ -18474,7 +18474,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C15" s="152">
         <v>20000</v>
@@ -18518,7 +18518,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B19" s="298" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C19" s="151">
         <v>2024</v>
@@ -18579,13 +18579,13 @@
         <v>37</v>
       </c>
       <c r="C26" s="153" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>38</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F26" s="274">
         <f>Grunddaten!E38</f>
@@ -18597,7 +18597,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B28" s="154" t="s">
-        <v>39</v>
+        <v>584</v>
       </c>
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
@@ -18621,17 +18621,17 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B30" s="170" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C30" s="10"/>
       <c r="D30" s="13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F30" s="10"/>
       <c r="G30" s="10"/>
       <c r="I30" s="7"/>
       <c r="J30" s="146" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K30" s="8"/>
       <c r="L30" s="8"/>
@@ -18643,14 +18643,14 @@
         <v>12</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C31" s="171">
         <v>50</v>
       </c>
       <c r="D31" s="242"/>
       <c r="E31" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F31" s="172"/>
       <c r="G31" s="173"/>
@@ -18666,7 +18666,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B32" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C32" s="10">
         <f>100-J31</f>
@@ -18790,7 +18790,7 @@
     </row>
     <row r="2" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C2" s="2" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D2" s="2"/>
       <c r="J2" s="7"/>
@@ -18811,7 +18811,7 @@
     </row>
     <row r="4" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C4" s="155" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D4" s="156"/>
       <c r="E4" s="156"/>
@@ -18841,7 +18841,7 @@
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C6" s="88" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D6" s="88"/>
       <c r="E6" s="161">
@@ -18867,23 +18867,23 @@
     </row>
     <row r="7" spans="2:18" s="91" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C7" s="162" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D7" s="162"/>
       <c r="E7" s="139" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" s="139" t="s">
+        <v>49</v>
+      </c>
+      <c r="G7" s="139" t="s">
+        <v>48</v>
+      </c>
+      <c r="H7" s="139" t="s">
+        <v>48</v>
+      </c>
+      <c r="I7" s="139" t="s">
         <v>50</v>
-      </c>
-      <c r="F7" s="139" t="s">
-        <v>50</v>
-      </c>
-      <c r="G7" s="139" t="s">
-        <v>49</v>
-      </c>
-      <c r="H7" s="139" t="s">
-        <v>49</v>
-      </c>
-      <c r="I7" s="139" t="s">
-        <v>51</v>
       </c>
       <c r="J7" s="163"/>
       <c r="K7" s="164"/>
@@ -18897,23 +18897,23 @@
     </row>
     <row r="8" spans="2:18" s="91" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C8" s="162" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D8" s="162"/>
       <c r="E8" s="139" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="139" t="s">
+        <v>53</v>
+      </c>
+      <c r="G8" s="139" t="s">
+        <v>52</v>
+      </c>
+      <c r="H8" s="139" t="s">
+        <v>52</v>
+      </c>
+      <c r="I8" s="139" t="s">
         <v>54</v>
-      </c>
-      <c r="F8" s="139" t="s">
-        <v>54</v>
-      </c>
-      <c r="G8" s="139" t="s">
-        <v>53</v>
-      </c>
-      <c r="H8" s="139" t="s">
-        <v>53</v>
-      </c>
-      <c r="I8" s="139" t="s">
-        <v>55</v>
       </c>
       <c r="J8" s="163"/>
       <c r="K8" s="235"/>
@@ -18930,23 +18930,23 @@
     </row>
     <row r="9" spans="2:18" s="91" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C9" s="162" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D9" s="162"/>
       <c r="E9" s="140" t="s">
+        <v>56</v>
+      </c>
+      <c r="F9" s="140" t="s">
         <v>57</v>
       </c>
-      <c r="F9" s="140" t="s">
+      <c r="G9" s="140" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="140" t="s">
+      <c r="H9" s="140" t="s">
         <v>59</v>
       </c>
-      <c r="H9" s="140" t="s">
+      <c r="I9" s="140" t="s">
         <v>60</v>
-      </c>
-      <c r="I9" s="140" t="s">
-        <v>61</v>
       </c>
       <c r="J9" s="238"/>
       <c r="K9" s="236"/>
@@ -18960,28 +18960,28 @@
     </row>
     <row r="10" spans="2:18" s="91" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C10" s="162" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D10" s="162"/>
       <c r="E10" s="140" t="s">
+        <v>63</v>
+      </c>
+      <c r="F10" s="140" t="s">
+        <v>62</v>
+      </c>
+      <c r="G10" s="140" t="s">
+        <v>62</v>
+      </c>
+      <c r="H10" s="140" t="s">
+        <v>459</v>
+      </c>
+      <c r="I10" s="140" t="s">
         <v>64</v>
-      </c>
-      <c r="F10" s="140" t="s">
-        <v>63</v>
-      </c>
-      <c r="G10" s="140" t="s">
-        <v>63</v>
-      </c>
-      <c r="H10" s="140" t="s">
-        <v>460</v>
-      </c>
-      <c r="I10" s="140" t="s">
-        <v>65</v>
       </c>
       <c r="J10" s="238"/>
       <c r="K10" s="236"/>
       <c r="L10" s="411" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="M10" s="411"/>
       <c r="N10" s="236"/>
@@ -18992,27 +18992,27 @@
     </row>
     <row r="11" spans="2:18" s="91" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="C11" s="162" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D11" s="162"/>
       <c r="E11" s="141" t="s">
+        <v>68</v>
+      </c>
+      <c r="F11" s="141" t="s">
+        <v>67</v>
+      </c>
+      <c r="G11" s="141" t="s">
+        <v>66</v>
+      </c>
+      <c r="H11" s="141" t="s">
+        <v>460</v>
+      </c>
+      <c r="I11" s="141" t="s">
         <v>69</v>
-      </c>
-      <c r="F11" s="141" t="s">
-        <v>68</v>
-      </c>
-      <c r="G11" s="141" t="s">
-        <v>67</v>
-      </c>
-      <c r="H11" s="141" t="s">
-        <v>461</v>
-      </c>
-      <c r="I11" s="141" t="s">
-        <v>70</v>
       </c>
       <c r="J11" s="238"/>
       <c r="K11" s="413" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="L11" s="413"/>
       <c r="M11" s="413"/>
@@ -19024,27 +19024,27 @@
     </row>
     <row r="12" spans="2:18" s="91" customFormat="1" ht="55.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C12" s="165" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D12" s="88"/>
       <c r="E12" s="141" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F12" s="141" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="G12" s="141" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H12" s="141" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="I12" s="141" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J12" s="164"/>
       <c r="K12" s="412" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L12" s="412"/>
       <c r="M12" s="412"/>
@@ -19090,10 +19090,10 @@
     </row>
     <row r="14" spans="2:18" s="91" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C14" s="162" t="s">
+        <v>74</v>
+      </c>
+      <c r="D14" s="263" t="s">
         <v>75</v>
-      </c>
-      <c r="D14" s="263" t="s">
-        <v>76</v>
       </c>
       <c r="E14" s="362"/>
       <c r="F14" s="365"/>
@@ -19101,7 +19101,7 @@
       <c r="H14" s="362"/>
       <c r="I14" s="362"/>
       <c r="J14" s="264" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="K14" s="236"/>
       <c r="L14" s="236"/>
@@ -19114,13 +19114,13 @@
     </row>
     <row r="15" spans="2:18" s="91" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="410" t="s">
+        <v>77</v>
+      </c>
+      <c r="C15" s="408" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="408" t="s">
+      <c r="D15" s="360" t="s">
         <v>79</v>
-      </c>
-      <c r="D15" s="360" t="s">
-        <v>80</v>
       </c>
       <c r="E15" s="366">
         <v>5</v>
@@ -19146,7 +19146,7 @@
       <c r="B16" s="410"/>
       <c r="C16" s="409"/>
       <c r="D16" s="166" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E16" s="358"/>
       <c r="F16" s="257"/>
@@ -19172,10 +19172,10 @@
     <row r="17" spans="2:18" s="91" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="410"/>
       <c r="C17" s="162" t="s">
+        <v>81</v>
+      </c>
+      <c r="D17" s="166" t="s">
         <v>82</v>
-      </c>
-      <c r="D17" s="166" t="s">
-        <v>83</v>
       </c>
       <c r="E17" s="258">
         <v>132</v>
@@ -19201,10 +19201,10 @@
     <row r="18" spans="2:18" s="91" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="410"/>
       <c r="C18" s="162" t="s">
+        <v>83</v>
+      </c>
+      <c r="D18" s="166" t="s">
         <v>84</v>
-      </c>
-      <c r="D18" s="166" t="s">
-        <v>85</v>
       </c>
       <c r="E18" s="258">
         <v>50.8</v>
@@ -19233,10 +19233,10 @@
     <row r="19" spans="2:18" s="91" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B19" s="410"/>
       <c r="C19" s="162" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D19" s="166" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E19" s="258">
         <v>0.35</v>
@@ -19262,10 +19262,10 @@
     <row r="20" spans="2:18" s="91" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="410"/>
       <c r="C20" s="162" t="s">
+        <v>86</v>
+      </c>
+      <c r="D20" s="166" t="s">
         <v>87</v>
-      </c>
-      <c r="D20" s="166" t="s">
-        <v>88</v>
       </c>
       <c r="E20" s="260"/>
       <c r="F20" s="261"/>
@@ -19286,10 +19286,10 @@
     </row>
     <row r="21" spans="2:18" s="91" customFormat="1" x14ac:dyDescent="0.3">
       <c r="C21" s="162" t="s">
+        <v>88</v>
+      </c>
+      <c r="D21" s="168" t="s">
         <v>89</v>
-      </c>
-      <c r="D21" s="168" t="s">
-        <v>90</v>
       </c>
       <c r="E21" s="257"/>
       <c r="F21" s="257"/>
@@ -19314,7 +19314,7 @@
     </row>
     <row r="22" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D22" s="228" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E22" s="368">
         <f>IF(AND(OR(Energie1="nicht verfügbar",COUNTIF(EnList1,Energie1)&lt;&gt;1),Antriebsart1&lt;&gt;0),1,0)</f>
@@ -19347,7 +19347,7 @@
     </row>
     <row r="23" spans="2:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C23" s="77" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D23" s="228"/>
       <c r="E23" s="368"/>
@@ -19362,14 +19362,14 @@
       <c r="R23" s="7"/>
     </row>
     <row r="24" spans="2:18" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="383" t="s">
+      <c r="B24" s="370" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="331" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D24" s="322" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E24" s="256">
         <v>219</v>
@@ -19393,10 +19393,10 @@
       <c r="R24" s="7"/>
     </row>
     <row r="25" spans="2:18" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="383"/>
+      <c r="B25" s="370"/>
       <c r="C25" s="331"/>
       <c r="D25" s="322" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E25" s="256"/>
       <c r="F25" s="256"/>
@@ -19410,10 +19410,10 @@
       <c r="R25" s="7"/>
     </row>
     <row r="26" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B26" s="383"/>
+      <c r="B26" s="370"/>
       <c r="C26" s="335"/>
       <c r="D26" s="322" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E26" s="256"/>
       <c r="F26" s="256"/>
@@ -19428,7 +19428,7 @@
     </row>
     <row r="27" spans="2:18" x14ac:dyDescent="0.25">
       <c r="D27" s="228" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E27" s="368">
         <f>IF(OR(AND(COUNT(E15:E21)&lt;7,Antriebsart1="Plug-In-Hybrid (PHEV)"),AND(COUNT(E16,E21)&lt;2,Antriebsart1="Vollelektrisch (BEV)"),AND(COUNT(E15,E17:E19)&lt;4,Antriebsart1="Verbrenner")),1,0)</f>
@@ -19461,7 +19461,7 @@
     </row>
     <row r="28" spans="2:18" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E28" s="405" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F28" s="406"/>
       <c r="G28" s="406"/>
@@ -19470,7 +19470,7 @@
     </row>
     <row r="29" spans="2:18" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E29" s="400" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F29" s="387"/>
       <c r="G29" s="387"/>
@@ -19486,7 +19486,7 @@
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C32" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
   </sheetData>
@@ -19870,7 +19870,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B1" s="118" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C1" s="118"/>
       <c r="D1" s="118"/>
@@ -19884,7 +19884,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="65" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C2" s="227"/>
       <c r="D2" s="230" t="str">
@@ -19912,7 +19912,7 @@
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="18"/>
       <c r="B4" s="154" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -19927,7 +19927,7 @@
     <row r="6" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="18"/>
       <c r="B6" s="12" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C6" s="418" t="str">
         <f>IF(Projektname=0,"",Projektname)</f>
@@ -20009,7 +20009,7 @@
       <c r="B12" s="12"/>
       <c r="C12" s="76"/>
       <c r="E12" s="58" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="F12" s="85">
         <f>Fahrleistung</f>
@@ -20049,7 +20049,7 @@
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="18"/>
       <c r="B15" s="293" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C15" s="21"/>
       <c r="D15" s="21"/>
@@ -20061,7 +20061,7 @@
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="18"/>
       <c r="B16" s="37" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C16" s="23"/>
       <c r="D16" s="24">
@@ -20108,10 +20108,10 @@
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="18"/>
       <c r="B18" s="177" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C18" s="178" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D18" s="179">
         <f>IF(FinArt="Kauf",Gesamtpreis1,"")</f>
@@ -20144,7 +20144,7 @@
         <v>Wertminderung</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D19" s="41">
         <f>Erg.Fzg._1!$C$54+Erg.Fzg._1!$C$55</f>
@@ -20170,10 +20170,10 @@
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="336"/>
       <c r="B20" s="45" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D20" s="41">
         <f>Erg.Fzg._1!$C$56</f>
@@ -20201,10 +20201,10 @@
         <v>12</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C21" s="28" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D21" s="43">
         <f>Erg.Fzg._1!$C$57</f>
@@ -20230,10 +20230,10 @@
     <row r="22" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="416"/>
       <c r="B22" s="27" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C22" s="28" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D22" s="43">
         <f>Erg.Fzg._1!C41*Haltedauer</f>
@@ -20260,10 +20260,10 @@
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" s="417"/>
       <c r="B23" s="45" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C23" s="325" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D23" s="326">
         <f>Erg.Fzg._1!$C$59</f>
@@ -20385,10 +20385,10 @@
     <row r="27" spans="1:9" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="18"/>
       <c r="B27" s="49" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C27" s="50" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D27" s="51">
         <f>IF(SUM(D19:D26)=0,"",SUM(D19:D26))</f>
@@ -20414,7 +20414,7 @@
     <row r="28" spans="1:9" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="18"/>
       <c r="B28" s="75" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C28" s="50"/>
       <c r="D28" s="51">
@@ -20442,10 +20442,10 @@
     <row r="29" spans="1:9" ht="20.399999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A29" s="18"/>
       <c r="B29" s="108" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C29" s="66" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D29" s="231">
         <f>IF(AND(COUNTIF(D19:D23,0)&gt;0,Antriebsart1="Plug-In-Hybrid (PHEV)"),1,IF(AND(COUNTIF(D19:D23,0)&gt;1,Antriebsart1&lt;&gt;0),1,0))</f>
@@ -20475,10 +20475,10 @@
     <row r="30" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="33"/>
       <c r="B30" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="C30" s="316" t="s">
         <v>105</v>
-      </c>
-      <c r="C30" s="316" t="s">
-        <v>106</v>
       </c>
       <c r="D30" s="314">
         <f>Erg.Fzg._1!$C$65</f>
@@ -20504,10 +20504,10 @@
     <row r="31" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="309"/>
       <c r="B31" s="98" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C31" s="317" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D31" s="318">
         <f>Erg.Fzg._1!$C$66</f>
@@ -20534,10 +20534,10 @@
     <row r="32" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="309"/>
       <c r="B32" s="310" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C32" s="311" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D32" s="312">
         <f>SUM(D30:D31)</f>
@@ -20563,7 +20563,7 @@
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B34" s="293" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C34" s="21"/>
       <c r="D34" s="21"/>
@@ -20694,7 +20694,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B1" s="118" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="C1" s="118"/>
       <c r="D1" s="118"/>
@@ -20708,7 +20708,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="65" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C2" s="227"/>
       <c r="D2" s="230" t="str">
@@ -20736,7 +20736,7 @@
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="18"/>
       <c r="B4" s="154" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -20751,7 +20751,7 @@
     <row r="6" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="18"/>
       <c r="B6" s="12" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C6" s="418" t="str">
         <f>IF(Projektname=0,"",Projektname)</f>
@@ -20833,7 +20833,7 @@
       <c r="B12" s="12"/>
       <c r="C12" s="76"/>
       <c r="E12" s="58" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="F12" s="85">
         <f>Fahrleistung</f>
@@ -20873,7 +20873,7 @@
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="18"/>
       <c r="B15" s="293" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C15" s="21"/>
       <c r="D15" s="21"/>
@@ -20885,7 +20885,7 @@
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="18"/>
       <c r="B16" s="37" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C16" s="23"/>
       <c r="D16" s="24">
@@ -20934,10 +20934,10 @@
         <v>12</v>
       </c>
       <c r="B18" s="27" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C18" s="28" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D18" s="43">
         <f>Erg.Fzg._1!$C$57-D19</f>
@@ -20963,10 +20963,10 @@
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" s="416"/>
       <c r="B19" s="27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C19" s="28" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D19" s="43">
         <f>(Erg.Fzg._1!$C$35+Erg.Fzg._1!$C$36)*Haltedauer</f>
@@ -20992,10 +20992,10 @@
     <row r="20" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="416"/>
       <c r="B20" s="27" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C20" s="28" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D20" s="43">
         <f>Erg.Fzg._1!C41*Haltedauer</f>
@@ -21022,10 +21022,10 @@
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="416"/>
       <c r="B21" s="29" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C21" s="46" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D21" s="47">
         <f>Erg.Fzg._1!$C$59</f>
@@ -21051,10 +21051,10 @@
     <row r="22" spans="1:9" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="18"/>
       <c r="B22" s="49" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C22" s="50" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D22" s="51">
         <f>IF(SUM(D18:D21)=0,"",SUM(D18:D21))</f>
@@ -21080,7 +21080,7 @@
     <row r="23" spans="1:9" ht="15" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="18"/>
       <c r="B23" s="75" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C23" s="50"/>
       <c r="D23" s="51">
@@ -21108,10 +21108,10 @@
     <row r="24" spans="1:9" ht="20.399999999999999" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A24" s="18"/>
       <c r="B24" s="108" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C24" s="66" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D24" s="231">
         <f>IF(AND(COUNTIF(D18:D21,0)&gt;0,Antriebsart1="Plug-In-Hybrid (PHEV)"),1,IF(AND(COUNTIF(D18:D21,0)&gt;1,Antriebsart1="Verbrenner"),1,IF(AND(COUNTIF(D18:D21,0)&gt;2,Antriebsart1&lt;&gt;""),1,0)))</f>
@@ -21141,10 +21141,10 @@
     <row r="25" spans="1:9" ht="25.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="33"/>
       <c r="B25" s="34" t="s">
+        <v>104</v>
+      </c>
+      <c r="C25" s="31" t="s">
         <v>105</v>
-      </c>
-      <c r="C25" s="31" t="s">
-        <v>106</v>
       </c>
       <c r="D25" s="32">
         <f>Erg.Fzg._1!$C$65</f>
@@ -21170,10 +21170,10 @@
     <row r="26" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="33"/>
       <c r="B26" s="98" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C26" s="99" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D26" s="35">
         <f>Erg.Fzg._1!$C$66</f>
@@ -21200,10 +21200,10 @@
     <row r="27" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="33"/>
       <c r="B27" s="310" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C27" s="311" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D27" s="312">
         <f>SUM(D25:D26)</f>
@@ -21229,7 +21229,7 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B29" s="293" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="C29" s="21"/>
       <c r="D29" s="21"/>
@@ -21366,7 +21366,7 @@
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="119"/>
       <c r="B2" s="189" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C2" s="119"/>
       <c r="D2" s="119"/>
@@ -21391,7 +21391,7 @@
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="119"/>
       <c r="B4" s="293" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C4" s="354"/>
       <c r="D4" s="354"/>
@@ -21401,7 +21401,7 @@
       <c r="H4" s="119"/>
     </row>
     <row r="5" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="383" t="s">
+      <c r="A5" s="370" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="219"/>
@@ -21412,30 +21412,30 @@
       <c r="G5" s="190"/>
       <c r="H5" s="119"/>
       <c r="J5" s="427" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K5" s="427"/>
       <c r="L5" s="427"/>
     </row>
     <row r="6" spans="1:12" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A6" s="383"/>
+      <c r="A6" s="370"/>
       <c r="B6" s="220" t="s">
+        <v>111</v>
+      </c>
+      <c r="C6" s="220" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" s="221" t="s">
         <v>112</v>
       </c>
-      <c r="C6" s="220" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" s="221" t="s">
+      <c r="E6" s="226" t="s">
         <v>113</v>
       </c>
-      <c r="E6" s="226" t="s">
+      <c r="F6" s="221" t="s">
         <v>114</v>
       </c>
-      <c r="F6" s="221" t="s">
+      <c r="G6" s="306" t="s">
         <v>115</v>
-      </c>
-      <c r="G6" s="306" t="s">
-        <v>116</v>
       </c>
       <c r="H6" s="119"/>
       <c r="J6" s="427"/>
@@ -21445,17 +21445,17 @@
     <row r="7" spans="1:12" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="352"/>
       <c r="B7" s="428" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C7" s="222" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D7" s="223">
         <v>120</v>
       </c>
       <c r="E7" s="272"/>
       <c r="F7" s="222" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G7" s="307">
         <f t="shared" ref="G7:G17" si="0">IF(ISBLANK(E7),D7,E7)</f>
@@ -21470,14 +21470,14 @@
       <c r="A8" s="352"/>
       <c r="B8" s="429"/>
       <c r="C8" s="222" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D8" s="223">
         <v>130</v>
       </c>
       <c r="E8" s="272"/>
       <c r="F8" s="222" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G8" s="307">
         <f t="shared" si="0"/>
@@ -21492,14 +21492,14 @@
       <c r="A9" s="352"/>
       <c r="B9" s="430"/>
       <c r="C9" s="222" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D9" s="223">
         <v>20</v>
       </c>
       <c r="E9" s="272"/>
       <c r="F9" s="222" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G9" s="307">
         <f t="shared" si="0"/>
@@ -21513,17 +21513,17 @@
     <row r="10" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
       <c r="A10" s="352"/>
       <c r="B10" s="356" t="s">
+        <v>119</v>
+      </c>
+      <c r="C10" s="222" t="s">
         <v>120</v>
-      </c>
-      <c r="C10" s="222" t="s">
-        <v>121</v>
       </c>
       <c r="D10" s="367">
         <v>64</v>
       </c>
       <c r="E10" s="272"/>
       <c r="F10" s="222" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G10" s="307">
         <f t="shared" si="0"/>
@@ -21537,17 +21537,17 @@
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="352"/>
       <c r="B11" s="356" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C11" s="222" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D11" s="367">
         <v>3.6</v>
       </c>
       <c r="E11" s="272"/>
       <c r="F11" s="222" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="G11" s="307">
         <f t="shared" si="0"/>
@@ -21561,17 +21561,17 @@
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="352"/>
       <c r="B12" s="428" t="s">
+        <v>122</v>
+      </c>
+      <c r="C12" s="222" t="s">
         <v>123</v>
-      </c>
-      <c r="C12" s="222" t="s">
-        <v>124</v>
       </c>
       <c r="D12" s="223">
         <v>19</v>
       </c>
       <c r="E12" s="272"/>
       <c r="F12" s="222" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G12" s="307">
         <f t="shared" si="0"/>
@@ -21586,14 +21586,14 @@
       <c r="A13" s="352"/>
       <c r="B13" s="429"/>
       <c r="C13" s="222" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D13" s="223">
         <v>21</v>
       </c>
       <c r="E13" s="272"/>
       <c r="F13" s="222" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G13" s="307">
         <f>IF(ISBLANK(E13),D13,E13)</f>
@@ -21610,14 +21610,14 @@
       </c>
       <c r="B14" s="429"/>
       <c r="C14" s="222" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D14" s="223" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E14" s="272"/>
       <c r="F14" s="222" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G14" s="307" t="str">
         <f>IF(ISBLANK(E14),"keine",E14)</f>
@@ -21632,14 +21632,14 @@
       <c r="A15" s="416"/>
       <c r="B15" s="429"/>
       <c r="C15" s="222" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D15" s="223" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E15" s="272"/>
       <c r="F15" s="222" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="G15" s="307" t="str">
         <f t="shared" ref="G15" si="1">IF(ISBLANK(E15),"keine",E15)</f>
@@ -21654,14 +21654,14 @@
       <c r="A16" s="416"/>
       <c r="B16" s="430"/>
       <c r="C16" s="222" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="D16" s="223" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E16" s="272"/>
       <c r="F16" s="222" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G16" s="307" t="str">
         <f>IF(ISBLANK(E16),"keine",E16)</f>
@@ -21675,17 +21675,17 @@
     <row r="17" spans="1:12" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A17" s="353"/>
       <c r="B17" s="357" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C17" s="225" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D17" s="224">
         <v>60</v>
       </c>
       <c r="E17" s="273"/>
       <c r="F17" s="225" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G17" s="307">
         <f t="shared" si="0"/>
@@ -21719,11 +21719,11 @@
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="193"/>
       <c r="B21" s="192" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C21" s="192"/>
       <c r="D21" s="193" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E21" s="193"/>
       <c r="F21" s="193"/>
@@ -21745,7 +21745,7 @@
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="196"/>
       <c r="B23" s="293" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C23" s="339"/>
       <c r="D23" s="340"/>
@@ -21769,15 +21769,15 @@
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="196"/>
       <c r="B25" s="346" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C25" s="327"/>
       <c r="D25" s="296" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E25" s="347"/>
       <c r="F25" s="295" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G25" s="194"/>
       <c r="H25" s="195"/>
@@ -21789,23 +21789,23 @@
       <c r="C26" s="327"/>
       <c r="D26" s="209"/>
       <c r="E26" s="210" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F26" s="294"/>
       <c r="G26" s="308" t="s">
+        <v>130</v>
+      </c>
+      <c r="H26" s="198" t="s">
         <v>131</v>
       </c>
-      <c r="H26" s="198" t="s">
+      <c r="I26" s="255" t="s">
         <v>132</v>
-      </c>
-      <c r="I26" s="255" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="27" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A27" s="204"/>
       <c r="B27" s="212" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C27" s="213"/>
       <c r="D27" s="214">
@@ -21813,21 +21813,21 @@
       </c>
       <c r="E27" s="243"/>
       <c r="F27" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G27" s="308">
         <f>IF(ISNUMBER(E27),E27,D27)/100</f>
         <v>0.41399999999999998</v>
       </c>
       <c r="H27" s="199" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="I27" s="254"/>
     </row>
     <row r="28" spans="1:12" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A28" s="204"/>
       <c r="B28" s="215" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C28" s="211"/>
       <c r="D28" s="214">
@@ -21835,21 +21835,21 @@
       </c>
       <c r="E28" s="243"/>
       <c r="F28" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G28" s="308">
         <f>IF(ISNUMBER(E28),E28,D28)/100</f>
         <v>0.59</v>
       </c>
       <c r="H28" s="199" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="I28" s="254"/>
     </row>
     <row r="29" spans="1:12" ht="14.4" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="205"/>
       <c r="B29" s="216" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C29" s="348"/>
       <c r="D29" s="349"/>
@@ -21865,7 +21865,7 @@
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="433"/>
       <c r="B30" s="212" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C30" s="213"/>
       <c r="D30" s="271">
@@ -21873,21 +21873,21 @@
       </c>
       <c r="E30" s="243"/>
       <c r="F30" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G30" s="308">
         <f t="shared" ref="G30:G32" si="2">IF(ISNUMBER(E30),E30,D30)</f>
         <v>1.6719999999999999</v>
       </c>
       <c r="H30" s="199" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="I30" s="254"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="433"/>
       <c r="B31" s="212" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C31" s="213"/>
       <c r="D31" s="271">
@@ -21895,21 +21895,21 @@
       </c>
       <c r="E31" s="243"/>
       <c r="F31" s="9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G31" s="308">
         <f t="shared" si="2"/>
         <v>1.788</v>
       </c>
       <c r="H31" s="199" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="I31" s="254"/>
     </row>
     <row r="32" spans="1:12" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A32" s="205"/>
       <c r="B32" s="212" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C32" s="213"/>
       <c r="D32" s="217">
@@ -21917,14 +21917,14 @@
       </c>
       <c r="E32" s="243"/>
       <c r="F32" s="9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="G32" s="308">
         <f t="shared" si="2"/>
         <v>1.3</v>
       </c>
       <c r="H32" s="199" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="I32" s="254"/>
     </row>
@@ -21953,7 +21953,7 @@
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="193"/>
       <c r="B35" s="293" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C35" s="339"/>
       <c r="D35" s="340"/>
@@ -21966,14 +21966,14 @@
     <row r="36" spans="1:9" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="193"/>
       <c r="B36" s="434" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C36" s="435"/>
       <c r="D36" s="435"/>
       <c r="E36" s="435"/>
       <c r="F36" s="436"/>
       <c r="G36" s="308" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H36" s="202"/>
       <c r="I36" s="202"/>
@@ -21984,10 +21984,10 @@
       <c r="C37" s="327"/>
       <c r="D37" s="327"/>
       <c r="E37" s="342" t="s">
+        <v>113</v>
+      </c>
+      <c r="F37" s="343" t="s">
         <v>114</v>
-      </c>
-      <c r="F37" s="343" t="s">
-        <v>115</v>
       </c>
       <c r="G37" s="308"/>
       <c r="H37" s="195"/>
@@ -21996,7 +21996,7 @@
     <row r="38" spans="1:9" ht="16.2" x14ac:dyDescent="0.35">
       <c r="A38" s="207"/>
       <c r="B38" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C38" s="327"/>
       <c r="D38" s="218">
@@ -22012,7 +22012,7 @@
         <v>860</v>
       </c>
       <c r="H38" s="199" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="I38" s="254"/>
     </row>
@@ -22030,7 +22030,7 @@
     <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" s="193"/>
       <c r="B40" s="6" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C40" s="327"/>
       <c r="D40" s="218">
@@ -22038,21 +22038,21 @@
       </c>
       <c r="E40" s="243"/>
       <c r="F40" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G40" s="308">
         <f>IF(ISNUMBER(E40),E40,D40)</f>
         <v>0.02</v>
       </c>
       <c r="H40" s="199" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I40" s="254"/>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" s="193"/>
       <c r="B41" s="215" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C41" s="72"/>
       <c r="D41" s="218">
@@ -22060,14 +22060,14 @@
       </c>
       <c r="E41" s="243"/>
       <c r="F41" s="9" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G41" s="308">
         <f>IF(ISNUMBER(E41),E41,D41)</f>
         <v>0.15</v>
       </c>
       <c r="H41" s="199" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="I41" s="254"/>
     </row>
@@ -22096,7 +22096,7 @@
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="193"/>
       <c r="B44" s="293" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C44" s="340"/>
       <c r="D44" s="340"/>
@@ -22109,7 +22109,7 @@
     <row r="45" spans="1:9" ht="16.2" x14ac:dyDescent="0.35">
       <c r="A45" s="193"/>
       <c r="B45" s="431" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="C45" s="432"/>
       <c r="D45" s="218">
@@ -22117,21 +22117,21 @@
       </c>
       <c r="E45" s="243"/>
       <c r="F45" s="9" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G45" s="308">
         <f>IF(ISNUMBER(E45),E45,D45)</f>
         <v>84</v>
       </c>
       <c r="H45" s="199" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I45" s="254"/>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" s="193"/>
       <c r="B46" s="246" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C46" s="247"/>
       <c r="D46" s="247"/>
@@ -22246,7 +22246,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>21</v>
@@ -22259,7 +22259,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B4" s="154" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C4" s="89"/>
       <c r="D4" s="89"/>
@@ -22273,7 +22273,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C6" s="54">
         <v>1</v>
@@ -22285,7 +22285,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C7" s="102" t="str">
         <f>IF(Anbieter1=0,"",Anbieter1)</f>
@@ -22305,14 +22305,14 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C9" s="102"/>
       <c r="F9" s="125"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C10" s="102" t="str">
         <f>IF(Hersteller1=0,"",Hersteller1)</f>
@@ -22323,7 +22323,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C11" s="102" t="str">
         <f>IF(Modell1=0,"",Modell1)</f>
@@ -22334,7 +22334,7 @@
     </row>
     <row r="12" spans="1:7" ht="43.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="56" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C12" s="102" t="str">
         <f>IF(Zusatzinfo1=0,"",Zusatzinfo1)</f>
@@ -22345,7 +22345,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B13" s="57" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C13" s="102" t="str">
         <f>IF(Antriebsart1=0,"",Antriebsart1)</f>
@@ -22356,7 +22356,7 @@
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="107"/>
       <c r="B14" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C14" s="102" t="str">
         <f>IF(Energie1=0,"",Energie1)</f>
@@ -22373,7 +22373,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B16" s="154" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -22387,7 +22387,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B18" s="72" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C18" s="288">
         <f>0.0057*(ReichwPHEV1/23)^3-0.0838*(ReichwPHEV1/23)^2+0.4261*(ReichwPHEV1/23)+ 0.1633</f>
@@ -22398,33 +22398,33 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C19" s="289">
         <f>Verbrauch1/(1-0.9*C18)</f>
         <v>5.8614585653494018</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F19" s="125"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B20" s="72" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C20" s="290">
         <f>VerbEl_WLTP1/C18</f>
         <v>0</v>
       </c>
       <c r="D20" s="184" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F20" s="125"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B21" s="186" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C21" s="291">
         <f>0.0021*(ReichwPHEV1/23)^3-0.0358*(ReichwPHEV1/23)^2+0.2607*(ReichwPHEV1/23)- 0.0267</f>
@@ -22438,14 +22438,14 @@
         <v>12</v>
       </c>
       <c r="B22" s="439" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C22" s="292">
         <f>C19*(1-0.9*C21)</f>
         <v>6.0023094146747482</v>
       </c>
       <c r="D22" s="185" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F22" s="125"/>
     </row>
@@ -22457,7 +22457,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="183" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F23" s="125"/>
     </row>
@@ -22468,7 +22468,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B25" s="154" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C25" s="89"/>
       <c r="D25" s="89"/>
@@ -22479,7 +22479,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B27" s="60" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C27" s="61"/>
       <c r="D27" s="60"/>
@@ -22487,39 +22487,39 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C28" s="279">
         <f>IF(Antriebsart1="Vollelektrisch (BEV)",0,IFERROR(VLOOKUP(Energie1,EnKostList,6,FALSE),0)*IF(Antriebsart1="Plug-In-Hybrid (PHEV)",VerbPHEV1,Verbrauch1)/100*Fahrleistung)</f>
         <v>1671.9999999999998</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F28" s="125"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C29" s="279">
         <f>IF(Antriebsart1="Verbrenner",0,VLOOKUP("Strom",EnKostList,6,FALSE)*IF(Antriebsart1="Plug-In-Hybrid (PHEV)",VerbElPHEV1,VerbEl_WLTP1)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="64" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C30" s="280">
         <f>SUM(C28:C29)</f>
         <v>1671.9999999999998</v>
       </c>
       <c r="D30" s="64" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="14.4" thickTop="1" x14ac:dyDescent="0.25">
@@ -22528,7 +22528,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B32" s="60" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C32" s="145" t="str">
         <f>CONCATENATE("Energieträger: ",Energie1)</f>
@@ -22539,63 +22539,63 @@
     </row>
     <row r="33" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B33" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C33" s="279">
         <f>IF(Antriebsart1="Plug-In-Hybrid (PHEV)",VerbPHEV1*VLOOKUP(Energie1,CO2List,2,FALSE)/100,CO2_1)*Fahrleistung/1000000</f>
         <v>2.64</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F33" s="107"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C34" s="279">
         <f>C33*Kost_THG</f>
         <v>2270.4</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B35" s="1" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C35" s="279">
         <f>IF(Energie1="Strom",0,NOX_1*Fahrleistung*Kost_NOX/1000)</f>
         <v>20.32</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B36" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C36" s="279">
         <f>IF(Energie1="Strom",0,Partikel1*Fahrleistung*Kost_Partikel/1000)</f>
         <v>1.05</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="64" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C37" s="280">
         <f>SUM(C34:C36)</f>
         <v>2291.7700000000004</v>
       </c>
       <c r="D37" s="64" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="14.4" thickTop="1" x14ac:dyDescent="0.25">
@@ -22603,7 +22603,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B39" s="60" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C39" s="145" t="str">
         <f>CONCATENATE("Energieträger: ",Energie1,IF(Antriebsart1="Plug-In-Hybrid (PHEV)","+Strom",""))</f>
@@ -22613,32 +22613,32 @@
     </row>
     <row r="40" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B40" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C40" s="279">
         <f>IFERROR(IF(Antriebsart1="Vollelektrisch (BEV)",VLOOKUP("Strom",CO2List,3,FALSE)*VerbEl_WLTP1/100*Fahrleistung/1000000,IF(Antriebsart1="Verbrenner",VLOOKUP(Energie1,CO2List,3,FALSE)*Verbrauch1/100*Fahrleistung/1000000,VLOOKUP(Energie1,CO2List,3,FALSE)*VerbPHEV1/100*Fahrleistung/1000000+VLOOKUP("Strom",CO2List,3,FALSE)*VerbElPHEV1/100*Fahrleistung/1000000)),0)</f>
         <v>0.83174607360000008</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F40" s="107"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B41" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C41" s="279">
         <f>C40*Kost_THG</f>
         <v>715.30162329600012</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B43" s="154" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C43" s="89"/>
       <c r="D43" s="89"/>
@@ -22652,53 +22652,53 @@
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="107"/>
       <c r="B45" s="90" t="s">
+        <v>170</v>
+      </c>
+      <c r="C45" s="134" t="s">
         <v>171</v>
       </c>
-      <c r="C45" s="134" t="s">
-        <v>172</v>
-      </c>
       <c r="D45" s="62"/>
     </row>
     <row r="46" spans="1:6" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="383" t="s">
+      <c r="A46" s="370" t="s">
         <v>12</v>
       </c>
       <c r="B46" s="437" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C46" s="281">
         <f>IF(OR(Antriebsart1="Vollelektrisch (BEV)",Antriebsart1="Plug-In-Hybrid (PHEV)"),Batterie1*Batterie_THG/1000,0)</f>
         <v>0</v>
       </c>
       <c r="D46" s="131" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E46" s="127"/>
       <c r="F46" s="107"/>
     </row>
     <row r="47" spans="1:6" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="383"/>
+      <c r="A47" s="370"/>
       <c r="B47" s="438"/>
       <c r="C47" s="281">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
         <v>0</v>
       </c>
       <c r="D47" s="130" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E47" s="127"/>
       <c r="F47" s="107"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B48" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C48" s="279">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Kost_THG, C46/Haltedauer*Kost_THG)</f>
         <v>0</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
@@ -22717,19 +22717,19 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B52" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B54" s="68" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C54" s="282">
         <f>IF(FinArt="Kauf",IF(KaufpreisRech="Kaufpreis",Gesamtpreis1,0),Gesamtpreis1*Haltedauer*12+IF(FinArt="Leasing",LeasSondZahl1,0))</f>
         <v>0</v>
       </c>
       <c r="D54" s="68" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F54" s="58"/>
     </row>
@@ -22738,71 +22738,71 @@
         <v>12</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C55" s="283">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis1-Gesamtpreis1*(-0.2*LN(Haltedauer)+0.667),0)</f>
         <v>24164.210717478156</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F55" s="58"/>
     </row>
     <row r="56" spans="1:6" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C56" s="283">
         <f>C30*Haltedauer</f>
         <v>11703.999999999998</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F56" s="58"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C57" s="283">
         <f>C37*Haltedauer</f>
         <v>16042.390000000003</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F57" s="58"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C58" s="283">
         <f>C41*Haltedauer</f>
         <v>5007.111363072001</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F58" s="58"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B59" s="329" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C59" s="330">
         <f>C48*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D59" s="329" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="383" t="s">
+      <c r="A60" s="370" t="s">
         <v>12</v>
       </c>
       <c r="B60" s="327" t="str">
@@ -22820,7 +22820,7 @@
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="383"/>
+      <c r="A61" s="370"/>
       <c r="B61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
@@ -22836,7 +22836,7 @@
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="383"/>
+      <c r="A62" s="370"/>
       <c r="B62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
@@ -22853,14 +22853,14 @@
     </row>
     <row r="63" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B63" s="64" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C63" s="284">
         <f>SUM(C54:C62)</f>
         <v>58450.712080550154</v>
       </c>
       <c r="D63" s="64" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F63" s="58"/>
     </row>
@@ -22869,26 +22869,26 @@
     </row>
     <row r="65" spans="2:4" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B65" s="68" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C65" s="285">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Haltedauer, C46)</f>
         <v>0</v>
       </c>
       <c r="D65" s="68" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="66" spans="2:4" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B66" s="72" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C66" s="286">
         <f>C33*Haltedauer+C40*Haltedauer</f>
         <v>24.3022225152</v>
       </c>
       <c r="D66" s="72" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -22938,7 +22938,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>21</v>
@@ -22951,7 +22951,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B4" s="154" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -22967,7 +22967,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C6" s="54">
         <v>2</v>
@@ -22980,7 +22980,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C7" s="102" t="str">
         <f>IF(Anbieter2=0,"",Anbieter2)</f>
@@ -23002,7 +23002,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C9" s="102"/>
       <c r="E9" s="125"/>
@@ -23010,7 +23010,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C10" s="102" t="str">
         <f>IF(Hersteller2=0,"",Hersteller2)</f>
@@ -23022,7 +23022,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C11" s="102" t="str">
         <f>IF(Modell2=0,"",Modell2)</f>
@@ -23034,7 +23034,7 @@
     </row>
     <row r="12" spans="1:6" ht="43.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="56" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C12" s="102" t="str">
         <f>IF(Zusatzinfo2=0,"",Zusatzinfo2)</f>
@@ -23046,7 +23046,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B13" s="57" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C13" s="102" t="str">
         <f>IF(Antriebsart2=0,"",Antriebsart2)</f>
@@ -23057,7 +23057,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C14" s="102" t="str">
         <f>IF(Energie2=0,"",Energie2)</f>
@@ -23073,7 +23073,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B16" s="154" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -23089,7 +23089,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B18" s="72" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C18" s="288">
         <f>0.0057*(ReichwPHEV2/23)^3-0.0838*(ReichwPHEV2/23)^2+0.4261*(ReichwPHEV2/23)+ 0.1633</f>
@@ -23101,35 +23101,35 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C19" s="289">
         <f>Verbrauch2/(1-0.9*C18)</f>
         <v>5.0408543662004854</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E19" s="125"/>
       <c r="F19" s="125"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B20" s="72" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C20" s="290">
         <f>VerbEl_WLTP2/C18</f>
         <v>0</v>
       </c>
       <c r="D20" s="184" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E20" s="125"/>
       <c r="F20" s="125"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B21" s="186" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C21" s="291">
         <f>0.0021*(ReichwPHEV2/23)^3-0.0358*(ReichwPHEV2/23)^2+0.2607*(ReichwPHEV2/23)- 0.0267</f>
@@ -23144,14 +23144,14 @@
         <v>12</v>
       </c>
       <c r="B22" s="439" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C22" s="292">
         <f>C19*(1-0.9*C21)</f>
         <v>5.1619860966202831</v>
       </c>
       <c r="D22" s="185" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E22" s="125"/>
       <c r="F22" s="125"/>
@@ -23164,7 +23164,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="183" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E23" s="125"/>
       <c r="F23" s="125"/>
@@ -23176,7 +23176,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B25" s="154" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
@@ -23189,7 +23189,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B27" s="60" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C27" s="61"/>
       <c r="D27" s="60"/>
@@ -23198,42 +23198,42 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C28" s="279">
         <f>IF(Antriebsart2="Vollelektrisch (BEV)",0,IFERROR(VLOOKUP(Energie2,EnKostList,6,FALSE),0)*IF(Antriebsart2="Plug-In-Hybrid (PHEV)",VerbPHEV2,Verbrauch2)/100*Fahrleistung)</f>
         <v>1437.92</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E28" s="125"/>
       <c r="F28" s="125"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C29" s="279">
         <f>IF(Antriebsart2="Verbrenner",0,VLOOKUP("Strom",EnKostList,6,FALSE)*IF(Antriebsart2="Plug-In-Hybrid (PHEV)",VerbElPHEV2,VerbEl_WLTP2)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E29" s="125"/>
       <c r="F29" s="125"/>
     </row>
     <row r="30" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="64" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C30" s="280">
         <f>SUM(C28:C29)</f>
         <v>1437.92</v>
       </c>
       <c r="D30" s="64" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E30" s="125"/>
       <c r="F30" s="125"/>
@@ -23246,7 +23246,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B32" s="60" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C32" s="145" t="str">
         <f>CONCATENATE("Energieträger: ",Energie2)</f>
@@ -23258,70 +23258,70 @@
     </row>
     <row r="33" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B33" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C33" s="279">
         <f>IF(Antriebsart2="Plug-In-Hybrid (PHEV)",VerbPHEV2*VLOOKUP(Energie2,CO2List,2,FALSE)/100,CO2_2)*Fahrleistung/1000000</f>
         <v>2.2799999999999998</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E33" s="125"/>
       <c r="F33" s="125"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C34" s="279">
         <f>C33*Kost_THG</f>
         <v>1960.7999999999997</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E34" s="125"/>
       <c r="F34" s="125"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B35" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C35" s="287">
         <f>IF(Energie2="Strom",0,NOX_2*Fahrleistung*Kost_NOX/1000)</f>
         <v>12.24</v>
       </c>
       <c r="D35" s="65" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E35" s="125"/>
       <c r="F35" s="125"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B36" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C36" s="287">
         <f>IF(Energie2="Strom",0,Partikel2*Fahrleistung*Kost_Partikel/1000)</f>
         <v>1.62</v>
       </c>
       <c r="D36" s="65" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E36" s="125"/>
       <c r="F36" s="125"/>
     </row>
     <row r="37" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="64" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C37" s="280">
         <f>SUM(C34:C36)</f>
         <v>1974.6599999999996</v>
       </c>
       <c r="D37" s="64" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E37" s="125"/>
       <c r="F37" s="125"/>
@@ -23334,7 +23334,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B39" s="60" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C39" s="145" t="str">
         <f>CONCATENATE("Energieträger: ",Energie2,IF(Antriebsart2="Plug-In-Hybrid (PHEV)","+Strom",""))</f>
@@ -23346,28 +23346,28 @@
     </row>
     <row r="40" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B40" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C40" s="279">
         <f>IFERROR(IF(Antriebsart2="Vollelektrisch (BEV)",VLOOKUP("Strom",CO2List,3,FALSE)*VerbEl_WLTP2/100*Fahrleistung/1000000,IF(Antriebsart2="Verbrenner",VLOOKUP(Energie2,CO2List,3,FALSE)*Verbrauch2/100*Fahrleistung/1000000,VLOOKUP(Energie2,CO2List,3,FALSE)*VerbPHEV2/100*Fahrleistung/1000000+VLOOKUP("Strom",CO2List,3,FALSE)*VerbElPHEV2/100*Fahrleistung/1000000)),0)</f>
         <v>0.71530162329600011</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E40" s="125"/>
       <c r="F40" s="125"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B41" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C41" s="279">
         <f>C40*Kost_THG</f>
         <v>615.15939603456013</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E41" s="125"/>
       <c r="F41" s="125"/>
@@ -23378,7 +23378,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B43" s="154" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
@@ -23395,55 +23395,55 @@
     <row r="45" spans="1:6" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="107"/>
       <c r="B45" s="90" t="s">
+        <v>170</v>
+      </c>
+      <c r="C45" s="134" t="s">
         <v>171</v>
-      </c>
-      <c r="C45" s="134" t="s">
-        <v>172</v>
       </c>
       <c r="D45" s="62"/>
       <c r="E45" s="125"/>
       <c r="F45" s="125"/>
     </row>
     <row r="46" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A46" s="383" t="s">
+      <c r="A46" s="370" t="s">
         <v>12</v>
       </c>
       <c r="B46" s="437" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C46" s="281">
         <f>IF(OR(Antriebsart2="Vollelektrisch (BEV)",Antriebsart2="Plug-In-Hybrid (PHEV)"),Batterie2*Batterie_THG/1000,0)</f>
         <v>0</v>
       </c>
       <c r="D46" s="131" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E46" s="127"/>
       <c r="F46" s="125"/>
     </row>
     <row r="47" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A47" s="383"/>
+      <c r="A47" s="370"/>
       <c r="B47" s="438"/>
       <c r="C47" s="281">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
         <v>0</v>
       </c>
       <c r="D47" s="130" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E47" s="127"/>
       <c r="F47" s="125"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B48" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C48" s="279">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Kost_THG, C46/Haltedauer*Kost_THG)</f>
         <v>0</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E48" s="125"/>
       <c r="F48" s="125"/>
@@ -23467,20 +23467,20 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B52" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="54" spans="1:6" s="70" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="68" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C54" s="282">
         <f>IF(FinArt="Kauf",IF(KaufpreisRech="Kaufpreis",Gesamtpreis2,0),Gesamtpreis2*Haltedauer*12+IF(FinArt="Leasing",LeasSondZahl2,0))</f>
         <v>0</v>
       </c>
       <c r="D54" s="68" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E54" s="69"/>
       <c r="F54" s="58"/>
@@ -23490,72 +23490,72 @@
         <v>12</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C55" s="283">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis2-Gesamtpreis2*(-0.2*LN(Haltedauer)+0.667),0)</f>
         <v>26020.218534092586</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E55" s="125"/>
       <c r="F55" s="73"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B56" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C56" s="283">
         <f>C30*Haltedauer</f>
         <v>10065.44</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F56" s="73"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C57" s="283">
         <f>C37*Haltedauer</f>
         <v>13822.619999999997</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F57" s="58"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C58" s="283">
         <f>C41*Haltedauer</f>
         <v>4306.1157722419211</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F58" s="58"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B59" s="329" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C59" s="330">
         <f>C48*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D59" s="329" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="383" t="s">
+      <c r="A60" s="370" t="s">
         <v>12</v>
       </c>
       <c r="B60" s="327" t="str">
@@ -23573,7 +23573,7 @@
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="383"/>
+      <c r="A61" s="370"/>
       <c r="B61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
@@ -23589,7 +23589,7 @@
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="383"/>
+      <c r="A62" s="370"/>
       <c r="B62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
@@ -23606,14 +23606,14 @@
     </row>
     <row r="63" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B63" s="64" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C63" s="284">
         <f>SUM(C54:C62)</f>
         <v>55810.394306334507</v>
       </c>
       <c r="D63" s="64" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E63" s="14"/>
       <c r="F63" s="58"/>
@@ -23628,26 +23628,26 @@
     </row>
     <row r="65" spans="2:5" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B65" s="68" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C65" s="285">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Haltedauer, C46)</f>
         <v>0</v>
       </c>
       <c r="D65" s="68" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="66" spans="2:5" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B66" s="72" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C66" s="286">
         <f>C33*Haltedauer+C40*Haltedauer</f>
         <v>20.967111363072</v>
       </c>
       <c r="D66" s="72" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E66" s="71"/>
     </row>
@@ -23698,7 +23698,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>21</v>
@@ -23711,7 +23711,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B4" s="154" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3"/>
@@ -23727,7 +23727,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C6" s="54">
         <v>3</v>
@@ -23740,7 +23740,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B7" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C7" s="102" t="str">
         <f>IF(Anbieter3=0,"",Anbieter3)</f>
@@ -23762,7 +23762,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B9" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C9" s="102"/>
       <c r="E9" s="125"/>
@@ -23770,7 +23770,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C10" s="102" t="str">
         <f>IF(Hersteller3=0,"",Hersteller3)</f>
@@ -23782,7 +23782,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C11" s="102" t="str">
         <f>IF(Modell3=0,"",Modell3)</f>
@@ -23794,7 +23794,7 @@
     </row>
     <row r="12" spans="1:6" ht="43.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="56" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C12" s="102" t="str">
         <f>IF(Zusatzinfo3=0,"",Zusatzinfo3)</f>
@@ -23806,7 +23806,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B13" s="57" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C13" s="102" t="str">
         <f>IF(Antriebsart3=0,"",Antriebsart3)</f>
@@ -23817,7 +23817,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B14" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C14" s="102" t="str">
         <f>IF(Energie3=0,"",Energie3)</f>
@@ -23833,7 +23833,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B16" s="154" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C16" s="3"/>
       <c r="D16" s="3"/>
@@ -23849,7 +23849,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B18" s="72" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C18" s="288">
         <f>0.0057*(ReichwPHEV3/23)^3-0.0838*(ReichwPHEV3/23)^2+0.4261*(ReichwPHEV3/23)+ 0.1633</f>
@@ -23861,35 +23861,35 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B19" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C19" s="289">
         <f>Verbrauch3/(1-0.9*C18)</f>
         <v>0</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E19" s="125"/>
       <c r="F19" s="125"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B20" s="72" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C20" s="290">
         <f>VerbEl_WLTP3/C18</f>
         <v>94.91733006736068</v>
       </c>
       <c r="D20" s="184" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E20" s="125"/>
       <c r="F20" s="125"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B21" s="186" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C21" s="291">
         <f>0.0021*(ReichwPHEV3/23)^3-0.0358*(ReichwPHEV3/23)^2+0.2607*(ReichwPHEV3/23)- 0.0267</f>
@@ -23904,14 +23904,14 @@
         <v>12</v>
       </c>
       <c r="B22" s="439" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C22" s="292">
         <f>C19*(1-0.9*C21)</f>
         <v>0</v>
       </c>
       <c r="D22" s="185" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E22" s="125"/>
       <c r="F22" s="125"/>
@@ -23924,7 +23924,7 @@
         <v>-2.5342927127985302</v>
       </c>
       <c r="D23" s="183" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E23" s="125"/>
       <c r="F23" s="125"/>
@@ -23936,7 +23936,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B25" s="154" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
@@ -23949,7 +23949,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B27" s="60" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C27" s="61"/>
       <c r="D27" s="60"/>
@@ -23958,42 +23958,42 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B28" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C28" s="279">
         <f>IF(Antriebsart3="Vollelektrisch (BEV)",0,IFERROR(VLOOKUP(Energie3,EnKostList,6,FALSE),0)*IF(Antriebsart3="Plug-In-Hybrid (PHEV)",VerbPHEV3,Verbrauch3)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E28" s="125"/>
       <c r="F28" s="125"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B29" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C29" s="279">
         <f>IF(Antriebsart3="Verbrenner",0,VLOOKUP("Strom",EnKostList,6,FALSE)*IF(Antriebsart3="Plug-In-Hybrid (PHEV)",VerbElPHEV3,VerbEl_WLTP3)/100*Fahrleistung)</f>
         <v>1556.1999999999998</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E29" s="125"/>
       <c r="F29" s="125"/>
     </row>
     <row r="30" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B30" s="64" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C30" s="280">
         <f>SUM(C28:C29)</f>
         <v>1556.1999999999998</v>
       </c>
       <c r="D30" s="64" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E30" s="125"/>
       <c r="F30" s="125"/>
@@ -24006,7 +24006,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B32" s="60" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C32" s="145" t="str">
         <f>CONCATENATE("Energieträger: ",Energie3)</f>
@@ -24018,70 +24018,70 @@
     </row>
     <row r="33" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B33" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C33" s="279">
         <f>IF(Antriebsart3="Plug-In-Hybrid (PHEV)",VerbPHEV3*VLOOKUP(Energie3,CO2List,2,FALSE)/100,CO2_3)*Fahrleistung/1000000</f>
         <v>0</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E33" s="125"/>
       <c r="F33" s="125"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B34" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C34" s="279">
         <f>C33*Kost_THG</f>
         <v>0</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E34" s="125"/>
       <c r="F34" s="125"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B35" s="7" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C35" s="287">
         <f>IF(Energie3="Strom",0,NOX_3*Fahrleistung*Kost_NOX/1000)</f>
         <v>0</v>
       </c>
       <c r="D35" s="65" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E35" s="125"/>
       <c r="F35" s="125"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B36" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C36" s="287">
         <f>IF(Energie3="Strom",0,Partikel3*Fahrleistung*Kost_Partikel/1000)</f>
         <v>0</v>
       </c>
       <c r="D36" s="65" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E36" s="125"/>
       <c r="F36" s="125"/>
     </row>
     <row r="37" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="64" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C37" s="280">
         <f>SUM(C34:C36)</f>
         <v>0</v>
       </c>
       <c r="D37" s="64" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E37" s="125"/>
       <c r="F37" s="125"/>
@@ -24094,7 +24094,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B39" s="60" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C39" s="145" t="str">
         <f>CONCATENATE("Energieträger: ",Energie3,IF(Antriebsart3="Plug-In-Hybrid (PHEV)","+Strom",""))</f>
@@ -24106,28 +24106,28 @@
     </row>
     <row r="40" spans="1:6" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B40" s="1" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C40" s="279">
         <f>IFERROR(IF(Antriebsart3="Vollelektrisch (BEV)",VLOOKUP("Strom",CO2List,3,FALSE)*VerbEl_WLTP3/100*Fahrleistung/1000000,IF(Antriebsart3="Verbrenner",VLOOKUP(Energie3,CO2List,3,FALSE)*Verbrauch3/100*Fahrleistung/1000000,VLOOKUP(Energie3,CO2List,3,FALSE)*VerbPHEV3/100*Fahrleistung/1000000+VLOOKUP("Strom",CO2List,3,FALSE)*VerbElPHEV3/100*Fahrleistung/1000000)),0)</f>
         <v>0.90209999999999979</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E40" s="125"/>
       <c r="F40" s="125"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B41" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C41" s="279">
         <f>C40*Kost_THG</f>
         <v>775.80599999999981</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E41" s="125"/>
       <c r="F41" s="125"/>
@@ -24138,7 +24138,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B43" s="154" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
@@ -24155,55 +24155,55 @@
     <row r="45" spans="1:6" s="67" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="107"/>
       <c r="B45" s="90" t="s">
+        <v>170</v>
+      </c>
+      <c r="C45" s="134" t="s">
         <v>171</v>
-      </c>
-      <c r="C45" s="134" t="s">
-        <v>172</v>
       </c>
       <c r="D45" s="62"/>
       <c r="E45" s="125"/>
       <c r="F45" s="125"/>
     </row>
     <row r="46" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A46" s="383" t="s">
+      <c r="A46" s="370" t="s">
         <v>12</v>
       </c>
       <c r="B46" s="437" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C46" s="281">
         <f>IF(OR(Antriebsart3="Vollelektrisch (BEV)",Antriebsart3="Plug-In-Hybrid (PHEV)"),Batterie3*Batterie_THG/1000,0)</f>
         <v>5.2080000000000002</v>
       </c>
       <c r="D46" s="131" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E46" s="127"/>
       <c r="F46" s="133"/>
     </row>
     <row r="47" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A47" s="383"/>
+      <c r="A47" s="370"/>
       <c r="B47" s="438"/>
       <c r="C47" s="281">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
         <v>23.672727272727272</v>
       </c>
       <c r="D47" s="130" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E47" s="127"/>
       <c r="F47" s="133"/>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B48" s="1" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C48" s="279">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Kost_THG, C46/Haltedauer*Kost_THG)</f>
         <v>407.17090909090905</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="E48" s="125"/>
       <c r="F48" s="125"/>
@@ -24227,20 +24227,20 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B52" s="1" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="54" spans="1:6" s="70" customFormat="1" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A54" s="1"/>
       <c r="B54" s="68" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C54" s="282">
         <f>IF(FinArt="Kauf",IF(KaufpreisRech="Kaufpreis",Gesamtpreis3,0),Gesamtpreis3*Haltedauer*12+IF(FinArt="Leasing",LeasSondZahl3,0))</f>
         <v>0</v>
       </c>
       <c r="D54" s="68" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E54" s="69"/>
       <c r="F54" s="58"/>
@@ -24250,72 +24250,72 @@
         <v>12</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="C55" s="283">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis3-Gesamtpreis3*(-0.2*LN(Haltedauer)+0.667),0)</f>
         <v>28472.026525301146</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E55" s="125"/>
       <c r="F55" s="73"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B56" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C56" s="283">
         <f>C30*Haltedauer</f>
         <v>10893.399999999998</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F56" s="73"/>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C57" s="283">
         <f>C37*Haltedauer</f>
         <v>0</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F57" s="58"/>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B58" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C58" s="283">
         <f>C41*Haltedauer</f>
         <v>5430.6419999999989</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F58" s="58"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B59" s="327" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C59" s="328">
         <f>C48*Haltedauer</f>
         <v>2850.1963636363635</v>
       </c>
       <c r="D59" s="327" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="383" t="s">
+      <c r="A60" s="370" t="s">
         <v>12</v>
       </c>
       <c r="B60" s="327" t="str">
@@ -24333,7 +24333,7 @@
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="383"/>
+      <c r="A61" s="370"/>
       <c r="B61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
@@ -24349,7 +24349,7 @@
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="383"/>
+      <c r="A62" s="370"/>
       <c r="B62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
@@ -24366,14 +24366,14 @@
     </row>
     <row r="63" spans="1:6" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B63" s="64" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C63" s="284">
         <f>SUM(C54:C62)</f>
         <v>47646.264888937505</v>
       </c>
       <c r="D63" s="64" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E63" s="14"/>
       <c r="F63" s="58"/>
@@ -24388,26 +24388,26 @@
     </row>
     <row r="65" spans="2:5" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B65" s="68" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C65" s="285">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Haltedauer, C46)</f>
         <v>3.3141818181818179</v>
       </c>
       <c r="D65" s="68" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="66" spans="2:5" ht="16.2" x14ac:dyDescent="0.35">
       <c r="B66" s="72" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C66" s="286">
         <f>C33*Haltedauer+C40*Haltedauer</f>
         <v>6.3146999999999984</v>
       </c>
       <c r="D66" s="72" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E66" s="71"/>
     </row>
@@ -24447,15 +24447,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101006A4EC2B1D245C948A7120CE5A36078F8" ma:contentTypeVersion="14" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="4b87026bc8dcc7f3f10cc45b8239b46f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5e4dc333-02c0-4d6f-a03d-d04a548a7be7" xmlns:ns3="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b7f15f5ac45b0ba6c0c6284d6c06137b" ns2:_="" ns3:_="">
     <xsd:import namespace="5e4dc333-02c0-4d6f-a03d-d04a548a7be7"/>
@@ -24684,17 +24675,26 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{651615EB-DE44-4BF4-BD1E-846AB7A3DA36}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="5e4dc333-02c0-4d6f-a03d-d04a548a7be7"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="5e4dc333-02c0-4d6f-a03d-d04a548a7be7"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
@@ -24702,14 +24702,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92A2CDCF-36F6-4C30-8F9B-D45880CB8E7E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C82CFA85-B81D-4C7D-99B5-F82C00D97DE4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -24726,4 +24718,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92A2CDCF-36F6-4C30-8F9B-D45880CB8E7E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/src/assets/downloads/LZK-Rechner_Pkw_V1.3_Beispiel.xlsx
+++ b/src/assets/downloads/LZK-Rechner_Pkw_V1.3_Beispiel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ifeu2.sharepoint.com/sites/DBUBeschaffungBerlin/Freigegebene Dokumente/General/Folgeprojekt/03_Arbeitsdokumente/A4 - Aktualisierung der Instrumente aus Basisprojekt/LZK-Rechner/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{F8E3439C-4500-4DCC-A4D0-17CF3516801A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{5282CB64-9BD1-4F78-BEE1-30AEB72C1434}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{F8E3439C-4500-4DCC-A4D0-17CF3516801A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{43ECE931-5FF1-4BEE-94AA-76E0326F3B61}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="887" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2702,49 +2702,6 @@
     <t>Gesellschaftliche Kosten von Umweltbelastungen - Klimakosten von Treibhausgas-Emissionen (02.07.2024)</t>
   </si>
   <si>
-    <r>
-      <t>Der Excel-Rechner ist</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> ohne Passwort</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> geschützt. Der Blattschutz kann unter "Überprüfen -&gt; Blattschutz aufheben" aufgehoben werden.
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Das Tool kann grundsätzlich nach eigenen Bedürfnissen über die vorgesehenen Anpassungsmöglichkeiten hinaus angepasst werden. 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>Es ist jedoch zu berücksichtigen, dass dadurch Berechnungsfehler entstehen können.</t>
-    </r>
-  </si>
-  <si>
     <t>Angaben zu den Energiekosten</t>
   </si>
   <si>
@@ -3364,6 +3321,49 @@
   </si>
   <si>
     <t>Ladeverhalten Elektrofahrzeug</t>
+  </si>
+  <si>
+    <r>
+      <t>Der Excel-Rechner ist</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> ohne Passwort</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> geschützt. Der Blattschutz kann unter "Überprüfen -&gt; Blattschutz aufheben" aufgehoben werden.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Das Tool kann grundsätzlich nach eigenen Bedürfnissen über die vorgesehenen Anpassungsmöglichkeiten hinaus angepasst werden. 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Es ist jedoch zu berücksichtigen, dass dadurch Berechnungsfehler entstehen können. Die Verantwortung liegt bei der Person, die den Rechner angepasst hat.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -5566,49 +5566,49 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" xfId="4" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" xfId="4" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" xfId="4" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="20" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" xfId="4" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" xfId="4" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" xfId="4" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="46" fillId="20" borderId="0" xfId="4" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
@@ -14042,7 +14042,7 @@
       <c r="H2" s="16"/>
       <c r="I2" s="16"/>
       <c r="J2" s="268" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.25">
@@ -14064,17 +14064,17 @@
       <c r="J4" s="115"/>
     </row>
     <row r="5" spans="2:10" ht="149.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="373" t="s">
-        <v>489</v>
-      </c>
-      <c r="C5" s="373"/>
-      <c r="D5" s="373"/>
-      <c r="E5" s="373"/>
-      <c r="F5" s="373"/>
-      <c r="G5" s="373"/>
-      <c r="H5" s="373"/>
-      <c r="I5" s="373"/>
-      <c r="J5" s="373"/>
+      <c r="B5" s="370" t="s">
+        <v>488</v>
+      </c>
+      <c r="C5" s="370"/>
+      <c r="D5" s="370"/>
+      <c r="E5" s="370"/>
+      <c r="F5" s="370"/>
+      <c r="G5" s="370"/>
+      <c r="H5" s="370"/>
+      <c r="I5" s="370"/>
+      <c r="J5" s="370"/>
     </row>
     <row r="6" spans="2:10" ht="11.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="245"/>
@@ -14112,13 +14112,13 @@
     <row r="9" spans="2:10" ht="52.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D9" s="245"/>
       <c r="E9" s="245"/>
-      <c r="F9" s="374" t="s">
-        <v>441</v>
-      </c>
-      <c r="G9" s="374"/>
-      <c r="H9" s="374"/>
-      <c r="I9" s="374"/>
-      <c r="J9" s="374"/>
+      <c r="F9" s="371" t="s">
+        <v>440</v>
+      </c>
+      <c r="G9" s="371"/>
+      <c r="H9" s="371"/>
+      <c r="I9" s="371"/>
+      <c r="J9" s="371"/>
     </row>
     <row r="10" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D10" s="245"/>
@@ -14132,31 +14132,31 @@
     <row r="11" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D11" s="245"/>
       <c r="E11" s="245"/>
-      <c r="F11" s="375" t="s">
-        <v>462</v>
-      </c>
-      <c r="G11" s="376"/>
-      <c r="H11" s="376"/>
-      <c r="I11" s="376"/>
-      <c r="J11" s="376"/>
+      <c r="F11" s="372" t="s">
+        <v>461</v>
+      </c>
+      <c r="G11" s="373"/>
+      <c r="H11" s="373"/>
+      <c r="I11" s="373"/>
+      <c r="J11" s="373"/>
     </row>
     <row r="12" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D12" s="245"/>
       <c r="E12" s="245"/>
-      <c r="F12" s="376"/>
-      <c r="G12" s="376"/>
-      <c r="H12" s="376"/>
-      <c r="I12" s="376"/>
-      <c r="J12" s="376"/>
+      <c r="F12" s="373"/>
+      <c r="G12" s="373"/>
+      <c r="H12" s="373"/>
+      <c r="I12" s="373"/>
+      <c r="J12" s="373"/>
     </row>
     <row r="13" spans="2:10" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D13" s="245"/>
       <c r="E13" s="245"/>
-      <c r="F13" s="376"/>
-      <c r="G13" s="376"/>
-      <c r="H13" s="376"/>
-      <c r="I13" s="376"/>
-      <c r="J13" s="376"/>
+      <c r="F13" s="373"/>
+      <c r="G13" s="373"/>
+      <c r="H13" s="373"/>
+      <c r="I13" s="373"/>
+      <c r="J13" s="373"/>
     </row>
     <row r="14" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D14" s="245"/>
@@ -14170,22 +14170,22 @@
     <row r="15" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D15" s="245"/>
       <c r="E15" s="245"/>
-      <c r="F15" s="377" t="s">
+      <c r="F15" s="374" t="s">
         <v>2</v>
       </c>
-      <c r="G15" s="378"/>
-      <c r="H15" s="378"/>
-      <c r="I15" s="378"/>
-      <c r="J15" s="378"/>
+      <c r="G15" s="375"/>
+      <c r="H15" s="375"/>
+      <c r="I15" s="375"/>
+      <c r="J15" s="375"/>
     </row>
     <row r="16" spans="2:10" ht="73.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D16" s="245"/>
       <c r="E16" s="245"/>
-      <c r="F16" s="378"/>
-      <c r="G16" s="378"/>
-      <c r="H16" s="378"/>
-      <c r="I16" s="378"/>
-      <c r="J16" s="378"/>
+      <c r="F16" s="375"/>
+      <c r="G16" s="375"/>
+      <c r="H16" s="375"/>
+      <c r="I16" s="375"/>
+      <c r="J16" s="375"/>
     </row>
     <row r="17" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D17" s="245"/>
@@ -14199,13 +14199,13 @@
     <row r="18" spans="2:10" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D18" s="245"/>
       <c r="E18" s="245"/>
-      <c r="F18" s="379" t="s">
+      <c r="F18" s="376" t="s">
         <v>3</v>
       </c>
-      <c r="G18" s="380"/>
-      <c r="H18" s="380"/>
-      <c r="I18" s="380"/>
-      <c r="J18" s="380"/>
+      <c r="G18" s="377"/>
+      <c r="H18" s="377"/>
+      <c r="I18" s="377"/>
+      <c r="J18" s="377"/>
     </row>
     <row r="19" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D19" s="245"/>
@@ -14219,31 +14219,31 @@
     <row r="20" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D20" s="245"/>
       <c r="E20" s="245"/>
-      <c r="F20" s="381" t="s">
+      <c r="F20" s="378" t="s">
         <v>4</v>
       </c>
-      <c r="G20" s="381"/>
-      <c r="H20" s="381"/>
-      <c r="I20" s="381"/>
-      <c r="J20" s="381"/>
+      <c r="G20" s="378"/>
+      <c r="H20" s="378"/>
+      <c r="I20" s="378"/>
+      <c r="J20" s="378"/>
     </row>
     <row r="21" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D21" s="245"/>
       <c r="E21" s="245"/>
-      <c r="F21" s="381"/>
-      <c r="G21" s="381"/>
-      <c r="H21" s="381"/>
-      <c r="I21" s="381"/>
-      <c r="J21" s="381"/>
+      <c r="F21" s="378"/>
+      <c r="G21" s="378"/>
+      <c r="H21" s="378"/>
+      <c r="I21" s="378"/>
+      <c r="J21" s="378"/>
     </row>
     <row r="22" spans="2:10" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D22" s="245"/>
       <c r="E22" s="245"/>
-      <c r="F22" s="381"/>
-      <c r="G22" s="381"/>
-      <c r="H22" s="381"/>
-      <c r="I22" s="381"/>
-      <c r="J22" s="381"/>
+      <c r="F22" s="378"/>
+      <c r="G22" s="378"/>
+      <c r="H22" s="378"/>
+      <c r="I22" s="378"/>
+      <c r="J22" s="378"/>
     </row>
     <row r="23" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D23" s="245"/>
@@ -14257,22 +14257,22 @@
     <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="D24" s="245"/>
       <c r="E24" s="245"/>
-      <c r="F24" s="382" t="s">
+      <c r="F24" s="379" t="s">
         <v>5</v>
       </c>
-      <c r="G24" s="382"/>
-      <c r="H24" s="382"/>
-      <c r="I24" s="382"/>
-      <c r="J24" s="382"/>
+      <c r="G24" s="379"/>
+      <c r="H24" s="379"/>
+      <c r="I24" s="379"/>
+      <c r="J24" s="379"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="D25" s="245"/>
       <c r="E25" s="245"/>
-      <c r="F25" s="382"/>
-      <c r="G25" s="382"/>
-      <c r="H25" s="382"/>
-      <c r="I25" s="382"/>
-      <c r="J25" s="382"/>
+      <c r="F25" s="379"/>
+      <c r="G25" s="379"/>
+      <c r="H25" s="379"/>
+      <c r="I25" s="379"/>
+      <c r="J25" s="379"/>
     </row>
     <row r="26" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D26" s="245"/>
@@ -14286,49 +14286,49 @@
     <row r="27" spans="2:10" ht="7.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D27" s="245"/>
       <c r="E27" s="245"/>
-      <c r="F27" s="372"/>
-      <c r="G27" s="372"/>
-      <c r="H27" s="372"/>
-      <c r="I27" s="372"/>
-      <c r="J27" s="372"/>
+      <c r="F27" s="369"/>
+      <c r="G27" s="369"/>
+      <c r="H27" s="369"/>
+      <c r="I27" s="369"/>
+      <c r="J27" s="369"/>
     </row>
     <row r="28" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D28" s="245"/>
       <c r="E28" s="245"/>
-      <c r="F28" s="383" t="s">
-        <v>463</v>
-      </c>
-      <c r="G28" s="383"/>
-      <c r="H28" s="383"/>
-      <c r="I28" s="383"/>
-      <c r="J28" s="383"/>
+      <c r="F28" s="380" t="s">
+        <v>462</v>
+      </c>
+      <c r="G28" s="380"/>
+      <c r="H28" s="380"/>
+      <c r="I28" s="380"/>
+      <c r="J28" s="380"/>
     </row>
     <row r="29" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D29" s="245"/>
       <c r="E29" s="245"/>
-      <c r="F29" s="383"/>
-      <c r="G29" s="383"/>
-      <c r="H29" s="383"/>
-      <c r="I29" s="383"/>
-      <c r="J29" s="383"/>
+      <c r="F29" s="380"/>
+      <c r="G29" s="380"/>
+      <c r="H29" s="380"/>
+      <c r="I29" s="380"/>
+      <c r="J29" s="380"/>
     </row>
     <row r="30" spans="2:10" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D30" s="245"/>
       <c r="E30" s="245"/>
-      <c r="F30" s="383"/>
-      <c r="G30" s="383"/>
-      <c r="H30" s="383"/>
-      <c r="I30" s="383"/>
-      <c r="J30" s="383"/>
+      <c r="F30" s="380"/>
+      <c r="G30" s="380"/>
+      <c r="H30" s="380"/>
+      <c r="I30" s="380"/>
+      <c r="J30" s="380"/>
     </row>
     <row r="31" spans="2:10" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D31" s="245"/>
       <c r="E31" s="245"/>
-      <c r="F31" s="371"/>
-      <c r="G31" s="371"/>
-      <c r="H31" s="371"/>
-      <c r="I31" s="371"/>
-      <c r="J31" s="371"/>
+      <c r="F31" s="381"/>
+      <c r="G31" s="381"/>
+      <c r="H31" s="381"/>
+      <c r="I31" s="381"/>
+      <c r="J31" s="381"/>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="250" t="s">
@@ -14377,15 +14377,15 @@
     <row r="36" spans="2:11" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="116"/>
       <c r="C36" s="113"/>
-      <c r="D36" s="371" t="s">
+      <c r="D36" s="381" t="s">
         <v>8</v>
       </c>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
-      <c r="G36" s="371"/>
-      <c r="H36" s="371"/>
-      <c r="I36" s="371"/>
-      <c r="J36" s="371"/>
+      <c r="E36" s="381"/>
+      <c r="F36" s="381"/>
+      <c r="G36" s="381"/>
+      <c r="H36" s="381"/>
+      <c r="I36" s="381"/>
+      <c r="J36" s="381"/>
     </row>
     <row r="37" spans="2:11" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="117"/>
@@ -14401,24 +14401,24 @@
     <row r="38" spans="2:11" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B38" s="241"/>
       <c r="C38" s="113"/>
-      <c r="D38" s="372" t="s">
+      <c r="D38" s="369" t="s">
         <v>9</v>
       </c>
-      <c r="E38" s="372"/>
-      <c r="F38" s="372"/>
-      <c r="G38" s="372"/>
-      <c r="H38" s="372"/>
-      <c r="I38" s="372"/>
-      <c r="J38" s="372"/>
+      <c r="E38" s="369"/>
+      <c r="F38" s="369"/>
+      <c r="G38" s="369"/>
+      <c r="H38" s="369"/>
+      <c r="I38" s="369"/>
+      <c r="J38" s="369"/>
     </row>
     <row r="39" spans="2:11" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D39" s="372"/>
-      <c r="E39" s="372"/>
-      <c r="F39" s="372"/>
-      <c r="G39" s="372"/>
-      <c r="H39" s="372"/>
-      <c r="I39" s="372"/>
-      <c r="J39" s="372"/>
+      <c r="D39" s="369"/>
+      <c r="E39" s="369"/>
+      <c r="F39" s="369"/>
+      <c r="G39" s="369"/>
+      <c r="H39" s="369"/>
+      <c r="I39" s="369"/>
+      <c r="J39" s="369"/>
     </row>
     <row r="40" spans="2:11" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="117"/>
@@ -14436,15 +14436,15 @@
         <v>10</v>
       </c>
       <c r="C41" s="113"/>
-      <c r="D41" s="369" t="s">
+      <c r="D41" s="382" t="s">
         <v>11</v>
       </c>
-      <c r="E41" s="369"/>
-      <c r="F41" s="369"/>
-      <c r="G41" s="369"/>
-      <c r="H41" s="369"/>
-      <c r="I41" s="369"/>
-      <c r="J41" s="369"/>
+      <c r="E41" s="382"/>
+      <c r="F41" s="382"/>
+      <c r="G41" s="382"/>
+      <c r="H41" s="382"/>
+      <c r="I41" s="382"/>
+      <c r="J41" s="382"/>
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" s="113"/>
@@ -14458,30 +14458,30 @@
       <c r="J42" s="245"/>
     </row>
     <row r="43" spans="2:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="370" t="s">
+      <c r="B43" s="383" t="s">
         <v>12</v>
       </c>
       <c r="C43" s="103"/>
-      <c r="D43" s="371" t="s">
+      <c r="D43" s="381" t="s">
         <v>13</v>
       </c>
-      <c r="E43" s="371"/>
-      <c r="F43" s="371"/>
-      <c r="G43" s="371"/>
-      <c r="H43" s="371"/>
-      <c r="I43" s="371"/>
-      <c r="J43" s="371"/>
+      <c r="E43" s="381"/>
+      <c r="F43" s="381"/>
+      <c r="G43" s="381"/>
+      <c r="H43" s="381"/>
+      <c r="I43" s="381"/>
+      <c r="J43" s="381"/>
     </row>
     <row r="44" spans="2:11" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="B44" s="370"/>
+      <c r="B44" s="383"/>
       <c r="C44" s="103"/>
-      <c r="D44" s="371"/>
-      <c r="E44" s="371"/>
-      <c r="F44" s="371"/>
-      <c r="G44" s="371"/>
-      <c r="H44" s="371"/>
-      <c r="I44" s="371"/>
-      <c r="J44" s="371"/>
+      <c r="D44" s="381"/>
+      <c r="E44" s="381"/>
+      <c r="F44" s="381"/>
+      <c r="G44" s="381"/>
+      <c r="H44" s="381"/>
+      <c r="I44" s="381"/>
+      <c r="J44" s="381"/>
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.25">
       <c r="D45" s="112"/>
@@ -14492,18 +14492,18 @@
       <c r="I45" s="114"/>
       <c r="J45" s="114"/>
     </row>
-    <row r="46" spans="2:11" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="371" t="s">
-        <v>432</v>
-      </c>
-      <c r="C46" s="371"/>
-      <c r="D46" s="371"/>
-      <c r="E46" s="371"/>
-      <c r="F46" s="371"/>
-      <c r="G46" s="371"/>
-      <c r="H46" s="371"/>
-      <c r="I46" s="371"/>
-      <c r="J46" s="371"/>
+    <row r="46" spans="2:11" ht="58.2" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="381" t="s">
+        <v>584</v>
+      </c>
+      <c r="C46" s="381"/>
+      <c r="D46" s="381"/>
+      <c r="E46" s="381"/>
+      <c r="F46" s="381"/>
+      <c r="G46" s="381"/>
+      <c r="H46" s="381"/>
+      <c r="I46" s="381"/>
+      <c r="J46" s="381"/>
       <c r="K46" s="107"/>
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.25">
@@ -14538,17 +14538,17 @@
       <c r="J49" s="112"/>
     </row>
     <row r="50" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="371" t="s">
+      <c r="B50" s="381" t="s">
         <v>15</v>
       </c>
-      <c r="C50" s="371"/>
-      <c r="D50" s="371"/>
-      <c r="E50" s="371"/>
-      <c r="F50" s="371"/>
-      <c r="G50" s="371"/>
-      <c r="H50" s="371"/>
-      <c r="I50" s="371"/>
-      <c r="J50" s="371"/>
+      <c r="C50" s="381"/>
+      <c r="D50" s="381"/>
+      <c r="E50" s="381"/>
+      <c r="F50" s="381"/>
+      <c r="G50" s="381"/>
+      <c r="H50" s="381"/>
+      <c r="I50" s="381"/>
+      <c r="J50" s="381"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D51" s="114"/>
@@ -14611,6 +14611,11 @@
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="17">
+    <mergeCell ref="D41:J41"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="D43:J44"/>
+    <mergeCell ref="B46:J46"/>
+    <mergeCell ref="B50:J50"/>
     <mergeCell ref="D38:J39"/>
     <mergeCell ref="B5:J5"/>
     <mergeCell ref="F9:J9"/>
@@ -14623,11 +14628,6 @@
     <mergeCell ref="F28:J30"/>
     <mergeCell ref="F31:J31"/>
     <mergeCell ref="D36:J36"/>
-    <mergeCell ref="D41:J41"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="D43:J44"/>
-    <mergeCell ref="B46:J46"/>
-    <mergeCell ref="B50:J50"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F9:J9" location="Input_Beschaffung!A1" display="Geben Sie die übergeordneten Informationen zu Ihrem Beschaffungsfall ein. Hier können Informationen wie die erwartete jährliche Fahrleistung, die Art der Beschaffung (Kauf/Leasing) und weitere Informationen eingegeben werden." xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -14669,7 +14669,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>21</v>
@@ -15136,7 +15136,7 @@
       <c r="F45" s="125"/>
     </row>
     <row r="46" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A46" s="370" t="s">
+      <c r="A46" s="383" t="s">
         <v>12</v>
       </c>
       <c r="B46" s="437" t="s">
@@ -15153,7 +15153,7 @@
       <c r="F46" s="125"/>
     </row>
     <row r="47" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A47" s="370"/>
+      <c r="A47" s="383"/>
       <c r="B47" s="438"/>
       <c r="C47" s="281">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
@@ -15221,7 +15221,7 @@
         <v>12</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C55" s="283">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis4-Gesamtpreis4*(-0.2*LN(Haltedauer)+0.667),0)</f>
@@ -15286,7 +15286,7 @@
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="370" t="s">
+      <c r="A60" s="383" t="s">
         <v>12</v>
       </c>
       <c r="B60" s="327" t="str">
@@ -15304,7 +15304,7 @@
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="370"/>
+      <c r="A61" s="383"/>
       <c r="B61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
@@ -15320,7 +15320,7 @@
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="370"/>
+      <c r="A62" s="383"/>
       <c r="B62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
@@ -15429,7 +15429,7 @@
     </row>
     <row r="2" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>21</v>
@@ -15900,7 +15900,7 @@
       <c r="F45" s="125"/>
     </row>
     <row r="46" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A46" s="370" t="s">
+      <c r="A46" s="383" t="s">
         <v>12</v>
       </c>
       <c r="B46" s="437" t="s">
@@ -15917,7 +15917,7 @@
       <c r="F46" s="125"/>
     </row>
     <row r="47" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A47" s="370"/>
+      <c r="A47" s="383"/>
       <c r="B47" s="438"/>
       <c r="C47" s="281">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
@@ -15985,7 +15985,7 @@
         <v>12</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C55" s="283">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis5-Gesamtpreis5*(-0.2*LN(Haltedauer)+0.667),0)</f>
@@ -16050,7 +16050,7 @@
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="370" t="s">
+      <c r="A60" s="383" t="s">
         <v>12</v>
       </c>
       <c r="B60" s="327" t="str">
@@ -16068,7 +16068,7 @@
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="370"/>
+      <c r="A61" s="383"/>
       <c r="B61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
@@ -16084,7 +16084,7 @@
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="370"/>
+      <c r="A62" s="383"/>
       <c r="B62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
@@ -16196,7 +16196,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B4" s="154" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
@@ -16258,7 +16258,7 @@
     </row>
     <row r="10" spans="1:9" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="92" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C10" s="10"/>
       <c r="D10" s="10"/>
@@ -16360,14 +16360,14 @@
     </row>
     <row r="18" spans="1:37" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="92" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D18" s="106"/>
       <c r="E18" s="10"/>
     </row>
     <row r="20" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B20" s="154" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
@@ -16383,13 +16383,13 @@
         <v>131</v>
       </c>
       <c r="J21" s="135" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="K21" s="135"/>
       <c r="L21" s="135"/>
       <c r="M21" s="135"/>
       <c r="O21" s="137" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="P21" s="137"/>
       <c r="Q21" s="137"/>
@@ -16531,7 +16531,7 @@
         <v>192</v>
       </c>
       <c r="I24" s="58" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="J24" s="300">
         <v>445</v>
@@ -16710,12 +16710,12 @@
     </row>
     <row r="39" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="234" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="40" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="234" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="41" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16731,12 +16731,12 @@
     </row>
     <row r="44" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="2" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="45" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="267" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="I45" s="106"/>
     </row>
@@ -16751,10 +16751,10 @@
     </row>
     <row r="50" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B50" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="51" spans="2:4" x14ac:dyDescent="0.25">
@@ -16762,7 +16762,7 @@
         <v>213</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="52" spans="2:4" x14ac:dyDescent="0.25">
@@ -16770,7 +16770,7 @@
         <v>214</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="53" spans="2:4" x14ac:dyDescent="0.25">
@@ -16778,7 +16778,7 @@
         <v>215</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.25">
@@ -16786,7 +16786,7 @@
         <v>33</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="55" spans="2:4" x14ac:dyDescent="0.25">
@@ -16794,7 +16794,7 @@
         <v>216</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="56" spans="2:4" x14ac:dyDescent="0.25">
@@ -16802,15 +16802,15 @@
         <v>217</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="57" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="58" spans="2:4" x14ac:dyDescent="0.25">
@@ -16818,7 +16818,7 @@
         <v>218</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.25">
@@ -16826,7 +16826,7 @@
         <v>219</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="60" spans="2:4" x14ac:dyDescent="0.25">
@@ -16834,7 +16834,7 @@
         <v>220</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="61" spans="2:4" x14ac:dyDescent="0.25">
@@ -17399,146 +17399,146 @@
     </row>
     <row r="131" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B131" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="D131" s="1" t="s">
         <v>530</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="132" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B132" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="D132" s="1" t="s">
         <v>532</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>533</v>
       </c>
     </row>
     <row r="133" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B133" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="D133" s="1" t="s">
         <v>534</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>535</v>
       </c>
     </row>
     <row r="134" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B134" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="D134" s="1" t="s">
         <v>536</v>
-      </c>
-      <c r="D134" s="1" t="s">
-        <v>537</v>
       </c>
     </row>
     <row r="135" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B135" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="D135" s="1" t="s">
         <v>538</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>539</v>
       </c>
     </row>
     <row r="136" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B136" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="D136" s="1" t="s">
         <v>540</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="137" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B137" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="D137" s="1" t="s">
         <v>542</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="138" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B138" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="D138" s="1" t="s">
         <v>544</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>545</v>
       </c>
     </row>
     <row r="139" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B139" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="D139" s="1" t="s">
         <v>546</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>547</v>
       </c>
     </row>
     <row r="140" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B140" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="D140" s="1" t="s">
         <v>548</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>549</v>
       </c>
     </row>
     <row r="141" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B141" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="D141" s="1" t="s">
         <v>550</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>551</v>
       </c>
     </row>
     <row r="142" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B142" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="D142" s="1" t="s">
         <v>552</v>
-      </c>
-      <c r="D142" s="1" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="143" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B143" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="D143" s="1" t="s">
         <v>554</v>
-      </c>
-      <c r="D143" s="1" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="144" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B144" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="D144" s="1" t="s">
         <v>556</v>
-      </c>
-      <c r="D144" s="1" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="145" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B145" s="1" t="s">
+        <v>557</v>
+      </c>
+      <c r="D145" s="1" t="s">
         <v>558</v>
-      </c>
-      <c r="D145" s="1" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="146" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B146" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="D146" s="1" t="s">
         <v>560</v>
-      </c>
-      <c r="D146" s="1" t="s">
-        <v>561</v>
       </c>
     </row>
     <row r="147" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B147" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="D147" s="1" t="s">
         <v>562</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="148" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B148" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="D148" s="1" t="s">
         <v>564</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>565</v>
       </c>
     </row>
     <row r="149" spans="2:4" x14ac:dyDescent="0.25">
@@ -17586,7 +17586,7 @@
         <v>401</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="155" spans="2:4" x14ac:dyDescent="0.25">
@@ -17594,7 +17594,7 @@
         <v>371</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="156" spans="2:4" x14ac:dyDescent="0.25">
@@ -17602,7 +17602,7 @@
         <v>372</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="157" spans="2:4" x14ac:dyDescent="0.25">
@@ -17618,31 +17618,31 @@
         <v>375</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="159" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B159" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="D159" s="1" t="s">
         <v>569</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="160" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B160" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="D160" s="1" t="s">
         <v>571</v>
-      </c>
-      <c r="D160" s="1" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="161" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B161" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="D161" s="1" t="s">
         <v>573</v>
-      </c>
-      <c r="D161" s="1" t="s">
-        <v>574</v>
       </c>
     </row>
     <row r="162" spans="2:4" x14ac:dyDescent="0.25">
@@ -17706,7 +17706,7 @@
         <v>390</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="170" spans="2:4" x14ac:dyDescent="0.25">
@@ -17714,7 +17714,7 @@
         <v>201</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="171" spans="2:4" x14ac:dyDescent="0.25">
@@ -17722,7 +17722,7 @@
         <v>202</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="172" spans="2:4" x14ac:dyDescent="0.25">
@@ -17730,7 +17730,7 @@
         <v>203</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="173" spans="2:4" x14ac:dyDescent="0.25">
@@ -17738,7 +17738,7 @@
         <v>205</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="174" spans="2:4" x14ac:dyDescent="0.25">
@@ -17746,7 +17746,7 @@
         <v>206</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="175" spans="2:4" x14ac:dyDescent="0.25">
@@ -17754,7 +17754,7 @@
         <v>391</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="176" spans="2:4" x14ac:dyDescent="0.25">
@@ -17762,7 +17762,7 @@
         <v>392</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="177" spans="2:4" x14ac:dyDescent="0.25">
@@ -17770,7 +17770,7 @@
         <v>393</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="178" spans="2:4" x14ac:dyDescent="0.25">
@@ -17778,7 +17778,7 @@
         <v>394</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="179" spans="2:4" x14ac:dyDescent="0.25">
@@ -17786,7 +17786,7 @@
         <v>395</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="180" spans="2:4" x14ac:dyDescent="0.25">
@@ -17794,7 +17794,7 @@
         <v>396</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="181" spans="2:4" x14ac:dyDescent="0.25">
@@ -17802,7 +17802,7 @@
         <v>397</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="182" spans="2:4" x14ac:dyDescent="0.25">
@@ -17810,7 +17810,7 @@
         <v>398</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="183" spans="2:4" x14ac:dyDescent="0.25">
@@ -17818,7 +17818,7 @@
         <v>399</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="184" spans="2:4" x14ac:dyDescent="0.25">
@@ -17826,7 +17826,7 @@
         <v>400</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
     </row>
     <row r="185" spans="2:4" x14ac:dyDescent="0.25">
@@ -17834,7 +17834,7 @@
         <v>402</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="186" spans="2:4" x14ac:dyDescent="0.25">
@@ -17842,7 +17842,7 @@
         <v>403</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="187" spans="2:4" x14ac:dyDescent="0.25">
@@ -17850,7 +17850,7 @@
         <v>404</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="188" spans="2:4" x14ac:dyDescent="0.25">
@@ -17858,7 +17858,7 @@
         <v>405</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="189" spans="2:4" x14ac:dyDescent="0.25">
@@ -17874,7 +17874,7 @@
         <v>408</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="191" spans="2:4" x14ac:dyDescent="0.25">
@@ -18022,7 +18022,7 @@
         <v>202</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.25">
@@ -18154,7 +18154,7 @@
     </row>
     <row r="4" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B4" s="275" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C4" s="275" t="s">
         <v>414</v>
@@ -18167,23 +18167,23 @@
     </row>
     <row r="6" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B6" s="275" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C6" s="275" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="7" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C7" s="276" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="8" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B8" s="275" t="s">
+        <v>479</v>
+      </c>
+      <c r="C8" s="270" t="s">
         <v>480</v>
-      </c>
-      <c r="C8" s="270" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="9" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
@@ -18220,15 +18220,15 @@
     </row>
     <row r="14" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B14" s="275" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C14" s="275" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="15" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C15" s="276" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="16" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
@@ -18246,15 +18246,15 @@
     </row>
     <row r="18" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B18" s="275" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C18" s="275" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="19" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C19" s="276" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="20" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
@@ -18272,20 +18272,20 @@
     </row>
     <row r="22" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B22" s="275" t="s">
+        <v>453</v>
+      </c>
+      <c r="C22" s="275" t="s">
         <v>454</v>
-      </c>
-      <c r="C22" s="275" t="s">
-        <v>455</v>
       </c>
     </row>
     <row r="23" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C23" s="276" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="24" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B24" s="275" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="C24" s="275" t="s">
         <v>431</v>
@@ -18298,15 +18298,15 @@
     </row>
     <row r="26" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B26" s="275" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C26" s="275" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="27" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
       <c r="C27" s="269" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="28" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -18355,7 +18355,7 @@
   <sheetData>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="I2" s="106" t="s">
         <v>21</v>
@@ -18374,10 +18374,10 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C6" s="388" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="D6" s="389"/>
       <c r="E6" s="389"/>
@@ -18474,7 +18474,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C15" s="152">
         <v>20000</v>
@@ -18518,7 +18518,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B19" s="298" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C19" s="151">
         <v>2024</v>
@@ -18585,7 +18585,7 @@
         <v>38</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="F26" s="274">
         <f>Grunddaten!E38</f>
@@ -18597,7 +18597,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B28" s="154" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
@@ -18790,7 +18790,7 @@
     </row>
     <row r="2" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C2" s="2" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="D2" s="2"/>
       <c r="J2" s="7"/>
@@ -18973,7 +18973,7 @@
         <v>62</v>
       </c>
       <c r="H10" s="140" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="I10" s="140" t="s">
         <v>64</v>
@@ -18981,7 +18981,7 @@
       <c r="J10" s="238"/>
       <c r="K10" s="236"/>
       <c r="L10" s="411" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="M10" s="411"/>
       <c r="N10" s="236"/>
@@ -19005,7 +19005,7 @@
         <v>66</v>
       </c>
       <c r="H11" s="141" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="I11" s="141" t="s">
         <v>69</v>
@@ -19028,16 +19028,16 @@
       </c>
       <c r="D12" s="88"/>
       <c r="E12" s="141" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F12" s="141" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="G12" s="141" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H12" s="141" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="I12" s="141" t="s">
         <v>72</v>
@@ -19347,7 +19347,7 @@
     </row>
     <row r="23" spans="2:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C23" s="77" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D23" s="228"/>
       <c r="E23" s="368"/>
@@ -19362,11 +19362,11 @@
       <c r="R23" s="7"/>
     </row>
     <row r="24" spans="2:18" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="370" t="s">
+      <c r="B24" s="383" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="331" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D24" s="322" t="s">
         <v>162</v>
@@ -19393,7 +19393,7 @@
       <c r="R24" s="7"/>
     </row>
     <row r="25" spans="2:18" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="370"/>
+      <c r="B25" s="383"/>
       <c r="C25" s="331"/>
       <c r="D25" s="322" t="s">
         <v>162</v>
@@ -19410,7 +19410,7 @@
       <c r="R25" s="7"/>
     </row>
     <row r="26" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B26" s="370"/>
+      <c r="B26" s="383"/>
       <c r="C26" s="335"/>
       <c r="D26" s="322" t="s">
         <v>162</v>
@@ -19486,7 +19486,7 @@
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C32" s="1" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
   </sheetData>
@@ -19870,7 +19870,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B1" s="118" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C1" s="118"/>
       <c r="D1" s="118"/>
@@ -19884,7 +19884,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="65" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C2" s="227"/>
       <c r="D2" s="230" t="str">
@@ -19927,7 +19927,7 @@
     <row r="6" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="18"/>
       <c r="B6" s="12" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C6" s="418" t="str">
         <f>IF(Projektname=0,"",Projektname)</f>
@@ -20009,7 +20009,7 @@
       <c r="B12" s="12"/>
       <c r="C12" s="76"/>
       <c r="E12" s="58" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F12" s="85">
         <f>Fahrleistung</f>
@@ -20504,7 +20504,7 @@
     <row r="31" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="309"/>
       <c r="B31" s="98" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C31" s="317" t="s">
         <v>105</v>
@@ -20534,10 +20534,10 @@
     <row r="32" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="309"/>
       <c r="B32" s="310" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C32" s="311" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D32" s="312">
         <f>SUM(D30:D31)</f>
@@ -20694,7 +20694,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B1" s="118" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="C1" s="118"/>
       <c r="D1" s="118"/>
@@ -20708,7 +20708,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="65" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="C2" s="227"/>
       <c r="D2" s="230" t="str">
@@ -20751,7 +20751,7 @@
     <row r="6" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="18"/>
       <c r="B6" s="12" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C6" s="418" t="str">
         <f>IF(Projektname=0,"",Projektname)</f>
@@ -20833,7 +20833,7 @@
       <c r="B12" s="12"/>
       <c r="C12" s="76"/>
       <c r="E12" s="58" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="F12" s="85">
         <f>Fahrleistung</f>
@@ -20873,7 +20873,7 @@
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="18"/>
       <c r="B15" s="293" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C15" s="21"/>
       <c r="D15" s="21"/>
@@ -21170,7 +21170,7 @@
     <row r="26" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="33"/>
       <c r="B26" s="98" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C26" s="99" t="s">
         <v>105</v>
@@ -21200,10 +21200,10 @@
     <row r="27" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="33"/>
       <c r="B27" s="310" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C27" s="311" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D27" s="312">
         <f>SUM(D25:D26)</f>
@@ -21229,7 +21229,7 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B29" s="293" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C29" s="21"/>
       <c r="D29" s="21"/>
@@ -21391,7 +21391,7 @@
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="119"/>
       <c r="B4" s="293" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="C4" s="354"/>
       <c r="D4" s="354"/>
@@ -21401,7 +21401,7 @@
       <c r="H4" s="119"/>
     </row>
     <row r="5" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="370" t="s">
+      <c r="A5" s="383" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="219"/>
@@ -21412,13 +21412,13 @@
       <c r="G5" s="190"/>
       <c r="H5" s="119"/>
       <c r="J5" s="427" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K5" s="427"/>
       <c r="L5" s="427"/>
     </row>
     <row r="6" spans="1:12" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A6" s="370"/>
+      <c r="A6" s="383"/>
       <c r="B6" s="220" t="s">
         <v>111</v>
       </c>
@@ -21613,7 +21613,7 @@
         <v>49</v>
       </c>
       <c r="D14" s="223" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="E14" s="272"/>
       <c r="F14" s="222" t="s">
@@ -21632,10 +21632,10 @@
       <c r="A15" s="416"/>
       <c r="B15" s="429"/>
       <c r="C15" s="222" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D15" s="223" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="E15" s="272"/>
       <c r="F15" s="222" t="s">
@@ -21654,10 +21654,10 @@
       <c r="A16" s="416"/>
       <c r="B16" s="430"/>
       <c r="C16" s="222" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="D16" s="223" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="E16" s="272"/>
       <c r="F16" s="222" t="s">
@@ -21745,7 +21745,7 @@
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="196"/>
       <c r="B23" s="293" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C23" s="339"/>
       <c r="D23" s="340"/>
@@ -21820,7 +21820,7 @@
         <v>0.41399999999999998</v>
       </c>
       <c r="H27" s="199" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="I27" s="254"/>
     </row>
@@ -21842,7 +21842,7 @@
         <v>0.59</v>
       </c>
       <c r="H28" s="199" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I28" s="254"/>
     </row>
@@ -21880,7 +21880,7 @@
         <v>1.6719999999999999</v>
       </c>
       <c r="H30" s="199" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="I30" s="254"/>
     </row>
@@ -21902,7 +21902,7 @@
         <v>1.788</v>
       </c>
       <c r="H31" s="199" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="I31" s="254"/>
     </row>
@@ -21924,7 +21924,7 @@
         <v>1.3</v>
       </c>
       <c r="H32" s="199" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="I32" s="254"/>
     </row>
@@ -22012,7 +22012,7 @@
         <v>860</v>
       </c>
       <c r="H38" s="199" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="I38" s="254"/>
     </row>
@@ -22109,7 +22109,7 @@
     <row r="45" spans="1:9" ht="16.2" x14ac:dyDescent="0.35">
       <c r="A45" s="193"/>
       <c r="B45" s="431" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="C45" s="432"/>
       <c r="D45" s="218">
@@ -22246,7 +22246,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>21</v>
@@ -22660,7 +22660,7 @@
       <c r="D45" s="62"/>
     </row>
     <row r="46" spans="1:6" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="370" t="s">
+      <c r="A46" s="383" t="s">
         <v>12</v>
       </c>
       <c r="B46" s="437" t="s">
@@ -22677,7 +22677,7 @@
       <c r="F46" s="107"/>
     </row>
     <row r="47" spans="1:6" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="370"/>
+      <c r="A47" s="383"/>
       <c r="B47" s="438"/>
       <c r="C47" s="281">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
@@ -22738,7 +22738,7 @@
         <v>12</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C55" s="283">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis1-Gesamtpreis1*(-0.2*LN(Haltedauer)+0.667),0)</f>
@@ -22802,7 +22802,7 @@
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="370" t="s">
+      <c r="A60" s="383" t="s">
         <v>12</v>
       </c>
       <c r="B60" s="327" t="str">
@@ -22820,7 +22820,7 @@
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="370"/>
+      <c r="A61" s="383"/>
       <c r="B61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
@@ -22836,7 +22836,7 @@
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="370"/>
+      <c r="A62" s="383"/>
       <c r="B62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
@@ -22938,7 +22938,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>21</v>
@@ -23405,7 +23405,7 @@
       <c r="F45" s="125"/>
     </row>
     <row r="46" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A46" s="370" t="s">
+      <c r="A46" s="383" t="s">
         <v>12</v>
       </c>
       <c r="B46" s="437" t="s">
@@ -23422,7 +23422,7 @@
       <c r="F46" s="125"/>
     </row>
     <row r="47" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A47" s="370"/>
+      <c r="A47" s="383"/>
       <c r="B47" s="438"/>
       <c r="C47" s="281">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
@@ -23490,7 +23490,7 @@
         <v>12</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C55" s="283">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis2-Gesamtpreis2*(-0.2*LN(Haltedauer)+0.667),0)</f>
@@ -23555,7 +23555,7 @@
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="370" t="s">
+      <c r="A60" s="383" t="s">
         <v>12</v>
       </c>
       <c r="B60" s="327" t="str">
@@ -23573,7 +23573,7 @@
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="370"/>
+      <c r="A61" s="383"/>
       <c r="B61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
@@ -23589,7 +23589,7 @@
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="370"/>
+      <c r="A62" s="383"/>
       <c r="B62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
@@ -23698,7 +23698,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>21</v>
@@ -24165,7 +24165,7 @@
       <c r="F45" s="125"/>
     </row>
     <row r="46" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A46" s="370" t="s">
+      <c r="A46" s="383" t="s">
         <v>12</v>
       </c>
       <c r="B46" s="437" t="s">
@@ -24182,7 +24182,7 @@
       <c r="F46" s="133"/>
     </row>
     <row r="47" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A47" s="370"/>
+      <c r="A47" s="383"/>
       <c r="B47" s="438"/>
       <c r="C47" s="281">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
@@ -24250,7 +24250,7 @@
         <v>12</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="C55" s="283">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis3-Gesamtpreis3*(-0.2*LN(Haltedauer)+0.667),0)</f>
@@ -24315,7 +24315,7 @@
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="370" t="s">
+      <c r="A60" s="383" t="s">
         <v>12</v>
       </c>
       <c r="B60" s="327" t="str">
@@ -24333,7 +24333,7 @@
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="370"/>
+      <c r="A61" s="383"/>
       <c r="B61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
@@ -24349,7 +24349,7 @@
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="370"/>
+      <c r="A62" s="383"/>
       <c r="B62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
@@ -24436,14 +24436,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5e4dc333-02c0-4d6f-a03d-d04a548a7be7">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -24676,27 +24674,20 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5e4dc333-02c0-4d6f-a03d-d04a548a7be7">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{651615EB-DE44-4BF4-BD1E-846AB7A3DA36}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92A2CDCF-36F6-4C30-8F9B-D45880CB8E7E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="5e4dc333-02c0-4d6f-a03d-d04a548a7be7"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -24721,9 +24712,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92A2CDCF-36F6-4C30-8F9B-D45880CB8E7E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{651615EB-DE44-4BF4-BD1E-846AB7A3DA36}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="5e4dc333-02c0-4d6f-a03d-d04a548a7be7"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/src/assets/downloads/LZK-Rechner_Pkw_V1.3_Beispiel.xlsx
+++ b/src/assets/downloads/LZK-Rechner_Pkw_V1.3_Beispiel.xlsx
@@ -5,12 +5,12 @@
   <workbookPr updateLinks="never"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ifeu2.sharepoint.com/sites/DBUBeschaffungBerlin/Freigegebene Dokumente/General/Folgeprojekt/03_Arbeitsdokumente/A4 - Aktualisierung der Instrumente aus Basisprojekt/LZK-Rechner/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Julia Pelzeter\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{F8E3439C-4500-4DCC-A4D0-17CF3516801A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{43ECE931-5FF1-4BEE-94AA-76E0326F3B61}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53026537-1F40-422F-8B47-C536A110038D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="887" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" tabRatio="887" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Anleitung" sheetId="27" r:id="rId1"/>
@@ -5566,6 +5566,15 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
@@ -5600,15 +5609,6 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="13" borderId="0" xfId="3" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
@@ -12437,7 +12437,7 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9090449" y="2604135"/>
+          <a:off x="9418109" y="2604135"/>
           <a:ext cx="1631979" cy="976630"/>
           <a:chOff x="8390255" y="2565400"/>
           <a:chExt cx="1643409" cy="965200"/>
@@ -14064,17 +14064,17 @@
       <c r="J4" s="115"/>
     </row>
     <row r="5" spans="2:10" ht="149.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="370" t="s">
+      <c r="B5" s="373" t="s">
         <v>488</v>
       </c>
-      <c r="C5" s="370"/>
-      <c r="D5" s="370"/>
-      <c r="E5" s="370"/>
-      <c r="F5" s="370"/>
-      <c r="G5" s="370"/>
-      <c r="H5" s="370"/>
-      <c r="I5" s="370"/>
-      <c r="J5" s="370"/>
+      <c r="C5" s="373"/>
+      <c r="D5" s="373"/>
+      <c r="E5" s="373"/>
+      <c r="F5" s="373"/>
+      <c r="G5" s="373"/>
+      <c r="H5" s="373"/>
+      <c r="I5" s="373"/>
+      <c r="J5" s="373"/>
     </row>
     <row r="6" spans="2:10" ht="11.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="245"/>
@@ -14112,13 +14112,13 @@
     <row r="9" spans="2:10" ht="52.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D9" s="245"/>
       <c r="E9" s="245"/>
-      <c r="F9" s="371" t="s">
+      <c r="F9" s="374" t="s">
         <v>440</v>
       </c>
-      <c r="G9" s="371"/>
-      <c r="H9" s="371"/>
-      <c r="I9" s="371"/>
-      <c r="J9" s="371"/>
+      <c r="G9" s="374"/>
+      <c r="H9" s="374"/>
+      <c r="I9" s="374"/>
+      <c r="J9" s="374"/>
     </row>
     <row r="10" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D10" s="245"/>
@@ -14132,31 +14132,31 @@
     <row r="11" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D11" s="245"/>
       <c r="E11" s="245"/>
-      <c r="F11" s="372" t="s">
+      <c r="F11" s="375" t="s">
         <v>461</v>
       </c>
-      <c r="G11" s="373"/>
-      <c r="H11" s="373"/>
-      <c r="I11" s="373"/>
-      <c r="J11" s="373"/>
+      <c r="G11" s="376"/>
+      <c r="H11" s="376"/>
+      <c r="I11" s="376"/>
+      <c r="J11" s="376"/>
     </row>
     <row r="12" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D12" s="245"/>
       <c r="E12" s="245"/>
-      <c r="F12" s="373"/>
-      <c r="G12" s="373"/>
-      <c r="H12" s="373"/>
-      <c r="I12" s="373"/>
-      <c r="J12" s="373"/>
+      <c r="F12" s="376"/>
+      <c r="G12" s="376"/>
+      <c r="H12" s="376"/>
+      <c r="I12" s="376"/>
+      <c r="J12" s="376"/>
     </row>
     <row r="13" spans="2:10" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D13" s="245"/>
       <c r="E13" s="245"/>
-      <c r="F13" s="373"/>
-      <c r="G13" s="373"/>
-      <c r="H13" s="373"/>
-      <c r="I13" s="373"/>
-      <c r="J13" s="373"/>
+      <c r="F13" s="376"/>
+      <c r="G13" s="376"/>
+      <c r="H13" s="376"/>
+      <c r="I13" s="376"/>
+      <c r="J13" s="376"/>
     </row>
     <row r="14" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D14" s="245"/>
@@ -14170,22 +14170,22 @@
     <row r="15" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D15" s="245"/>
       <c r="E15" s="245"/>
-      <c r="F15" s="374" t="s">
+      <c r="F15" s="377" t="s">
         <v>2</v>
       </c>
-      <c r="G15" s="375"/>
-      <c r="H15" s="375"/>
-      <c r="I15" s="375"/>
-      <c r="J15" s="375"/>
+      <c r="G15" s="378"/>
+      <c r="H15" s="378"/>
+      <c r="I15" s="378"/>
+      <c r="J15" s="378"/>
     </row>
     <row r="16" spans="2:10" ht="73.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D16" s="245"/>
       <c r="E16" s="245"/>
-      <c r="F16" s="375"/>
-      <c r="G16" s="375"/>
-      <c r="H16" s="375"/>
-      <c r="I16" s="375"/>
-      <c r="J16" s="375"/>
+      <c r="F16" s="378"/>
+      <c r="G16" s="378"/>
+      <c r="H16" s="378"/>
+      <c r="I16" s="378"/>
+      <c r="J16" s="378"/>
     </row>
     <row r="17" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D17" s="245"/>
@@ -14199,13 +14199,13 @@
     <row r="18" spans="2:10" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D18" s="245"/>
       <c r="E18" s="245"/>
-      <c r="F18" s="376" t="s">
+      <c r="F18" s="379" t="s">
         <v>3</v>
       </c>
-      <c r="G18" s="377"/>
-      <c r="H18" s="377"/>
-      <c r="I18" s="377"/>
-      <c r="J18" s="377"/>
+      <c r="G18" s="380"/>
+      <c r="H18" s="380"/>
+      <c r="I18" s="380"/>
+      <c r="J18" s="380"/>
     </row>
     <row r="19" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D19" s="245"/>
@@ -14219,31 +14219,31 @@
     <row r="20" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D20" s="245"/>
       <c r="E20" s="245"/>
-      <c r="F20" s="378" t="s">
+      <c r="F20" s="381" t="s">
         <v>4</v>
       </c>
-      <c r="G20" s="378"/>
-      <c r="H20" s="378"/>
-      <c r="I20" s="378"/>
-      <c r="J20" s="378"/>
+      <c r="G20" s="381"/>
+      <c r="H20" s="381"/>
+      <c r="I20" s="381"/>
+      <c r="J20" s="381"/>
     </row>
     <row r="21" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D21" s="245"/>
       <c r="E21" s="245"/>
-      <c r="F21" s="378"/>
-      <c r="G21" s="378"/>
-      <c r="H21" s="378"/>
-      <c r="I21" s="378"/>
-      <c r="J21" s="378"/>
+      <c r="F21" s="381"/>
+      <c r="G21" s="381"/>
+      <c r="H21" s="381"/>
+      <c r="I21" s="381"/>
+      <c r="J21" s="381"/>
     </row>
     <row r="22" spans="2:10" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D22" s="245"/>
       <c r="E22" s="245"/>
-      <c r="F22" s="378"/>
-      <c r="G22" s="378"/>
-      <c r="H22" s="378"/>
-      <c r="I22" s="378"/>
-      <c r="J22" s="378"/>
+      <c r="F22" s="381"/>
+      <c r="G22" s="381"/>
+      <c r="H22" s="381"/>
+      <c r="I22" s="381"/>
+      <c r="J22" s="381"/>
     </row>
     <row r="23" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D23" s="245"/>
@@ -14257,22 +14257,22 @@
     <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="D24" s="245"/>
       <c r="E24" s="245"/>
-      <c r="F24" s="379" t="s">
+      <c r="F24" s="382" t="s">
         <v>5</v>
       </c>
-      <c r="G24" s="379"/>
-      <c r="H24" s="379"/>
-      <c r="I24" s="379"/>
-      <c r="J24" s="379"/>
+      <c r="G24" s="382"/>
+      <c r="H24" s="382"/>
+      <c r="I24" s="382"/>
+      <c r="J24" s="382"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="D25" s="245"/>
       <c r="E25" s="245"/>
-      <c r="F25" s="379"/>
-      <c r="G25" s="379"/>
-      <c r="H25" s="379"/>
-      <c r="I25" s="379"/>
-      <c r="J25" s="379"/>
+      <c r="F25" s="382"/>
+      <c r="G25" s="382"/>
+      <c r="H25" s="382"/>
+      <c r="I25" s="382"/>
+      <c r="J25" s="382"/>
     </row>
     <row r="26" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D26" s="245"/>
@@ -14286,49 +14286,49 @@
     <row r="27" spans="2:10" ht="7.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D27" s="245"/>
       <c r="E27" s="245"/>
-      <c r="F27" s="369"/>
-      <c r="G27" s="369"/>
-      <c r="H27" s="369"/>
-      <c r="I27" s="369"/>
-      <c r="J27" s="369"/>
+      <c r="F27" s="372"/>
+      <c r="G27" s="372"/>
+      <c r="H27" s="372"/>
+      <c r="I27" s="372"/>
+      <c r="J27" s="372"/>
     </row>
     <row r="28" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D28" s="245"/>
       <c r="E28" s="245"/>
-      <c r="F28" s="380" t="s">
+      <c r="F28" s="383" t="s">
         <v>462</v>
       </c>
-      <c r="G28" s="380"/>
-      <c r="H28" s="380"/>
-      <c r="I28" s="380"/>
-      <c r="J28" s="380"/>
+      <c r="G28" s="383"/>
+      <c r="H28" s="383"/>
+      <c r="I28" s="383"/>
+      <c r="J28" s="383"/>
     </row>
     <row r="29" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D29" s="245"/>
       <c r="E29" s="245"/>
-      <c r="F29" s="380"/>
-      <c r="G29" s="380"/>
-      <c r="H29" s="380"/>
-      <c r="I29" s="380"/>
-      <c r="J29" s="380"/>
+      <c r="F29" s="383"/>
+      <c r="G29" s="383"/>
+      <c r="H29" s="383"/>
+      <c r="I29" s="383"/>
+      <c r="J29" s="383"/>
     </row>
     <row r="30" spans="2:10" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D30" s="245"/>
       <c r="E30" s="245"/>
-      <c r="F30" s="380"/>
-      <c r="G30" s="380"/>
-      <c r="H30" s="380"/>
-      <c r="I30" s="380"/>
-      <c r="J30" s="380"/>
+      <c r="F30" s="383"/>
+      <c r="G30" s="383"/>
+      <c r="H30" s="383"/>
+      <c r="I30" s="383"/>
+      <c r="J30" s="383"/>
     </row>
     <row r="31" spans="2:10" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D31" s="245"/>
       <c r="E31" s="245"/>
-      <c r="F31" s="381"/>
-      <c r="G31" s="381"/>
-      <c r="H31" s="381"/>
-      <c r="I31" s="381"/>
-      <c r="J31" s="381"/>
+      <c r="F31" s="371"/>
+      <c r="G31" s="371"/>
+      <c r="H31" s="371"/>
+      <c r="I31" s="371"/>
+      <c r="J31" s="371"/>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="250" t="s">
@@ -14377,15 +14377,15 @@
     <row r="36" spans="2:11" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="116"/>
       <c r="C36" s="113"/>
-      <c r="D36" s="381" t="s">
+      <c r="D36" s="371" t="s">
         <v>8</v>
       </c>
-      <c r="E36" s="381"/>
-      <c r="F36" s="381"/>
-      <c r="G36" s="381"/>
-      <c r="H36" s="381"/>
-      <c r="I36" s="381"/>
-      <c r="J36" s="381"/>
+      <c r="E36" s="371"/>
+      <c r="F36" s="371"/>
+      <c r="G36" s="371"/>
+      <c r="H36" s="371"/>
+      <c r="I36" s="371"/>
+      <c r="J36" s="371"/>
     </row>
     <row r="37" spans="2:11" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="117"/>
@@ -14401,24 +14401,24 @@
     <row r="38" spans="2:11" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B38" s="241"/>
       <c r="C38" s="113"/>
-      <c r="D38" s="369" t="s">
+      <c r="D38" s="372" t="s">
         <v>9</v>
       </c>
-      <c r="E38" s="369"/>
-      <c r="F38" s="369"/>
-      <c r="G38" s="369"/>
-      <c r="H38" s="369"/>
-      <c r="I38" s="369"/>
-      <c r="J38" s="369"/>
+      <c r="E38" s="372"/>
+      <c r="F38" s="372"/>
+      <c r="G38" s="372"/>
+      <c r="H38" s="372"/>
+      <c r="I38" s="372"/>
+      <c r="J38" s="372"/>
     </row>
     <row r="39" spans="2:11" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D39" s="369"/>
-      <c r="E39" s="369"/>
-      <c r="F39" s="369"/>
-      <c r="G39" s="369"/>
-      <c r="H39" s="369"/>
-      <c r="I39" s="369"/>
-      <c r="J39" s="369"/>
+      <c r="D39" s="372"/>
+      <c r="E39" s="372"/>
+      <c r="F39" s="372"/>
+      <c r="G39" s="372"/>
+      <c r="H39" s="372"/>
+      <c r="I39" s="372"/>
+      <c r="J39" s="372"/>
     </row>
     <row r="40" spans="2:11" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="117"/>
@@ -14436,15 +14436,15 @@
         <v>10</v>
       </c>
       <c r="C41" s="113"/>
-      <c r="D41" s="382" t="s">
+      <c r="D41" s="369" t="s">
         <v>11</v>
       </c>
-      <c r="E41" s="382"/>
-      <c r="F41" s="382"/>
-      <c r="G41" s="382"/>
-      <c r="H41" s="382"/>
-      <c r="I41" s="382"/>
-      <c r="J41" s="382"/>
+      <c r="E41" s="369"/>
+      <c r="F41" s="369"/>
+      <c r="G41" s="369"/>
+      <c r="H41" s="369"/>
+      <c r="I41" s="369"/>
+      <c r="J41" s="369"/>
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" s="113"/>
@@ -14458,30 +14458,30 @@
       <c r="J42" s="245"/>
     </row>
     <row r="43" spans="2:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="383" t="s">
+      <c r="B43" s="370" t="s">
         <v>12</v>
       </c>
       <c r="C43" s="103"/>
-      <c r="D43" s="381" t="s">
+      <c r="D43" s="371" t="s">
         <v>13</v>
       </c>
-      <c r="E43" s="381"/>
-      <c r="F43" s="381"/>
-      <c r="G43" s="381"/>
-      <c r="H43" s="381"/>
-      <c r="I43" s="381"/>
-      <c r="J43" s="381"/>
+      <c r="E43" s="371"/>
+      <c r="F43" s="371"/>
+      <c r="G43" s="371"/>
+      <c r="H43" s="371"/>
+      <c r="I43" s="371"/>
+      <c r="J43" s="371"/>
     </row>
     <row r="44" spans="2:11" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="B44" s="383"/>
+      <c r="B44" s="370"/>
       <c r="C44" s="103"/>
-      <c r="D44" s="381"/>
-      <c r="E44" s="381"/>
-      <c r="F44" s="381"/>
-      <c r="G44" s="381"/>
-      <c r="H44" s="381"/>
-      <c r="I44" s="381"/>
-      <c r="J44" s="381"/>
+      <c r="D44" s="371"/>
+      <c r="E44" s="371"/>
+      <c r="F44" s="371"/>
+      <c r="G44" s="371"/>
+      <c r="H44" s="371"/>
+      <c r="I44" s="371"/>
+      <c r="J44" s="371"/>
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.25">
       <c r="D45" s="112"/>
@@ -14493,17 +14493,17 @@
       <c r="J45" s="114"/>
     </row>
     <row r="46" spans="2:11" ht="58.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="381" t="s">
+      <c r="B46" s="371" t="s">
         <v>584</v>
       </c>
-      <c r="C46" s="381"/>
-      <c r="D46" s="381"/>
-      <c r="E46" s="381"/>
-      <c r="F46" s="381"/>
-      <c r="G46" s="381"/>
-      <c r="H46" s="381"/>
-      <c r="I46" s="381"/>
-      <c r="J46" s="381"/>
+      <c r="C46" s="371"/>
+      <c r="D46" s="371"/>
+      <c r="E46" s="371"/>
+      <c r="F46" s="371"/>
+      <c r="G46" s="371"/>
+      <c r="H46" s="371"/>
+      <c r="I46" s="371"/>
+      <c r="J46" s="371"/>
       <c r="K46" s="107"/>
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.25">
@@ -14538,17 +14538,17 @@
       <c r="J49" s="112"/>
     </row>
     <row r="50" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="381" t="s">
+      <c r="B50" s="371" t="s">
         <v>15</v>
       </c>
-      <c r="C50" s="381"/>
-      <c r="D50" s="381"/>
-      <c r="E50" s="381"/>
-      <c r="F50" s="381"/>
-      <c r="G50" s="381"/>
-      <c r="H50" s="381"/>
-      <c r="I50" s="381"/>
-      <c r="J50" s="381"/>
+      <c r="C50" s="371"/>
+      <c r="D50" s="371"/>
+      <c r="E50" s="371"/>
+      <c r="F50" s="371"/>
+      <c r="G50" s="371"/>
+      <c r="H50" s="371"/>
+      <c r="I50" s="371"/>
+      <c r="J50" s="371"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D51" s="114"/>
@@ -14611,11 +14611,6 @@
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="17">
-    <mergeCell ref="D41:J41"/>
-    <mergeCell ref="B43:B44"/>
-    <mergeCell ref="D43:J44"/>
-    <mergeCell ref="B46:J46"/>
-    <mergeCell ref="B50:J50"/>
     <mergeCell ref="D38:J39"/>
     <mergeCell ref="B5:J5"/>
     <mergeCell ref="F9:J9"/>
@@ -14628,6 +14623,11 @@
     <mergeCell ref="F28:J30"/>
     <mergeCell ref="F31:J31"/>
     <mergeCell ref="D36:J36"/>
+    <mergeCell ref="D41:J41"/>
+    <mergeCell ref="B43:B44"/>
+    <mergeCell ref="D43:J44"/>
+    <mergeCell ref="B46:J46"/>
+    <mergeCell ref="B50:J50"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="F9:J9" location="Input_Beschaffung!A1" display="Geben Sie die übergeordneten Informationen zu Ihrem Beschaffungsfall ein. Hier können Informationen wie die erwartete jährliche Fahrleistung, die Art der Beschaffung (Kauf/Leasing) und weitere Informationen eingegeben werden." xr:uid="{00000000-0004-0000-0000-000000000000}"/>
@@ -15136,7 +15136,7 @@
       <c r="F45" s="125"/>
     </row>
     <row r="46" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A46" s="383" t="s">
+      <c r="A46" s="370" t="s">
         <v>12</v>
       </c>
       <c r="B46" s="437" t="s">
@@ -15153,7 +15153,7 @@
       <c r="F46" s="125"/>
     </row>
     <row r="47" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A47" s="383"/>
+      <c r="A47" s="370"/>
       <c r="B47" s="438"/>
       <c r="C47" s="281">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
@@ -15286,7 +15286,7 @@
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="383" t="s">
+      <c r="A60" s="370" t="s">
         <v>12</v>
       </c>
       <c r="B60" s="327" t="str">
@@ -15304,7 +15304,7 @@
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="383"/>
+      <c r="A61" s="370"/>
       <c r="B61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
@@ -15320,7 +15320,7 @@
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="383"/>
+      <c r="A62" s="370"/>
       <c r="B62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
@@ -15900,7 +15900,7 @@
       <c r="F45" s="125"/>
     </row>
     <row r="46" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A46" s="383" t="s">
+      <c r="A46" s="370" t="s">
         <v>12</v>
       </c>
       <c r="B46" s="437" t="s">
@@ -15917,7 +15917,7 @@
       <c r="F46" s="125"/>
     </row>
     <row r="47" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A47" s="383"/>
+      <c r="A47" s="370"/>
       <c r="B47" s="438"/>
       <c r="C47" s="281">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
@@ -16050,7 +16050,7 @@
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="383" t="s">
+      <c r="A60" s="370" t="s">
         <v>12</v>
       </c>
       <c r="B60" s="327" t="str">
@@ -16068,7 +16068,7 @@
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="383"/>
+      <c r="A61" s="370"/>
       <c r="B61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
@@ -16084,7 +16084,7 @@
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="383"/>
+      <c r="A62" s="370"/>
       <c r="B62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
@@ -18771,7 +18771,7 @@
     <col min="1" max="1" width="2.109375" style="1" customWidth="1"/>
     <col min="2" max="2" width="5.109375" style="1" customWidth="1"/>
     <col min="3" max="3" width="28.6640625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.6640625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.44140625" style="1" customWidth="1"/>
     <col min="5" max="9" width="14.33203125" style="1" customWidth="1"/>
     <col min="10" max="10" width="3.33203125" style="1" customWidth="1"/>
     <col min="11" max="11" width="7.109375" style="7" customWidth="1"/>
@@ -19060,7 +19060,7 @@
         <v>Fahrzeuggesamtpreis (brutto)</v>
       </c>
       <c r="D13" s="166" t="str">
-        <f>IF(ISBLANK(FinArt), "Input_Projekt", VLOOKUP(FinArt,FinArtList,2,FALSE))</f>
+        <f>IF(ISBLANK(FinArt), "Input_Beschaffung", VLOOKUP(FinArt,FinArtList,2,FALSE))</f>
         <v>EUR</v>
       </c>
       <c r="E13" s="142">
@@ -19362,7 +19362,7 @@
       <c r="R23" s="7"/>
     </row>
     <row r="24" spans="2:18" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="383" t="s">
+      <c r="B24" s="370" t="s">
         <v>12</v>
       </c>
       <c r="C24" s="331" t="s">
@@ -19393,7 +19393,7 @@
       <c r="R24" s="7"/>
     </row>
     <row r="25" spans="2:18" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="383"/>
+      <c r="B25" s="370"/>
       <c r="C25" s="331"/>
       <c r="D25" s="322" t="s">
         <v>162</v>
@@ -19410,7 +19410,7 @@
       <c r="R25" s="7"/>
     </row>
     <row r="26" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B26" s="383"/>
+      <c r="B26" s="370"/>
       <c r="C26" s="335"/>
       <c r="D26" s="322" t="s">
         <v>162</v>
@@ -21401,7 +21401,7 @@
       <c r="H4" s="119"/>
     </row>
     <row r="5" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="383" t="s">
+      <c r="A5" s="370" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="219"/>
@@ -21418,7 +21418,7 @@
       <c r="L5" s="427"/>
     </row>
     <row r="6" spans="1:12" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A6" s="383"/>
+      <c r="A6" s="370"/>
       <c r="B6" s="220" t="s">
         <v>111</v>
       </c>
@@ -22660,7 +22660,7 @@
       <c r="D45" s="62"/>
     </row>
     <row r="46" spans="1:6" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="383" t="s">
+      <c r="A46" s="370" t="s">
         <v>12</v>
       </c>
       <c r="B46" s="437" t="s">
@@ -22677,7 +22677,7 @@
       <c r="F46" s="107"/>
     </row>
     <row r="47" spans="1:6" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="383"/>
+      <c r="A47" s="370"/>
       <c r="B47" s="438"/>
       <c r="C47" s="281">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
@@ -22802,7 +22802,7 @@
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="383" t="s">
+      <c r="A60" s="370" t="s">
         <v>12</v>
       </c>
       <c r="B60" s="327" t="str">
@@ -22820,7 +22820,7 @@
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="383"/>
+      <c r="A61" s="370"/>
       <c r="B61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
@@ -22836,7 +22836,7 @@
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="383"/>
+      <c r="A62" s="370"/>
       <c r="B62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
@@ -23405,7 +23405,7 @@
       <c r="F45" s="125"/>
     </row>
     <row r="46" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A46" s="383" t="s">
+      <c r="A46" s="370" t="s">
         <v>12</v>
       </c>
       <c r="B46" s="437" t="s">
@@ -23422,7 +23422,7 @@
       <c r="F46" s="125"/>
     </row>
     <row r="47" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A47" s="383"/>
+      <c r="A47" s="370"/>
       <c r="B47" s="438"/>
       <c r="C47" s="281">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
@@ -23555,7 +23555,7 @@
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="383" t="s">
+      <c r="A60" s="370" t="s">
         <v>12</v>
       </c>
       <c r="B60" s="327" t="str">
@@ -23573,7 +23573,7 @@
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="383"/>
+      <c r="A61" s="370"/>
       <c r="B61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
@@ -23589,7 +23589,7 @@
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="383"/>
+      <c r="A62" s="370"/>
       <c r="B62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
@@ -24165,7 +24165,7 @@
       <c r="F45" s="125"/>
     </row>
     <row r="46" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A46" s="383" t="s">
+      <c r="A46" s="370" t="s">
         <v>12</v>
       </c>
       <c r="B46" s="437" t="s">
@@ -24182,7 +24182,7 @@
       <c r="F46" s="133"/>
     </row>
     <row r="47" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A47" s="383"/>
+      <c r="A47" s="370"/>
       <c r="B47" s="438"/>
       <c r="C47" s="281">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
@@ -24315,7 +24315,7 @@
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="383" t="s">
+      <c r="A60" s="370" t="s">
         <v>12</v>
       </c>
       <c r="B60" s="327" t="str">
@@ -24333,7 +24333,7 @@
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="383"/>
+      <c r="A61" s="370"/>
       <c r="B61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
@@ -24349,7 +24349,7 @@
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="383"/>
+      <c r="A62" s="370"/>
       <c r="B62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
@@ -24436,12 +24436,14 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5e4dc333-02c0-4d6f-a03d-d04a548a7be7">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -24674,20 +24676,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5e4dc333-02c0-4d6f-a03d-d04a548a7be7">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92A2CDCF-36F6-4C30-8F9B-D45880CB8E7E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{651615EB-DE44-4BF4-BD1E-846AB7A3DA36}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="5e4dc333-02c0-4d6f-a03d-d04a548a7be7"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -24712,18 +24721,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{651615EB-DE44-4BF4-BD1E-846AB7A3DA36}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92A2CDCF-36F6-4C30-8F9B-D45880CB8E7E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="5e4dc333-02c0-4d6f-a03d-d04a548a7be7"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/src/assets/downloads/LZK-Rechner_Pkw_V1.3_Beispiel.xlsx
+++ b/src/assets/downloads/LZK-Rechner_Pkw_V1.3_Beispiel.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Julia Pelzeter\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53026537-1F40-422F-8B47-C536A110038D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{453D6D5E-EDB8-46DA-AFAC-9E1DCB46BFD8}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8940" tabRatio="887" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="11124" tabRatio="887" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Anleitung" sheetId="27" r:id="rId1"/>
@@ -180,7 +180,7 @@
     <definedName name="Zusatzinfo5">Eingabe_Angebotswerte!$I$12</definedName>
     <definedName name="Zustaendig">Input_Beschaffung!$C$10</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterate="1" iterateCount="1000"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -2760,9 +2760,6 @@
     <t>UBA (2024b)</t>
   </si>
   <si>
-    <t>https://www.umweltbundesamt.de/sites/default/files/medien/11850/publikationen/23_2024_cc_strommix_07_2024.pdf</t>
-  </si>
-  <si>
     <t>Entwicklung der spezifischen Treibhausgas-Emissionen des deutschen Strommix in den Jahren 1990 - 2023</t>
   </si>
   <si>
@@ -3364,6 +3361,9 @@
       </rPr>
       <t>Es ist jedoch zu berücksichtigen, dass dadurch Berechnungsfehler entstehen können. Die Verantwortung liegt bei der Person, die den Rechner angepasst hat.</t>
     </r>
+  </si>
+  <si>
+    <t>https://www.umweltbundesamt.de/publikationen/entwicklung-der-spezifischen-treibhausgas-10</t>
   </si>
 </sst>
 </file>
@@ -4674,7 +4674,7 @@
     <xf numFmtId="166" fontId="12" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="443">
+  <cellXfs count="442">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5297,9 +5297,6 @@
     <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="4" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -12437,8 +12434,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9418109" y="2604135"/>
-          <a:ext cx="1631979" cy="976630"/>
+          <a:off x="9400964" y="2569845"/>
+          <a:ext cx="1630074" cy="963295"/>
           <a:chOff x="8390255" y="2565400"/>
           <a:chExt cx="1643409" cy="965200"/>
         </a:xfrm>
@@ -14042,7 +14039,7 @@
       <c r="H2" s="16"/>
       <c r="I2" s="16"/>
       <c r="J2" s="268" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="3" spans="2:10" x14ac:dyDescent="0.25">
@@ -14064,17 +14061,17 @@
       <c r="J4" s="115"/>
     </row>
     <row r="5" spans="2:10" ht="149.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="373" t="s">
-        <v>488</v>
-      </c>
-      <c r="C5" s="373"/>
-      <c r="D5" s="373"/>
-      <c r="E5" s="373"/>
-      <c r="F5" s="373"/>
-      <c r="G5" s="373"/>
-      <c r="H5" s="373"/>
-      <c r="I5" s="373"/>
-      <c r="J5" s="373"/>
+      <c r="B5" s="372" t="s">
+        <v>487</v>
+      </c>
+      <c r="C5" s="372"/>
+      <c r="D5" s="372"/>
+      <c r="E5" s="372"/>
+      <c r="F5" s="372"/>
+      <c r="G5" s="372"/>
+      <c r="H5" s="372"/>
+      <c r="I5" s="372"/>
+      <c r="J5" s="372"/>
     </row>
     <row r="6" spans="2:10" ht="11.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="245"/>
@@ -14112,13 +14109,13 @@
     <row r="9" spans="2:10" ht="52.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D9" s="245"/>
       <c r="E9" s="245"/>
-      <c r="F9" s="374" t="s">
+      <c r="F9" s="373" t="s">
         <v>440</v>
       </c>
-      <c r="G9" s="374"/>
-      <c r="H9" s="374"/>
-      <c r="I9" s="374"/>
-      <c r="J9" s="374"/>
+      <c r="G9" s="373"/>
+      <c r="H9" s="373"/>
+      <c r="I9" s="373"/>
+      <c r="J9" s="373"/>
     </row>
     <row r="10" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D10" s="245"/>
@@ -14132,31 +14129,31 @@
     <row r="11" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D11" s="245"/>
       <c r="E11" s="245"/>
-      <c r="F11" s="375" t="s">
-        <v>461</v>
-      </c>
-      <c r="G11" s="376"/>
-      <c r="H11" s="376"/>
-      <c r="I11" s="376"/>
-      <c r="J11" s="376"/>
+      <c r="F11" s="374" t="s">
+        <v>460</v>
+      </c>
+      <c r="G11" s="375"/>
+      <c r="H11" s="375"/>
+      <c r="I11" s="375"/>
+      <c r="J11" s="375"/>
     </row>
     <row r="12" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D12" s="245"/>
       <c r="E12" s="245"/>
-      <c r="F12" s="376"/>
-      <c r="G12" s="376"/>
-      <c r="H12" s="376"/>
-      <c r="I12" s="376"/>
-      <c r="J12" s="376"/>
+      <c r="F12" s="375"/>
+      <c r="G12" s="375"/>
+      <c r="H12" s="375"/>
+      <c r="I12" s="375"/>
+      <c r="J12" s="375"/>
     </row>
     <row r="13" spans="2:10" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D13" s="245"/>
       <c r="E13" s="245"/>
-      <c r="F13" s="376"/>
-      <c r="G13" s="376"/>
-      <c r="H13" s="376"/>
-      <c r="I13" s="376"/>
-      <c r="J13" s="376"/>
+      <c r="F13" s="375"/>
+      <c r="G13" s="375"/>
+      <c r="H13" s="375"/>
+      <c r="I13" s="375"/>
+      <c r="J13" s="375"/>
     </row>
     <row r="14" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D14" s="245"/>
@@ -14170,22 +14167,22 @@
     <row r="15" spans="2:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D15" s="245"/>
       <c r="E15" s="245"/>
-      <c r="F15" s="377" t="s">
+      <c r="F15" s="376" t="s">
         <v>2</v>
       </c>
-      <c r="G15" s="378"/>
-      <c r="H15" s="378"/>
-      <c r="I15" s="378"/>
-      <c r="J15" s="378"/>
+      <c r="G15" s="377"/>
+      <c r="H15" s="377"/>
+      <c r="I15" s="377"/>
+      <c r="J15" s="377"/>
     </row>
     <row r="16" spans="2:10" ht="73.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D16" s="245"/>
       <c r="E16" s="245"/>
-      <c r="F16" s="378"/>
-      <c r="G16" s="378"/>
-      <c r="H16" s="378"/>
-      <c r="I16" s="378"/>
-      <c r="J16" s="378"/>
+      <c r="F16" s="377"/>
+      <c r="G16" s="377"/>
+      <c r="H16" s="377"/>
+      <c r="I16" s="377"/>
+      <c r="J16" s="377"/>
     </row>
     <row r="17" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D17" s="245"/>
@@ -14199,13 +14196,13 @@
     <row r="18" spans="2:10" ht="40.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D18" s="245"/>
       <c r="E18" s="245"/>
-      <c r="F18" s="379" t="s">
+      <c r="F18" s="378" t="s">
         <v>3</v>
       </c>
-      <c r="G18" s="380"/>
-      <c r="H18" s="380"/>
-      <c r="I18" s="380"/>
-      <c r="J18" s="380"/>
+      <c r="G18" s="379"/>
+      <c r="H18" s="379"/>
+      <c r="I18" s="379"/>
+      <c r="J18" s="379"/>
     </row>
     <row r="19" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D19" s="245"/>
@@ -14219,31 +14216,31 @@
     <row r="20" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D20" s="245"/>
       <c r="E20" s="245"/>
-      <c r="F20" s="381" t="s">
+      <c r="F20" s="380" t="s">
         <v>4</v>
       </c>
-      <c r="G20" s="381"/>
-      <c r="H20" s="381"/>
-      <c r="I20" s="381"/>
-      <c r="J20" s="381"/>
+      <c r="G20" s="380"/>
+      <c r="H20" s="380"/>
+      <c r="I20" s="380"/>
+      <c r="J20" s="380"/>
     </row>
     <row r="21" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D21" s="245"/>
       <c r="E21" s="245"/>
-      <c r="F21" s="381"/>
-      <c r="G21" s="381"/>
-      <c r="H21" s="381"/>
-      <c r="I21" s="381"/>
-      <c r="J21" s="381"/>
+      <c r="F21" s="380"/>
+      <c r="G21" s="380"/>
+      <c r="H21" s="380"/>
+      <c r="I21" s="380"/>
+      <c r="J21" s="380"/>
     </row>
     <row r="22" spans="2:10" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D22" s="245"/>
       <c r="E22" s="245"/>
-      <c r="F22" s="381"/>
-      <c r="G22" s="381"/>
-      <c r="H22" s="381"/>
-      <c r="I22" s="381"/>
-      <c r="J22" s="381"/>
+      <c r="F22" s="380"/>
+      <c r="G22" s="380"/>
+      <c r="H22" s="380"/>
+      <c r="I22" s="380"/>
+      <c r="J22" s="380"/>
     </row>
     <row r="23" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D23" s="245"/>
@@ -14257,22 +14254,22 @@
     <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="D24" s="245"/>
       <c r="E24" s="245"/>
-      <c r="F24" s="382" t="s">
+      <c r="F24" s="381" t="s">
         <v>5</v>
       </c>
-      <c r="G24" s="382"/>
-      <c r="H24" s="382"/>
-      <c r="I24" s="382"/>
-      <c r="J24" s="382"/>
+      <c r="G24" s="381"/>
+      <c r="H24" s="381"/>
+      <c r="I24" s="381"/>
+      <c r="J24" s="381"/>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="D25" s="245"/>
       <c r="E25" s="245"/>
-      <c r="F25" s="382"/>
-      <c r="G25" s="382"/>
-      <c r="H25" s="382"/>
-      <c r="I25" s="382"/>
-      <c r="J25" s="382"/>
+      <c r="F25" s="381"/>
+      <c r="G25" s="381"/>
+      <c r="H25" s="381"/>
+      <c r="I25" s="381"/>
+      <c r="J25" s="381"/>
     </row>
     <row r="26" spans="2:10" ht="4.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D26" s="245"/>
@@ -14286,49 +14283,49 @@
     <row r="27" spans="2:10" ht="7.2" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D27" s="245"/>
       <c r="E27" s="245"/>
-      <c r="F27" s="372"/>
-      <c r="G27" s="372"/>
-      <c r="H27" s="372"/>
-      <c r="I27" s="372"/>
-      <c r="J27" s="372"/>
+      <c r="F27" s="371"/>
+      <c r="G27" s="371"/>
+      <c r="H27" s="371"/>
+      <c r="I27" s="371"/>
+      <c r="J27" s="371"/>
     </row>
     <row r="28" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D28" s="245"/>
       <c r="E28" s="245"/>
-      <c r="F28" s="383" t="s">
-        <v>462</v>
-      </c>
-      <c r="G28" s="383"/>
-      <c r="H28" s="383"/>
-      <c r="I28" s="383"/>
-      <c r="J28" s="383"/>
+      <c r="F28" s="382" t="s">
+        <v>461</v>
+      </c>
+      <c r="G28" s="382"/>
+      <c r="H28" s="382"/>
+      <c r="I28" s="382"/>
+      <c r="J28" s="382"/>
     </row>
     <row r="29" spans="2:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D29" s="245"/>
       <c r="E29" s="245"/>
-      <c r="F29" s="383"/>
-      <c r="G29" s="383"/>
-      <c r="H29" s="383"/>
-      <c r="I29" s="383"/>
-      <c r="J29" s="383"/>
+      <c r="F29" s="382"/>
+      <c r="G29" s="382"/>
+      <c r="H29" s="382"/>
+      <c r="I29" s="382"/>
+      <c r="J29" s="382"/>
     </row>
     <row r="30" spans="2:10" ht="6.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D30" s="245"/>
       <c r="E30" s="245"/>
-      <c r="F30" s="383"/>
-      <c r="G30" s="383"/>
-      <c r="H30" s="383"/>
-      <c r="I30" s="383"/>
-      <c r="J30" s="383"/>
+      <c r="F30" s="382"/>
+      <c r="G30" s="382"/>
+      <c r="H30" s="382"/>
+      <c r="I30" s="382"/>
+      <c r="J30" s="382"/>
     </row>
     <row r="31" spans="2:10" ht="10.199999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D31" s="245"/>
       <c r="E31" s="245"/>
-      <c r="F31" s="371"/>
-      <c r="G31" s="371"/>
-      <c r="H31" s="371"/>
-      <c r="I31" s="371"/>
-      <c r="J31" s="371"/>
+      <c r="F31" s="370"/>
+      <c r="G31" s="370"/>
+      <c r="H31" s="370"/>
+      <c r="I31" s="370"/>
+      <c r="J31" s="370"/>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="250" t="s">
@@ -14377,15 +14374,15 @@
     <row r="36" spans="2:11" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="116"/>
       <c r="C36" s="113"/>
-      <c r="D36" s="371" t="s">
+      <c r="D36" s="370" t="s">
         <v>8</v>
       </c>
-      <c r="E36" s="371"/>
-      <c r="F36" s="371"/>
-      <c r="G36" s="371"/>
-      <c r="H36" s="371"/>
-      <c r="I36" s="371"/>
-      <c r="J36" s="371"/>
+      <c r="E36" s="370"/>
+      <c r="F36" s="370"/>
+      <c r="G36" s="370"/>
+      <c r="H36" s="370"/>
+      <c r="I36" s="370"/>
+      <c r="J36" s="370"/>
     </row>
     <row r="37" spans="2:11" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B37" s="117"/>
@@ -14401,24 +14398,24 @@
     <row r="38" spans="2:11" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B38" s="241"/>
       <c r="C38" s="113"/>
-      <c r="D38" s="372" t="s">
+      <c r="D38" s="371" t="s">
         <v>9</v>
       </c>
-      <c r="E38" s="372"/>
-      <c r="F38" s="372"/>
-      <c r="G38" s="372"/>
-      <c r="H38" s="372"/>
-      <c r="I38" s="372"/>
-      <c r="J38" s="372"/>
+      <c r="E38" s="371"/>
+      <c r="F38" s="371"/>
+      <c r="G38" s="371"/>
+      <c r="H38" s="371"/>
+      <c r="I38" s="371"/>
+      <c r="J38" s="371"/>
     </row>
     <row r="39" spans="2:11" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D39" s="372"/>
-      <c r="E39" s="372"/>
-      <c r="F39" s="372"/>
-      <c r="G39" s="372"/>
-      <c r="H39" s="372"/>
-      <c r="I39" s="372"/>
-      <c r="J39" s="372"/>
+      <c r="D39" s="371"/>
+      <c r="E39" s="371"/>
+      <c r="F39" s="371"/>
+      <c r="G39" s="371"/>
+      <c r="H39" s="371"/>
+      <c r="I39" s="371"/>
+      <c r="J39" s="371"/>
     </row>
     <row r="40" spans="2:11" ht="14.4" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B40" s="117"/>
@@ -14436,15 +14433,15 @@
         <v>10</v>
       </c>
       <c r="C41" s="113"/>
-      <c r="D41" s="369" t="s">
+      <c r="D41" s="368" t="s">
         <v>11</v>
       </c>
-      <c r="E41" s="369"/>
-      <c r="F41" s="369"/>
-      <c r="G41" s="369"/>
-      <c r="H41" s="369"/>
-      <c r="I41" s="369"/>
-      <c r="J41" s="369"/>
+      <c r="E41" s="368"/>
+      <c r="F41" s="368"/>
+      <c r="G41" s="368"/>
+      <c r="H41" s="368"/>
+      <c r="I41" s="368"/>
+      <c r="J41" s="368"/>
     </row>
     <row r="42" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B42" s="113"/>
@@ -14458,30 +14455,30 @@
       <c r="J42" s="245"/>
     </row>
     <row r="43" spans="2:11" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="370" t="s">
+      <c r="B43" s="369" t="s">
         <v>12</v>
       </c>
       <c r="C43" s="103"/>
-      <c r="D43" s="371" t="s">
+      <c r="D43" s="370" t="s">
         <v>13</v>
       </c>
-      <c r="E43" s="371"/>
-      <c r="F43" s="371"/>
-      <c r="G43" s="371"/>
-      <c r="H43" s="371"/>
-      <c r="I43" s="371"/>
-      <c r="J43" s="371"/>
+      <c r="E43" s="370"/>
+      <c r="F43" s="370"/>
+      <c r="G43" s="370"/>
+      <c r="H43" s="370"/>
+      <c r="I43" s="370"/>
+      <c r="J43" s="370"/>
     </row>
     <row r="44" spans="2:11" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="B44" s="370"/>
+      <c r="B44" s="369"/>
       <c r="C44" s="103"/>
-      <c r="D44" s="371"/>
-      <c r="E44" s="371"/>
-      <c r="F44" s="371"/>
-      <c r="G44" s="371"/>
-      <c r="H44" s="371"/>
-      <c r="I44" s="371"/>
-      <c r="J44" s="371"/>
+      <c r="D44" s="370"/>
+      <c r="E44" s="370"/>
+      <c r="F44" s="370"/>
+      <c r="G44" s="370"/>
+      <c r="H44" s="370"/>
+      <c r="I44" s="370"/>
+      <c r="J44" s="370"/>
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.25">
       <c r="D45" s="112"/>
@@ -14493,17 +14490,17 @@
       <c r="J45" s="114"/>
     </row>
     <row r="46" spans="2:11" ht="58.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="371" t="s">
-        <v>584</v>
-      </c>
-      <c r="C46" s="371"/>
-      <c r="D46" s="371"/>
-      <c r="E46" s="371"/>
-      <c r="F46" s="371"/>
-      <c r="G46" s="371"/>
-      <c r="H46" s="371"/>
-      <c r="I46" s="371"/>
-      <c r="J46" s="371"/>
+      <c r="B46" s="370" t="s">
+        <v>583</v>
+      </c>
+      <c r="C46" s="370"/>
+      <c r="D46" s="370"/>
+      <c r="E46" s="370"/>
+      <c r="F46" s="370"/>
+      <c r="G46" s="370"/>
+      <c r="H46" s="370"/>
+      <c r="I46" s="370"/>
+      <c r="J46" s="370"/>
       <c r="K46" s="107"/>
     </row>
     <row r="47" spans="2:11" x14ac:dyDescent="0.25">
@@ -14538,17 +14535,17 @@
       <c r="J49" s="112"/>
     </row>
     <row r="50" spans="1:10" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="371" t="s">
+      <c r="B50" s="370" t="s">
         <v>15</v>
       </c>
-      <c r="C50" s="371"/>
-      <c r="D50" s="371"/>
-      <c r="E50" s="371"/>
-      <c r="F50" s="371"/>
-      <c r="G50" s="371"/>
-      <c r="H50" s="371"/>
-      <c r="I50" s="371"/>
-      <c r="J50" s="371"/>
+      <c r="C50" s="370"/>
+      <c r="D50" s="370"/>
+      <c r="E50" s="370"/>
+      <c r="F50" s="370"/>
+      <c r="G50" s="370"/>
+      <c r="H50" s="370"/>
+      <c r="I50" s="370"/>
+      <c r="J50" s="370"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="D51" s="114"/>
@@ -14669,7 +14666,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>21</v>
@@ -14822,7 +14819,7 @@
       <c r="B18" s="72" t="s">
         <v>155</v>
       </c>
-      <c r="C18" s="288">
+      <c r="C18" s="287">
         <f>0.0057*(ReichwPHEV4/23)^3-0.0838*(ReichwPHEV4/23)^2+0.4261*(ReichwPHEV4/23)+ 0.1633</f>
         <v>0.1633</v>
       </c>
@@ -14834,7 +14831,7 @@
       <c r="B19" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C19" s="289">
+      <c r="C19" s="288">
         <f>Verbrauch4/(1-0.9*C18)</f>
         <v>0</v>
       </c>
@@ -14848,7 +14845,7 @@
       <c r="B20" s="72" t="s">
         <v>157</v>
       </c>
-      <c r="C20" s="290">
+      <c r="C20" s="289">
         <f>VerbEl_WLTP4/C18</f>
         <v>97.366809552969997</v>
       </c>
@@ -14862,7 +14859,7 @@
       <c r="B21" s="186" t="s">
         <v>158</v>
       </c>
-      <c r="C21" s="291">
+      <c r="C21" s="290">
         <f>0.0021*(ReichwPHEV4/23)^3-0.0358*(ReichwPHEV4/23)^2+0.2607*(ReichwPHEV4/23)- 0.0267</f>
         <v>-2.6700000000000002E-2</v>
       </c>
@@ -14871,13 +14868,13 @@
       <c r="F21" s="125"/>
     </row>
     <row r="22" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="440" t="s">
+      <c r="A22" s="439" t="s">
         <v>12</v>
       </c>
-      <c r="B22" s="439" t="s">
+      <c r="B22" s="438" t="s">
         <v>159</v>
       </c>
-      <c r="C22" s="292">
+      <c r="C22" s="291">
         <f>C19*(1-0.9*C21)</f>
         <v>0</v>
       </c>
@@ -14888,9 +14885,9 @@
       <c r="F22" s="125"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="440"/>
-      <c r="B23" s="409"/>
-      <c r="C23" s="292">
+      <c r="A23" s="439"/>
+      <c r="B23" s="408"/>
+      <c r="C23" s="291">
         <f>C20*C21</f>
         <v>-2.599693815064299</v>
       </c>
@@ -14931,7 +14928,7 @@
       <c r="B28" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C28" s="279">
+      <c r="C28" s="278">
         <f>IF(Antriebsart4="Vollelektrisch (BEV)",0,IFERROR(VLOOKUP(Energie4,EnKostList,6,FALSE),0)*IF(Antriebsart4="Plug-In-Hybrid (PHEV)",VerbPHEV4,Verbrauch4)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
@@ -14945,7 +14942,7 @@
       <c r="B29" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C29" s="279">
+      <c r="C29" s="278">
         <f>IF(Antriebsart4="Verbrenner",0,VLOOKUP("Strom",EnKostList,6,FALSE)*IF(Antriebsart4="Plug-In-Hybrid (PHEV)",VerbElPHEV4,VerbEl_WLTP4)/100*Fahrleistung)</f>
         <v>1596.36</v>
       </c>
@@ -14959,7 +14956,7 @@
       <c r="B30" s="64" t="s">
         <v>101</v>
       </c>
-      <c r="C30" s="280">
+      <c r="C30" s="279">
         <f>SUM(C28:C29)</f>
         <v>1596.36</v>
       </c>
@@ -14991,7 +14988,7 @@
       <c r="B33" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="C33" s="279">
+      <c r="C33" s="278">
         <f>IF(Antriebsart4="Plug-In-Hybrid (PHEV)",VerbPHEV4*VLOOKUP(Energie4,CO2List,2,FALSE)/100,CO2_4)*Fahrleistung/1000000</f>
         <v>0</v>
       </c>
@@ -15005,7 +15002,7 @@
       <c r="B34" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C34" s="279">
+      <c r="C34" s="278">
         <f>C33*Kost_THG</f>
         <v>0</v>
       </c>
@@ -15019,7 +15016,7 @@
       <c r="B35" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="C35" s="287">
+      <c r="C35" s="286">
         <f>IF(Energie4="Strom",0,NOX_4*Fahrleistung*Kost_NOX/1000)</f>
         <v>0</v>
       </c>
@@ -15033,7 +15030,7 @@
       <c r="B36" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C36" s="287">
+      <c r="C36" s="286">
         <f>IF(Energie4="Strom",0,Partikel4*Fahrleistung*Kost_Partikel/1000)</f>
         <v>0</v>
       </c>
@@ -15047,7 +15044,7 @@
       <c r="B37" s="64" t="s">
         <v>101</v>
       </c>
-      <c r="C37" s="280">
+      <c r="C37" s="279">
         <f>SUM(C34:C36)</f>
         <v>0</v>
       </c>
@@ -15079,7 +15076,7 @@
       <c r="B40" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="C40" s="279">
+      <c r="C40" s="278">
         <f>IFERROR(IF(Antriebsart4="Vollelektrisch (BEV)",VLOOKUP("Strom",CO2List,3,FALSE)*VerbEl_WLTP4/100*Fahrleistung/1000000,IF(Antriebsart4="Verbrenner",VLOOKUP(Energie4,CO2List,3,FALSE)*Verbrauch4/100*Fahrleistung/1000000,VLOOKUP(Energie4,CO2List,3,FALSE)*VerbPHEV4/100*Fahrleistung/1000000+VLOOKUP("Strom",CO2List,3,FALSE)*VerbElPHEV4/100*Fahrleistung/1000000)),0)</f>
         <v>0.92537999999999998</v>
       </c>
@@ -15093,7 +15090,7 @@
       <c r="B41" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C41" s="279">
+      <c r="C41" s="278">
         <f>C40*Kost_THG</f>
         <v>795.82679999999993</v>
       </c>
@@ -15136,13 +15133,13 @@
       <c r="F45" s="125"/>
     </row>
     <row r="46" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A46" s="370" t="s">
+      <c r="A46" s="369" t="s">
         <v>12</v>
       </c>
-      <c r="B46" s="437" t="s">
+      <c r="B46" s="436" t="s">
         <v>164</v>
       </c>
-      <c r="C46" s="281">
+      <c r="C46" s="280">
         <f>IF(OR(Antriebsart4="Vollelektrisch (BEV)",Antriebsart4="Plug-In-Hybrid (PHEV)"),Batterie4*Batterie_THG/1000,0)</f>
         <v>5.0735999999999999</v>
       </c>
@@ -15153,9 +15150,9 @@
       <c r="F46" s="125"/>
     </row>
     <row r="47" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A47" s="370"/>
-      <c r="B47" s="438"/>
-      <c r="C47" s="281">
+      <c r="A47" s="369"/>
+      <c r="B47" s="437"/>
+      <c r="C47" s="280">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
         <v>23.061818181818182</v>
       </c>
@@ -15169,7 +15166,7 @@
       <c r="B48" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="C48" s="279">
+      <c r="C48" s="278">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Kost_THG, C46/Haltedauer*Kost_THG)</f>
         <v>396.66327272727273</v>
       </c>
@@ -15206,7 +15203,7 @@
       <c r="B54" s="68" t="s">
         <v>176</v>
       </c>
-      <c r="C54" s="282">
+      <c r="C54" s="281">
         <f>IF(FinArt="Kauf",IF(KaufpreisRech="Kaufpreis",Gesamtpreis4,0),Gesamtpreis4*Haltedauer*12+IF(FinArt="Leasing",LeasSondZahl4,0))</f>
         <v>0</v>
       </c>
@@ -15217,13 +15214,13 @@
       <c r="F54" s="58"/>
     </row>
     <row r="55" spans="1:6" s="71" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A55" s="305" t="s">
+      <c r="A55" s="304" t="s">
         <v>12</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="C55" s="283">
+        <v>474</v>
+      </c>
+      <c r="C55" s="282">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis4-Gesamtpreis4*(-0.2*LN(Haltedauer)+0.667),0)</f>
         <v>25269.14922308908</v>
       </c>
@@ -15237,7 +15234,7 @@
       <c r="B56" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C56" s="283">
+      <c r="C56" s="282">
         <f>C30*Haltedauer</f>
         <v>11174.519999999999</v>
       </c>
@@ -15250,7 +15247,7 @@
       <c r="B57" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C57" s="283">
+      <c r="C57" s="282">
         <f>C37*Haltedauer</f>
         <v>0</v>
       </c>
@@ -15263,7 +15260,7 @@
       <c r="B58" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C58" s="283">
+      <c r="C58" s="282">
         <f>C41*Haltedauer</f>
         <v>5570.7875999999997</v>
       </c>
@@ -15273,10 +15270,10 @@
       <c r="F58" s="58"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B59" s="333" t="s">
+      <c r="B59" s="332" t="s">
         <v>100</v>
       </c>
-      <c r="C59" s="334">
+      <c r="C59" s="333">
         <f>C48*Haltedauer</f>
         <v>2776.6429090909091</v>
       </c>
@@ -15286,50 +15283,50 @@
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="370" t="s">
+      <c r="A60" s="369" t="s">
         <v>12</v>
       </c>
-      <c r="B60" s="327" t="str">
+      <c r="B60" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", Zusatzangabe_x)</f>
         <v>Kfz-Steuer</v>
       </c>
-      <c r="C60" s="328">
+      <c r="C60" s="327">
         <f>IF(ISBLANK(Zusatzangabe_x), "", Zusatzangabe_x4*Haltedauer)</f>
         <v>0</v>
       </c>
-      <c r="D60" s="327" t="str">
+      <c r="D60" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", "EUR")</f>
         <v>EUR</v>
       </c>
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="370"/>
-      <c r="B61" s="327" t="str">
+      <c r="A61" s="369"/>
+      <c r="B61" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
       </c>
-      <c r="C61" s="328" t="str">
+      <c r="C61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y4*Haltedauer)</f>
         <v/>
       </c>
-      <c r="D61" s="327" t="str">
+      <c r="D61" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", "EUR")</f>
         <v/>
       </c>
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="370"/>
-      <c r="B62" s="327" t="str">
+      <c r="A62" s="369"/>
+      <c r="B62" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
       </c>
-      <c r="C62" s="328" t="str">
+      <c r="C62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z4*Haltedauer)</f>
         <v/>
       </c>
-      <c r="D62" s="327" t="str">
+      <c r="D62" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", "EUR")</f>
         <v/>
       </c>
@@ -15339,7 +15336,7 @@
       <c r="B63" s="64" t="s">
         <v>101</v>
       </c>
-      <c r="C63" s="284">
+      <c r="C63" s="283">
         <f>SUM(C54:C62)</f>
         <v>44791.09973217998</v>
       </c>
@@ -15361,7 +15358,7 @@
       <c r="B65" s="68" t="s">
         <v>178</v>
       </c>
-      <c r="C65" s="285">
+      <c r="C65" s="284">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Haltedauer, C46)</f>
         <v>3.2286545454545457</v>
       </c>
@@ -15373,7 +15370,7 @@
       <c r="B66" s="72" t="s">
         <v>106</v>
       </c>
-      <c r="C66" s="286">
+      <c r="C66" s="285">
         <f>C33*Haltedauer+C40*Haltedauer</f>
         <v>6.4776600000000002</v>
       </c>
@@ -15429,7 +15426,7 @@
     </row>
     <row r="2" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>21</v>
@@ -15585,7 +15582,7 @@
       <c r="B18" s="72" t="s">
         <v>155</v>
       </c>
-      <c r="C18" s="288">
+      <c r="C18" s="287">
         <f>0.0057*(ReichwPHEV5/23)^3-0.0838*(ReichwPHEV5/23)^2+0.4261*(ReichwPHEV5/23)+ 0.1633</f>
         <v>0.82686094353579342</v>
       </c>
@@ -15597,7 +15594,7 @@
       <c r="B19" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C19" s="289">
+      <c r="C19" s="288">
         <f>Verbrauch5/(1-0.9*C18)</f>
         <v>3.1271358482255263</v>
       </c>
@@ -15611,7 +15608,7 @@
       <c r="B20" s="72" t="s">
         <v>157</v>
       </c>
-      <c r="C20" s="290">
+      <c r="C20" s="289">
         <f>VerbEl_WLTP5/C18</f>
         <v>15.601172241655869</v>
       </c>
@@ -15625,7 +15622,7 @@
       <c r="B21" s="186" t="s">
         <v>158</v>
       </c>
-      <c r="C21" s="291">
+      <c r="C21" s="290">
         <f>0.0021*(ReichwPHEV5/23)^3-0.0358*(ReichwPHEV5/23)^2+0.2607*(ReichwPHEV5/23)- 0.0267</f>
         <v>0.47153432234733289</v>
       </c>
@@ -15634,13 +15631,13 @@
       <c r="F21" s="125"/>
     </row>
     <row r="22" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="440" t="s">
+      <c r="A22" s="439" t="s">
         <v>12</v>
       </c>
-      <c r="B22" s="439" t="s">
+      <c r="B22" s="438" t="s">
         <v>159</v>
       </c>
-      <c r="C22" s="292">
+      <c r="C22" s="291">
         <f>C19*(1-0.9*C21)</f>
         <v>1.8000391534525582</v>
       </c>
@@ -15651,9 +15648,9 @@
       <c r="F22" s="125"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="440"/>
-      <c r="B23" s="409"/>
-      <c r="C23" s="292">
+      <c r="A23" s="439"/>
+      <c r="B23" s="408"/>
+      <c r="C23" s="291">
         <f>C20*C21</f>
         <v>7.3564881807932201</v>
       </c>
@@ -15694,7 +15691,7 @@
       <c r="B28" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C28" s="279">
+      <c r="C28" s="278">
         <f>IF(Antriebsart5="Vollelektrisch (BEV)",0,IFERROR(VLOOKUP(Energie5,EnKostList,6,FALSE),0)*IF(Antriebsart5="Plug-In-Hybrid (PHEV)",VerbPHEV5,Verbrauch5)/100*Fahrleistung)</f>
         <v>643.69400127463473</v>
       </c>
@@ -15708,7 +15705,7 @@
       <c r="B29" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C29" s="279">
+      <c r="C29" s="278">
         <f>IF(Antriebsart5="Verbrenner",0,VLOOKUP("Strom",EnKostList,6,FALSE)*IF(Antriebsart5="Plug-In-Hybrid (PHEV)",VerbElPHEV5,VerbEl_WLTP5)/100*Fahrleistung)</f>
         <v>738.59141335163929</v>
       </c>
@@ -15722,7 +15719,7 @@
       <c r="B30" s="64" t="s">
         <v>101</v>
       </c>
-      <c r="C30" s="280">
+      <c r="C30" s="279">
         <f>SUM(C28:C29)</f>
         <v>1382.2854146262739</v>
       </c>
@@ -15755,7 +15752,7 @@
       <c r="B33" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="C33" s="279">
+      <c r="C33" s="278">
         <f>IF(Antriebsart5="Plug-In-Hybrid (PHEV)",VerbPHEV5*VLOOKUP(Energie5,CO2List,2,FALSE)/100,CO2_5)*Fahrleistung/1000000</f>
         <v>0.84661901795488459</v>
       </c>
@@ -15769,7 +15766,7 @@
       <c r="B34" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C34" s="279">
+      <c r="C34" s="278">
         <f>C33*Kost_THG</f>
         <v>728.09235544120077</v>
       </c>
@@ -15783,7 +15780,7 @@
       <c r="B35" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="C35" s="287">
+      <c r="C35" s="286">
         <f>IF(Energie5="Strom",0,NOX_5*Fahrleistung*Kost_NOX/1000)</f>
         <v>2.3199999999999998</v>
       </c>
@@ -15797,7 +15794,7 @@
       <c r="B36" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C36" s="287">
+      <c r="C36" s="286">
         <f>IF(Energie5="Strom",0,Partikel5*Fahrleistung*Kost_Partikel/1000)</f>
         <v>0.75</v>
       </c>
@@ -15811,7 +15808,7 @@
       <c r="B37" s="64" t="s">
         <v>101</v>
       </c>
-      <c r="C37" s="280">
+      <c r="C37" s="279">
         <f>SUM(C34:C36)</f>
         <v>731.16235544120082</v>
       </c>
@@ -15843,7 +15840,7 @@
       <c r="B40" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="C40" s="279">
+      <c r="C40" s="278">
         <f>IFERROR(IF(Antriebsart5="Vollelektrisch (BEV)",VLOOKUP("Strom",CO2List,3,FALSE)*VerbEl_WLTP5/100*Fahrleistung/1000000,IF(Antriebsart5="Verbrenner",VLOOKUP(Energie5,CO2List,3,FALSE)*Verbrauch5/100*Fahrleistung/1000000,VLOOKUP(Energie5,CO2List,3,FALSE)*VerbPHEV5/100*Fahrleistung/1000000+VLOOKUP("Strom",CO2List,3,FALSE)*VerbElPHEV5/100*Fahrleistung/1000000)),0)</f>
         <v>0.6979974646583782</v>
       </c>
@@ -15857,7 +15854,7 @@
       <c r="B41" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C41" s="279">
+      <c r="C41" s="278">
         <f>C40*Kost_THG</f>
         <v>600.2778196062053</v>
       </c>
@@ -15900,13 +15897,13 @@
       <c r="F45" s="125"/>
     </row>
     <row r="46" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A46" s="370" t="s">
+      <c r="A46" s="369" t="s">
         <v>12</v>
       </c>
-      <c r="B46" s="437" t="s">
+      <c r="B46" s="436" t="s">
         <v>164</v>
       </c>
-      <c r="C46" s="281">
+      <c r="C46" s="280">
         <f>IF(OR(Antriebsart5="Vollelektrisch (BEV)",Antriebsart5="Plug-In-Hybrid (PHEV)"),Batterie5*Batterie_THG/1000,0)</f>
         <v>1.008</v>
       </c>
@@ -15917,9 +15914,9 @@
       <c r="F46" s="125"/>
     </row>
     <row r="47" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A47" s="370"/>
-      <c r="B47" s="438"/>
-      <c r="C47" s="281">
+      <c r="A47" s="369"/>
+      <c r="B47" s="437"/>
+      <c r="C47" s="280">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
         <v>4.581818181818182</v>
       </c>
@@ -15933,7 +15930,7 @@
       <c r="B48" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="C48" s="279">
+      <c r="C48" s="278">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Kost_THG, C46/Haltedauer*Kost_THG)</f>
         <v>78.807272727272732</v>
       </c>
@@ -15970,7 +15967,7 @@
       <c r="B54" s="68" t="s">
         <v>176</v>
       </c>
-      <c r="C54" s="282">
+      <c r="C54" s="281">
         <f>IF(FinArt="Kauf",IF(KaufpreisRech="Kaufpreis",Gesamtpreis5,0),Gesamtpreis5*Haltedauer*12+IF(FinArt="Leasing",LeasSondZahl5,0))</f>
         <v>0</v>
       </c>
@@ -15981,13 +15978,13 @@
       <c r="F54" s="58"/>
     </row>
     <row r="55" spans="1:6" s="71" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A55" s="305" t="s">
+      <c r="A55" s="304" t="s">
         <v>12</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="C55" s="283">
+        <v>474</v>
+      </c>
+      <c r="C55" s="282">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis5-Gesamtpreis5*(-0.2*LN(Haltedauer)+0.667),0)</f>
         <v>27941.222733390012</v>
       </c>
@@ -16001,7 +15998,7 @@
       <c r="B56" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C56" s="283">
+      <c r="C56" s="282">
         <f>C30*Haltedauer</f>
         <v>9675.9979023839169</v>
       </c>
@@ -16014,7 +16011,7 @@
       <c r="B57" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C57" s="283">
+      <c r="C57" s="282">
         <f>C37*Haltedauer</f>
         <v>5118.1364880884057</v>
       </c>
@@ -16027,7 +16024,7 @@
       <c r="B58" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C58" s="283">
+      <c r="C58" s="282">
         <f>C41*Haltedauer</f>
         <v>4201.944737243437</v>
       </c>
@@ -16037,63 +16034,63 @@
       <c r="F58" s="58"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B59" s="329" t="s">
+      <c r="B59" s="328" t="s">
         <v>100</v>
       </c>
-      <c r="C59" s="330">
+      <c r="C59" s="329">
         <f>C48*Haltedauer</f>
         <v>551.65090909090918</v>
       </c>
-      <c r="D59" s="329" t="s">
+      <c r="D59" s="328" t="s">
         <v>75</v>
       </c>
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="370" t="s">
+      <c r="A60" s="369" t="s">
         <v>12</v>
       </c>
-      <c r="B60" s="327" t="str">
+      <c r="B60" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", Zusatzangabe_x)</f>
         <v>Kfz-Steuer</v>
       </c>
-      <c r="C60" s="328">
+      <c r="C60" s="327">
         <f>IF(ISBLANK(Zusatzangabe_x), "", Zusatzangabe_x5*Haltedauer)</f>
         <v>224</v>
       </c>
-      <c r="D60" s="327" t="str">
+      <c r="D60" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", "EUR")</f>
         <v>EUR</v>
       </c>
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="370"/>
-      <c r="B61" s="327" t="str">
+      <c r="A61" s="369"/>
+      <c r="B61" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
       </c>
-      <c r="C61" s="328" t="str">
+      <c r="C61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y5*Haltedauer)</f>
         <v/>
       </c>
-      <c r="D61" s="327" t="str">
+      <c r="D61" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", "EUR")</f>
         <v/>
       </c>
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="370"/>
-      <c r="B62" s="327" t="str">
+      <c r="A62" s="369"/>
+      <c r="B62" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
       </c>
-      <c r="C62" s="328" t="str">
+      <c r="C62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z5*Haltedauer)</f>
         <v/>
       </c>
-      <c r="D62" s="327" t="str">
+      <c r="D62" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", "EUR")</f>
         <v/>
       </c>
@@ -16103,7 +16100,7 @@
       <c r="B63" s="64" t="s">
         <v>101</v>
       </c>
-      <c r="C63" s="284">
+      <c r="C63" s="283">
         <f>SUM(C54:C62)</f>
         <v>47712.95277019668</v>
       </c>
@@ -16125,7 +16122,7 @@
       <c r="B65" s="68" t="s">
         <v>178</v>
       </c>
-      <c r="C65" s="285">
+      <c r="C65" s="284">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Haltedauer, C46)</f>
         <v>0.6414545454545455</v>
       </c>
@@ -16137,7 +16134,7 @@
       <c r="B66" s="72" t="s">
         <v>106</v>
       </c>
-      <c r="C66" s="286">
+      <c r="C66" s="285">
         <f>C33*Haltedauer+C40*Haltedauer</f>
         <v>10.812315378292841</v>
       </c>
@@ -16196,7 +16193,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B4" s="154" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5"/>
@@ -16218,7 +16215,7 @@
       <c r="B7" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C7" s="302">
+      <c r="C7" s="301">
         <v>74.027000000000001</v>
       </c>
       <c r="D7" s="10">
@@ -16232,7 +16229,7 @@
       <c r="B8" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C8" s="302">
+      <c r="C8" s="301">
         <v>72.787000000000006</v>
       </c>
       <c r="D8" s="10">
@@ -16246,7 +16243,7 @@
       <c r="B9" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="C9" s="302">
+      <c r="C9" s="301">
         <v>56.220999999999997</v>
       </c>
       <c r="D9" s="10">
@@ -16258,7 +16255,7 @@
     </row>
     <row r="10" spans="1:9" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="92" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C10" s="10"/>
       <c r="D10" s="10"/>
@@ -16288,15 +16285,15 @@
       <c r="B14" s="110" t="s">
         <v>51</v>
       </c>
-      <c r="C14" s="441" t="s">
+      <c r="C14" s="440" t="s">
         <v>185</v>
       </c>
-      <c r="D14" s="441"/>
-      <c r="E14" s="442" t="s">
+      <c r="D14" s="440"/>
+      <c r="E14" s="441" t="s">
         <v>186</v>
       </c>
-      <c r="F14" s="442"/>
-      <c r="G14" s="304"/>
+      <c r="F14" s="441"/>
+      <c r="G14" s="303"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="66"/>
@@ -16350,7 +16347,7 @@
       <c r="D17" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="E17" s="303">
+      <c r="E17" s="302">
         <v>46.5</v>
       </c>
       <c r="F17" s="111" t="s">
@@ -16360,14 +16357,14 @@
     </row>
     <row r="18" spans="1:37" ht="21.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="92" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D18" s="106"/>
       <c r="E18" s="10"/>
     </row>
     <row r="20" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B20" s="154" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="5"/>
@@ -16389,7 +16386,7 @@
       <c r="L21" s="135"/>
       <c r="M21" s="135"/>
       <c r="O21" s="137" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="P21" s="137"/>
       <c r="Q21" s="137"/>
@@ -16418,7 +16415,7 @@
       <c r="C23" s="58">
         <v>0</v>
       </c>
-      <c r="D23" s="299">
+      <c r="D23" s="298">
         <f>SUMIFS(J24:AE24, J23:AE23, "&gt;=" &amp; Anschaffungsjahr, J23:AE23,  "&lt;" &amp; Anschaffungsjahr + ROUND(Haltedauer, 0))/ROUND(Haltedauer, 0)</f>
         <v>290.99999999999994</v>
       </c>
@@ -16531,15 +16528,15 @@
         <v>192</v>
       </c>
       <c r="I24" s="58" t="s">
-        <v>492</v>
-      </c>
-      <c r="J24" s="300">
+        <v>491</v>
+      </c>
+      <c r="J24" s="299">
         <v>445</v>
       </c>
       <c r="K24" s="96">
         <v>408</v>
       </c>
-      <c r="L24" s="301">
+      <c r="L24" s="300">
         <v>371</v>
       </c>
       <c r="M24" s="96">
@@ -16554,7 +16551,7 @@
       <c r="P24" s="96">
         <v>211.8</v>
       </c>
-      <c r="Q24" s="301">
+      <c r="Q24" s="300">
         <v>172</v>
       </c>
       <c r="R24" s="96">
@@ -16569,7 +16566,7 @@
       <c r="U24" s="96">
         <v>119.2</v>
       </c>
-      <c r="V24" s="301">
+      <c r="V24" s="300">
         <v>106</v>
       </c>
       <c r="W24" s="96">
@@ -16584,7 +16581,7 @@
       <c r="Z24" s="96">
         <v>82</v>
       </c>
-      <c r="AA24" s="301">
+      <c r="AA24" s="300">
         <v>76</v>
       </c>
       <c r="AB24" s="136">
@@ -16614,7 +16611,7 @@
       <c r="AJ24" s="136">
         <v>79.599999999999994</v>
       </c>
-      <c r="AK24" s="301">
+      <c r="AK24" s="300">
         <v>80</v>
       </c>
     </row>
@@ -16710,12 +16707,12 @@
     </row>
     <row r="39" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="234" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="40" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="234" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="41" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -16731,12 +16728,12 @@
     </row>
     <row r="44" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="2" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="45" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="267" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="I45" s="106"/>
     </row>
@@ -16754,7 +16751,7 @@
         <v>439</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="51" spans="2:4" x14ac:dyDescent="0.25">
@@ -16762,7 +16759,7 @@
         <v>213</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="52" spans="2:4" x14ac:dyDescent="0.25">
@@ -16770,7 +16767,7 @@
         <v>214</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="53" spans="2:4" x14ac:dyDescent="0.25">
@@ -16778,7 +16775,7 @@
         <v>215</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.25">
@@ -16786,7 +16783,7 @@
         <v>33</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="55" spans="2:4" x14ac:dyDescent="0.25">
@@ -16794,7 +16791,7 @@
         <v>216</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="56" spans="2:4" x14ac:dyDescent="0.25">
@@ -16802,15 +16799,15 @@
         <v>217</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="57" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B57" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="58" spans="2:4" x14ac:dyDescent="0.25">
@@ -16818,7 +16815,7 @@
         <v>218</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="59" spans="2:4" x14ac:dyDescent="0.25">
@@ -16826,7 +16823,7 @@
         <v>219</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="60" spans="2:4" x14ac:dyDescent="0.25">
@@ -16834,7 +16831,7 @@
         <v>220</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="61" spans="2:4" x14ac:dyDescent="0.25">
@@ -17399,146 +17396,146 @@
     </row>
     <row r="131" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B131" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="D131" s="1" t="s">
         <v>529</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>530</v>
       </c>
     </row>
     <row r="132" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B132" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="D132" s="1" t="s">
         <v>531</v>
-      </c>
-      <c r="D132" s="1" t="s">
-        <v>532</v>
       </c>
     </row>
     <row r="133" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B133" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="D133" s="1" t="s">
         <v>533</v>
-      </c>
-      <c r="D133" s="1" t="s">
-        <v>534</v>
       </c>
     </row>
     <row r="134" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B134" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="D134" s="1" t="s">
         <v>535</v>
-      </c>
-      <c r="D134" s="1" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="135" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B135" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="D135" s="1" t="s">
         <v>537</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>538</v>
       </c>
     </row>
     <row r="136" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B136" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="D136" s="1" t="s">
         <v>539</v>
-      </c>
-      <c r="D136" s="1" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="137" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B137" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="D137" s="1" t="s">
         <v>541</v>
-      </c>
-      <c r="D137" s="1" t="s">
-        <v>542</v>
       </c>
     </row>
     <row r="138" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B138" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="D138" s="1" t="s">
         <v>543</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>544</v>
       </c>
     </row>
     <row r="139" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B139" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="D139" s="1" t="s">
         <v>545</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="140" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B140" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="D140" s="1" t="s">
         <v>547</v>
-      </c>
-      <c r="D140" s="1" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="141" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B141" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="D141" s="1" t="s">
         <v>549</v>
-      </c>
-      <c r="D141" s="1" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="142" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B142" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="D142" s="1" t="s">
         <v>551</v>
-      </c>
-      <c r="D142" s="1" t="s">
-        <v>552</v>
       </c>
     </row>
     <row r="143" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B143" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="D143" s="1" t="s">
         <v>553</v>
-      </c>
-      <c r="D143" s="1" t="s">
-        <v>554</v>
       </c>
     </row>
     <row r="144" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B144" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="D144" s="1" t="s">
         <v>555</v>
-      </c>
-      <c r="D144" s="1" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="145" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B145" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="D145" s="1" t="s">
         <v>557</v>
-      </c>
-      <c r="D145" s="1" t="s">
-        <v>558</v>
       </c>
     </row>
     <row r="146" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B146" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="D146" s="1" t="s">
         <v>559</v>
-      </c>
-      <c r="D146" s="1" t="s">
-        <v>560</v>
       </c>
     </row>
     <row r="147" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B147" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="D147" s="1" t="s">
         <v>561</v>
-      </c>
-      <c r="D147" s="1" t="s">
-        <v>562</v>
       </c>
     </row>
     <row r="148" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B148" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="D148" s="1" t="s">
         <v>563</v>
-      </c>
-      <c r="D148" s="1" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="149" spans="2:4" x14ac:dyDescent="0.25">
@@ -17586,7 +17583,7 @@
         <v>401</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="155" spans="2:4" x14ac:dyDescent="0.25">
@@ -17594,7 +17591,7 @@
         <v>371</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="156" spans="2:4" x14ac:dyDescent="0.25">
@@ -17602,7 +17599,7 @@
         <v>372</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="157" spans="2:4" x14ac:dyDescent="0.25">
@@ -17618,31 +17615,31 @@
         <v>375</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="159" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B159" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="D159" s="1" t="s">
         <v>568</v>
-      </c>
-      <c r="D159" s="1" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="160" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B160" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="D160" s="1" t="s">
         <v>570</v>
-      </c>
-      <c r="D160" s="1" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="161" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B161" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="D161" s="1" t="s">
         <v>572</v>
-      </c>
-      <c r="D161" s="1" t="s">
-        <v>573</v>
       </c>
     </row>
     <row r="162" spans="2:4" x14ac:dyDescent="0.25">
@@ -17706,7 +17703,7 @@
         <v>390</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="170" spans="2:4" x14ac:dyDescent="0.25">
@@ -17714,7 +17711,7 @@
         <v>201</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="171" spans="2:4" x14ac:dyDescent="0.25">
@@ -17722,7 +17719,7 @@
         <v>202</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="172" spans="2:4" x14ac:dyDescent="0.25">
@@ -17730,7 +17727,7 @@
         <v>203</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="173" spans="2:4" x14ac:dyDescent="0.25">
@@ -17738,7 +17735,7 @@
         <v>205</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="174" spans="2:4" x14ac:dyDescent="0.25">
@@ -17746,7 +17743,7 @@
         <v>206</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="175" spans="2:4" x14ac:dyDescent="0.25">
@@ -17754,7 +17751,7 @@
         <v>391</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="176" spans="2:4" x14ac:dyDescent="0.25">
@@ -17762,7 +17759,7 @@
         <v>392</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="177" spans="2:4" x14ac:dyDescent="0.25">
@@ -17770,7 +17767,7 @@
         <v>393</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="178" spans="2:4" x14ac:dyDescent="0.25">
@@ -17778,7 +17775,7 @@
         <v>394</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="179" spans="2:4" x14ac:dyDescent="0.25">
@@ -17786,7 +17783,7 @@
         <v>395</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="180" spans="2:4" x14ac:dyDescent="0.25">
@@ -17794,7 +17791,7 @@
         <v>396</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="181" spans="2:4" x14ac:dyDescent="0.25">
@@ -17802,7 +17799,7 @@
         <v>397</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="182" spans="2:4" x14ac:dyDescent="0.25">
@@ -17810,7 +17807,7 @@
         <v>398</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="183" spans="2:4" x14ac:dyDescent="0.25">
@@ -17818,7 +17815,7 @@
         <v>399</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
     </row>
     <row r="184" spans="2:4" x14ac:dyDescent="0.25">
@@ -17826,7 +17823,7 @@
         <v>400</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
     </row>
     <row r="185" spans="2:4" x14ac:dyDescent="0.25">
@@ -17834,7 +17831,7 @@
         <v>402</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="186" spans="2:4" x14ac:dyDescent="0.25">
@@ -17842,7 +17839,7 @@
         <v>403</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="187" spans="2:4" x14ac:dyDescent="0.25">
@@ -17850,7 +17847,7 @@
         <v>404</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="188" spans="2:4" x14ac:dyDescent="0.25">
@@ -17858,7 +17855,7 @@
         <v>405</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="189" spans="2:4" x14ac:dyDescent="0.25">
@@ -17874,7 +17871,7 @@
         <v>408</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="191" spans="2:4" x14ac:dyDescent="0.25">
@@ -18022,7 +18019,7 @@
         <v>202</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.25">
@@ -18152,164 +18149,164 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="275" t="s">
+    <row r="4" spans="2:5" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B4" s="274" t="s">
+        <v>483</v>
+      </c>
+      <c r="C4" s="274" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C5" s="275" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B6" s="274" t="s">
+        <v>447</v>
+      </c>
+      <c r="C6" s="274" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C7" s="275" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="274" t="s">
+        <v>478</v>
+      </c>
+      <c r="C8" s="269" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C9" s="275" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" s="274" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="276" t="s">
+        <v>417</v>
+      </c>
+      <c r="C10" s="269" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="269"/>
+      <c r="C11" s="275" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" s="274" customFormat="1" ht="22.8" x14ac:dyDescent="0.2">
+      <c r="B12" s="277" t="s">
+        <v>148</v>
+      </c>
+      <c r="C12" s="274" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C13" s="275" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B14" s="274" t="s">
+        <v>480</v>
+      </c>
+      <c r="C14" s="274" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C15" s="275" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B16" s="277" t="s">
+        <v>142</v>
+      </c>
+      <c r="C16" s="274" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" s="274" customFormat="1" ht="22.8" x14ac:dyDescent="0.2">
+      <c r="C17" s="275" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B18" s="274" t="s">
+        <v>486</v>
+      </c>
+      <c r="C18" s="274" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C19" s="275" t="s">
         <v>484</v>
       </c>
-      <c r="C4" s="275" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="5" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C5" s="276" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="6" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B6" s="275" t="s">
-        <v>448</v>
-      </c>
-      <c r="C6" s="275" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C7" s="276" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="275" t="s">
-        <v>479</v>
-      </c>
-      <c r="C8" s="270" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="9" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C9" s="276" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="10" spans="2:5" s="275" customFormat="1" ht="22.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="277" t="s">
-        <v>417</v>
-      </c>
-      <c r="C10" s="270" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="11" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="270"/>
-      <c r="C11" s="276" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="12" spans="2:5" s="275" customFormat="1" ht="22.8" x14ac:dyDescent="0.2">
-      <c r="B12" s="278" t="s">
-        <v>148</v>
-      </c>
-      <c r="C12" s="275" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="13" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C13" s="276" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="14" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="275" t="s">
-        <v>481</v>
-      </c>
-      <c r="C14" s="275" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="15" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C15" s="276" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="16" spans="2:5" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="278" t="s">
-        <v>142</v>
-      </c>
-      <c r="C16" s="275" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" s="275" customFormat="1" ht="22.8" x14ac:dyDescent="0.2">
-      <c r="C17" s="276" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="275" t="s">
-        <v>487</v>
-      </c>
-      <c r="C18" s="275" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C19" s="276" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="20" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="275" t="s">
+    </row>
+    <row r="20" spans="2:3" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="274" t="s">
         <v>424</v>
       </c>
-      <c r="C20" s="275" t="s">
+      <c r="C20" s="274" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="21" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C21" s="276" t="s">
+    <row r="21" spans="2:3" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C21" s="275" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="22" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="275" t="s">
+    <row r="22" spans="2:3" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="274" t="s">
+        <v>452</v>
+      </c>
+      <c r="C22" s="274" t="s">
         <v>453</v>
       </c>
-      <c r="C22" s="275" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="23" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C23" s="276" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="24" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="275" t="s">
+    </row>
+    <row r="23" spans="2:3" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C23" s="275" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="274" t="s">
         <v>442</v>
       </c>
-      <c r="C24" s="275" t="s">
+      <c r="C24" s="274" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="25" spans="2:3" s="275" customFormat="1" ht="22.8" x14ac:dyDescent="0.2">
-      <c r="C25" s="276" t="s">
+    <row r="25" spans="2:3" s="274" customFormat="1" ht="22.8" x14ac:dyDescent="0.2">
+      <c r="C25" s="275" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="26" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="275" t="s">
+    <row r="26" spans="2:3" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="274" t="s">
         <v>443</v>
       </c>
-      <c r="C26" s="275" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="27" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="C27" s="269" t="s">
+      <c r="C26" s="274" t="s">
         <v>444</v>
       </c>
     </row>
-    <row r="28" spans="2:3" s="275" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="27" spans="2:3" s="274" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="C27" s="275" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" s="274" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <hyperlinks>
@@ -18355,7 +18352,7 @@
   <sheetData>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="I2" s="106" t="s">
         <v>21</v>
@@ -18374,58 +18371,58 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B6" s="1" t="s">
-        <v>478</v>
-      </c>
-      <c r="C6" s="388" t="s">
-        <v>575</v>
-      </c>
-      <c r="D6" s="389"/>
-      <c r="E6" s="389"/>
-      <c r="F6" s="389"/>
-      <c r="G6" s="389"/>
-      <c r="H6" s="390"/>
+        <v>477</v>
+      </c>
+      <c r="C6" s="387" t="s">
+        <v>574</v>
+      </c>
+      <c r="D6" s="388"/>
+      <c r="E6" s="388"/>
+      <c r="F6" s="388"/>
+      <c r="G6" s="388"/>
+      <c r="H6" s="389"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C7" s="391"/>
-      <c r="D7" s="392"/>
-      <c r="E7" s="392"/>
-      <c r="F7" s="392"/>
-      <c r="G7" s="392"/>
-      <c r="H7" s="393"/>
+      <c r="C7" s="390"/>
+      <c r="D7" s="391"/>
+      <c r="E7" s="391"/>
+      <c r="F7" s="391"/>
+      <c r="G7" s="391"/>
+      <c r="H7" s="392"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="C8" s="394"/>
-      <c r="D8" s="395"/>
-      <c r="E8" s="395"/>
-      <c r="F8" s="395"/>
-      <c r="G8" s="395"/>
-      <c r="H8" s="396"/>
+      <c r="C8" s="393"/>
+      <c r="D8" s="394"/>
+      <c r="E8" s="394"/>
+      <c r="F8" s="394"/>
+      <c r="G8" s="394"/>
+      <c r="H8" s="395"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B9" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="397" t="s">
+      <c r="C9" s="396" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="398"/>
-      <c r="E9" s="398"/>
-      <c r="F9" s="398"/>
-      <c r="G9" s="398"/>
-      <c r="H9" s="399"/>
+      <c r="D9" s="397"/>
+      <c r="E9" s="397"/>
+      <c r="F9" s="397"/>
+      <c r="G9" s="397"/>
+      <c r="H9" s="398"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B10" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C10" s="397" t="s">
+      <c r="C10" s="396" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="398"/>
-      <c r="E10" s="398"/>
-      <c r="F10" s="398"/>
-      <c r="G10" s="398"/>
-      <c r="H10" s="399"/>
+      <c r="D10" s="397"/>
+      <c r="E10" s="397"/>
+      <c r="F10" s="397"/>
+      <c r="G10" s="397"/>
+      <c r="H10" s="398"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B11" s="1" t="s">
@@ -18455,10 +18452,10 @@
       <c r="B13" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="385" t="s">
+      <c r="C13" s="384" t="s">
         <v>29</v>
       </c>
-      <c r="D13" s="386"/>
+      <c r="D13" s="385"/>
       <c r="E13" s="55"/>
       <c r="F13" s="55"/>
       <c r="G13" s="55"/>
@@ -18474,7 +18471,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B15" s="1" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C15" s="152">
         <v>20000</v>
@@ -18517,7 +18514,7 @@
       <c r="H18" s="55"/>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B19" s="298" t="s">
+      <c r="B19" s="297" t="s">
         <v>439</v>
       </c>
       <c r="C19" s="151">
@@ -18530,7 +18527,7 @@
       <c r="H19" s="55"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B20" s="297"/>
+      <c r="B20" s="296"/>
       <c r="C20" s="55"/>
       <c r="D20" s="55"/>
       <c r="E20" s="55"/>
@@ -18557,16 +18554,16 @@
       <c r="A23" s="97" t="s">
         <v>12</v>
       </c>
-      <c r="B23" s="387" t="s">
+      <c r="B23" s="386" t="s">
         <v>35</v>
       </c>
-      <c r="C23" s="384" t="s">
+      <c r="C23" s="383" t="s">
         <v>36</v>
       </c>
-      <c r="D23" s="384"/>
+      <c r="D23" s="383"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="B24" s="387"/>
+      <c r="B24" s="386"/>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B25" s="176"/>
@@ -18587,7 +18584,7 @@
       <c r="E26" s="1" t="s">
         <v>438</v>
       </c>
-      <c r="F26" s="274">
+      <c r="F26" s="273">
         <f>Grunddaten!E38</f>
         <v>0</v>
       </c>
@@ -18597,7 +18594,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B28" s="154" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
@@ -18973,17 +18970,17 @@
         <v>62</v>
       </c>
       <c r="H10" s="140" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="I10" s="140" t="s">
         <v>64</v>
       </c>
       <c r="J10" s="238"/>
       <c r="K10" s="236"/>
-      <c r="L10" s="411" t="s">
+      <c r="L10" s="410" t="s">
         <v>435</v>
       </c>
-      <c r="M10" s="411"/>
+      <c r="M10" s="410"/>
       <c r="N10" s="236"/>
       <c r="O10" s="164"/>
       <c r="P10" s="164"/>
@@ -19005,18 +19002,18 @@
         <v>66</v>
       </c>
       <c r="H11" s="141" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="I11" s="141" t="s">
         <v>69</v>
       </c>
       <c r="J11" s="238"/>
-      <c r="K11" s="413" t="s">
+      <c r="K11" s="412" t="s">
         <v>70</v>
       </c>
-      <c r="L11" s="413"/>
-      <c r="M11" s="413"/>
-      <c r="N11" s="413"/>
+      <c r="L11" s="412"/>
+      <c r="M11" s="412"/>
+      <c r="N11" s="412"/>
       <c r="O11" s="164"/>
       <c r="P11" s="164"/>
       <c r="Q11" s="164"/>
@@ -19028,27 +19025,27 @@
       </c>
       <c r="D12" s="88"/>
       <c r="E12" s="141" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="F12" s="141" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="G12" s="141" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H12" s="141" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="I12" s="141" t="s">
         <v>72</v>
       </c>
       <c r="J12" s="164"/>
-      <c r="K12" s="412" t="s">
+      <c r="K12" s="411" t="s">
         <v>73</v>
       </c>
-      <c r="L12" s="412"/>
-      <c r="M12" s="412"/>
-      <c r="N12" s="412"/>
+      <c r="L12" s="411"/>
+      <c r="M12" s="411"/>
+      <c r="N12" s="411"/>
       <c r="O12" s="164"/>
       <c r="P12" s="164"/>
       <c r="Q12" s="164"/>
@@ -19095,11 +19092,11 @@
       <c r="D14" s="263" t="s">
         <v>75</v>
       </c>
-      <c r="E14" s="362"/>
-      <c r="F14" s="365"/>
-      <c r="G14" s="362"/>
-      <c r="H14" s="362"/>
-      <c r="I14" s="362"/>
+      <c r="E14" s="361"/>
+      <c r="F14" s="364"/>
+      <c r="G14" s="361"/>
+      <c r="H14" s="361"/>
+      <c r="I14" s="361"/>
       <c r="J14" s="264" t="s">
         <v>76</v>
       </c>
@@ -19113,27 +19110,27 @@
       <c r="R14" s="164"/>
     </row>
     <row r="15" spans="2:18" s="91" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="410" t="s">
+      <c r="B15" s="409" t="s">
         <v>77</v>
       </c>
-      <c r="C15" s="408" t="s">
+      <c r="C15" s="407" t="s">
         <v>78</v>
       </c>
-      <c r="D15" s="360" t="s">
+      <c r="D15" s="359" t="s">
         <v>79</v>
       </c>
-      <c r="E15" s="366">
+      <c r="E15" s="365">
         <v>5</v>
       </c>
       <c r="F15" s="257">
         <v>4.3</v>
       </c>
-      <c r="G15" s="364"/>
-      <c r="H15" s="364"/>
-      <c r="I15" s="363">
+      <c r="G15" s="363"/>
+      <c r="H15" s="363"/>
+      <c r="I15" s="362">
         <v>0.8</v>
       </c>
-      <c r="J15" s="361"/>
+      <c r="J15" s="360"/>
       <c r="K15" s="236"/>
       <c r="L15" s="236"/>
       <c r="M15" s="237"/>
@@ -19143,12 +19140,12 @@
       <c r="R15" s="164"/>
     </row>
     <row r="16" spans="2:18" s="91" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="410"/>
-      <c r="C16" s="409"/>
+      <c r="B16" s="409"/>
+      <c r="C16" s="408"/>
       <c r="D16" s="166" t="s">
         <v>80</v>
       </c>
-      <c r="E16" s="358"/>
+      <c r="E16" s="357"/>
       <c r="F16" s="257"/>
       <c r="G16" s="257">
         <v>15.5</v>
@@ -19156,7 +19153,7 @@
       <c r="H16" s="257">
         <v>15.9</v>
       </c>
-      <c r="I16" s="359">
+      <c r="I16" s="358">
         <v>12.9</v>
       </c>
       <c r="J16" s="164"/>
@@ -19170,7 +19167,7 @@
       <c r="R16" s="164"/>
     </row>
     <row r="17" spans="2:18" s="91" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="410"/>
+      <c r="B17" s="409"/>
       <c r="C17" s="162" t="s">
         <v>81</v>
       </c>
@@ -19199,7 +19196,7 @@
       <c r="R17" s="164"/>
     </row>
     <row r="18" spans="2:18" s="91" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="410"/>
+      <c r="B18" s="409"/>
       <c r="C18" s="162" t="s">
         <v>83</v>
       </c>
@@ -19231,7 +19228,7 @@
       <c r="R18" s="164"/>
     </row>
     <row r="19" spans="2:18" s="91" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="410"/>
+      <c r="B19" s="409"/>
       <c r="C19" s="162" t="s">
         <v>85</v>
       </c>
@@ -19260,7 +19257,7 @@
       <c r="R19" s="164"/>
     </row>
     <row r="20" spans="2:18" s="91" customFormat="1" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="410"/>
+      <c r="B20" s="409"/>
       <c r="C20" s="162" t="s">
         <v>86</v>
       </c>
@@ -19316,23 +19313,23 @@
       <c r="D22" s="228" t="s">
         <v>90</v>
       </c>
-      <c r="E22" s="368">
+      <c r="E22" s="367">
         <f>IF(AND(OR(Energie1="nicht verfügbar",COUNTIF(EnList1,Energie1)&lt;&gt;1),Antriebsart1&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="F22" s="368">
+      <c r="F22" s="367">
         <f>IF(AND(OR(Energie2="nicht verfügbar",COUNTIF(EnList2,Energie2)&lt;&gt;1),Antriebsart2&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="G22" s="368">
+      <c r="G22" s="367">
         <f>IF(AND(OR(Energie3="nicht verfügbar",COUNTIF(EnList3,Energie3)&lt;&gt;1),Antriebsart3&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="H22" s="368">
+      <c r="H22" s="367">
         <f>IF(AND(OR(Energie4="nicht verfügbar",COUNTIF(EnList4,Energie4)&lt;&gt;1),Antriebsart4&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
-      <c r="I22" s="368">
+      <c r="I22" s="367">
         <f>IF(AND(OR(Energie5="nicht verfügbar",COUNTIF(EnList5,Energie5)&lt;&gt;1),Antriebsart5&lt;&gt;0),1,0)</f>
         <v>0</v>
       </c>
@@ -19347,14 +19344,14 @@
     </row>
     <row r="23" spans="2:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C23" s="77" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D23" s="228"/>
-      <c r="E23" s="368"/>
-      <c r="F23" s="368"/>
-      <c r="G23" s="368"/>
-      <c r="H23" s="368"/>
-      <c r="I23" s="368"/>
+      <c r="E23" s="367"/>
+      <c r="F23" s="367"/>
+      <c r="G23" s="367"/>
+      <c r="H23" s="367"/>
+      <c r="I23" s="367"/>
       <c r="J23" s="146"/>
       <c r="O23" s="7"/>
       <c r="P23" s="7"/>
@@ -19362,13 +19359,13 @@
       <c r="R23" s="7"/>
     </row>
     <row r="24" spans="2:18" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="370" t="s">
+      <c r="B24" s="369" t="s">
         <v>12</v>
       </c>
-      <c r="C24" s="331" t="s">
-        <v>489</v>
-      </c>
-      <c r="D24" s="322" t="s">
+      <c r="C24" s="330" t="s">
+        <v>488</v>
+      </c>
+      <c r="D24" s="321" t="s">
         <v>162</v>
       </c>
       <c r="E24" s="256">
@@ -19393,9 +19390,9 @@
       <c r="R24" s="7"/>
     </row>
     <row r="25" spans="2:18" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="370"/>
-      <c r="C25" s="331"/>
-      <c r="D25" s="322" t="s">
+      <c r="B25" s="369"/>
+      <c r="C25" s="330"/>
+      <c r="D25" s="321" t="s">
         <v>162</v>
       </c>
       <c r="E25" s="256"/>
@@ -19410,9 +19407,9 @@
       <c r="R25" s="7"/>
     </row>
     <row r="26" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="B26" s="370"/>
-      <c r="C26" s="335"/>
-      <c r="D26" s="322" t="s">
+      <c r="B26" s="369"/>
+      <c r="C26" s="334"/>
+      <c r="D26" s="321" t="s">
         <v>162</v>
       </c>
       <c r="E26" s="256"/>
@@ -19430,23 +19427,23 @@
       <c r="D27" s="228" t="s">
         <v>91</v>
       </c>
-      <c r="E27" s="368">
+      <c r="E27" s="367">
         <f>IF(OR(AND(COUNT(E15:E21)&lt;7,Antriebsart1="Plug-In-Hybrid (PHEV)"),AND(COUNT(E16,E21)&lt;2,Antriebsart1="Vollelektrisch (BEV)"),AND(COUNT(E15,E17:E19)&lt;4,Antriebsart1="Verbrenner")),1,0)</f>
         <v>0</v>
       </c>
-      <c r="F27" s="368">
+      <c r="F27" s="367">
         <f>IF(OR(AND(COUNT(F15:F21)&lt;7,Antriebsart2="Plug-In-Hybrid (PHEV)"),AND(COUNT(F16,F21)&lt;2,Antriebsart2="Vollelektrisch (BEV)"),AND(COUNT(F15,F17:F19)&lt;4,Antriebsart2="Verbrenner")),1,0)</f>
         <v>0</v>
       </c>
-      <c r="G27" s="368">
+      <c r="G27" s="367">
         <f>IF(OR(AND(COUNT(G15:G21)&lt;7,Antriebsart3="Plug-In-Hybrid (PHEV)"),AND(COUNT(G16,G21)&lt;2,Antriebsart3="Vollelektrisch (BEV)"),AND(COUNT(G15,G17:G19)&lt;4,Antriebsart3="Verbrenner")),1,0)</f>
         <v>0</v>
       </c>
-      <c r="H27" s="368">
+      <c r="H27" s="367">
         <f>IF(OR(AND(COUNT(H15:H21)&lt;7,Antriebsart4="Plug-In-Hybrid (PHEV)"),AND(COUNT(H16,H21)&lt;2,Antriebsart4="Vollelektrisch (BEV)"),AND(COUNT(H15,H17:H19)&lt;4,Antriebsart4="Verbrenner")),1,0)</f>
         <v>0</v>
       </c>
-      <c r="I27" s="368">
+      <c r="I27" s="367">
         <f>IF(OR(AND(COUNT(I15:I21)&lt;7,Antriebsart5="Plug-In-Hybrid (PHEV)"),AND(COUNT(I16,I21)&lt;2,Antriebsart5="Vollelektrisch (BEV)"),AND(COUNT(I15,I17:I19)&lt;4,Antriebsart5="Verbrenner")),1,0)</f>
         <v>0</v>
       </c>
@@ -19460,33 +19457,33 @@
       <c r="R27" s="7"/>
     </row>
     <row r="28" spans="2:18" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E28" s="405" t="s">
+      <c r="E28" s="404" t="s">
         <v>92</v>
       </c>
-      <c r="F28" s="406"/>
-      <c r="G28" s="406"/>
-      <c r="H28" s="406"/>
-      <c r="I28" s="407"/>
+      <c r="F28" s="405"/>
+      <c r="G28" s="405"/>
+      <c r="H28" s="405"/>
+      <c r="I28" s="406"/>
     </row>
     <row r="29" spans="2:18" ht="13.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E29" s="400" t="s">
+      <c r="E29" s="399" t="s">
         <v>93</v>
       </c>
-      <c r="F29" s="387"/>
-      <c r="G29" s="387"/>
-      <c r="H29" s="387"/>
-      <c r="I29" s="401"/>
+      <c r="F29" s="386"/>
+      <c r="G29" s="386"/>
+      <c r="H29" s="386"/>
+      <c r="I29" s="400"/>
     </row>
     <row r="30" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="E30" s="402"/>
-      <c r="F30" s="403"/>
-      <c r="G30" s="403"/>
-      <c r="H30" s="403"/>
-      <c r="I30" s="404"/>
+      <c r="E30" s="401"/>
+      <c r="F30" s="402"/>
+      <c r="G30" s="402"/>
+      <c r="H30" s="402"/>
+      <c r="I30" s="403"/>
     </row>
     <row r="32" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C32" s="1" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
   </sheetData>
@@ -19870,7 +19867,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B1" s="118" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C1" s="118"/>
       <c r="D1" s="118"/>
@@ -19884,7 +19881,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="65" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C2" s="227"/>
       <c r="D2" s="230" t="str">
@@ -19927,37 +19924,37 @@
     <row r="6" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="18"/>
       <c r="B6" s="12" t="s">
-        <v>478</v>
-      </c>
-      <c r="C6" s="418" t="str">
+        <v>477</v>
+      </c>
+      <c r="C6" s="417" t="str">
         <f>IF(Projektname=0,"",Projektname)</f>
         <v>Los 1 - Kauf von einem Kompaktklasse-Pkw</v>
       </c>
-      <c r="D6" s="419"/>
-      <c r="E6" s="419"/>
-      <c r="F6" s="419"/>
-      <c r="G6" s="419"/>
-      <c r="H6" s="420"/>
+      <c r="D6" s="418"/>
+      <c r="E6" s="418"/>
+      <c r="F6" s="418"/>
+      <c r="G6" s="418"/>
+      <c r="H6" s="419"/>
     </row>
     <row r="7" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="18"/>
       <c r="B7" s="12"/>
-      <c r="C7" s="421"/>
-      <c r="D7" s="422"/>
-      <c r="E7" s="422"/>
-      <c r="F7" s="422"/>
-      <c r="G7" s="422"/>
-      <c r="H7" s="423"/>
+      <c r="C7" s="420"/>
+      <c r="D7" s="421"/>
+      <c r="E7" s="421"/>
+      <c r="F7" s="421"/>
+      <c r="G7" s="421"/>
+      <c r="H7" s="422"/>
     </row>
     <row r="8" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="18"/>
       <c r="B8" s="12"/>
-      <c r="C8" s="424"/>
-      <c r="D8" s="425"/>
-      <c r="E8" s="425"/>
-      <c r="F8" s="425"/>
-      <c r="G8" s="425"/>
-      <c r="H8" s="426"/>
+      <c r="C8" s="423"/>
+      <c r="D8" s="424"/>
+      <c r="E8" s="424"/>
+      <c r="F8" s="424"/>
+      <c r="G8" s="424"/>
+      <c r="H8" s="425"/>
     </row>
     <row r="9" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="18"/>
@@ -19994,11 +19991,11 @@
       <c r="B11" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="414">
+      <c r="C11" s="413">
         <f>IF(Datum=0,"",Datum)</f>
         <v>45588</v>
       </c>
-      <c r="D11" s="415"/>
+      <c r="D11" s="414"/>
       <c r="E11" s="79"/>
       <c r="F11" s="81"/>
       <c r="G11" s="81"/>
@@ -20009,7 +20006,7 @@
       <c r="B12" s="12"/>
       <c r="C12" s="76"/>
       <c r="E12" s="58" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F12" s="85">
         <f>Fahrleistung</f>
@@ -20048,7 +20045,7 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="18"/>
-      <c r="B15" s="293" t="s">
+      <c r="B15" s="292" t="s">
         <v>95</v>
       </c>
       <c r="C15" s="21"/>
@@ -20136,10 +20133,10 @@
       <c r="I18" s="107"/>
     </row>
     <row r="19" spans="1:9" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A19" s="321" t="s">
+      <c r="A19" s="320" t="s">
         <v>12</v>
       </c>
-      <c r="B19" s="338" t="str">
+      <c r="B19" s="337" t="str">
         <f>IF(FinArt="Kauf",KaufpreisRech,"Fahrzeugkosten (Leasingrate/Miete)")</f>
         <v>Wertminderung</v>
       </c>
@@ -20162,13 +20159,13 @@
         <f>Erg.Fzg._4!$C$54+Erg.Fzg._4!$C$55</f>
         <v>25269.14922308908</v>
       </c>
-      <c r="H19" s="337">
+      <c r="H19" s="336">
         <f>Erg.Fzg._5!$C$54+Erg.Fzg._5!$C$55</f>
         <v>27941.222733390012</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="336"/>
+      <c r="A20" s="335"/>
       <c r="B20" s="45" t="s">
         <v>97</v>
       </c>
@@ -20197,7 +20194,7 @@
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="416" t="s">
+      <c r="A21" s="415" t="s">
         <v>12</v>
       </c>
       <c r="B21" s="27" t="s">
@@ -20228,7 +20225,7 @@
       </c>
     </row>
     <row r="22" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="416"/>
+      <c r="A22" s="415"/>
       <c r="B22" s="27" t="s">
         <v>99</v>
       </c>
@@ -20258,26 +20255,26 @@
       <c r="I22" s="107"/>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A23" s="417"/>
+      <c r="A23" s="416"/>
       <c r="B23" s="45" t="s">
         <v>100</v>
       </c>
-      <c r="C23" s="325" t="s">
+      <c r="C23" s="324" t="s">
         <v>75</v>
       </c>
-      <c r="D23" s="326">
+      <c r="D23" s="325">
         <f>Erg.Fzg._1!$C$59</f>
         <v>0</v>
       </c>
-      <c r="E23" s="326">
+      <c r="E23" s="325">
         <f>Erg.Fzg._2!$C$59</f>
         <v>0</v>
       </c>
-      <c r="F23" s="326">
+      <c r="F23" s="325">
         <f>Erg.Fzg._3!$C$59</f>
         <v>2850.1963636363635</v>
       </c>
-      <c r="G23" s="326">
+      <c r="G23" s="325">
         <f>Erg.Fzg._4!$C$59</f>
         <v>2776.6429090909091</v>
       </c>
@@ -20287,30 +20284,30 @@
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24" s="416" t="s">
+      <c r="A24" s="415" t="s">
         <v>12</v>
       </c>
-      <c r="B24" s="332" t="str">
+      <c r="B24" s="331" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", Zusatzangabe_x)</f>
         <v>Kfz-Steuer</v>
       </c>
-      <c r="C24" s="323" t="str">
+      <c r="C24" s="322" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", "EUR")</f>
         <v>EUR</v>
       </c>
-      <c r="D24" s="324">
+      <c r="D24" s="323">
         <f>Erg.Fzg._1!$C$60</f>
         <v>1533</v>
       </c>
-      <c r="E24" s="324">
+      <c r="E24" s="323">
         <f>Erg.Fzg._2!$C$60</f>
         <v>1596</v>
       </c>
-      <c r="F24" s="324">
+      <c r="F24" s="323">
         <f>Erg.Fzg._3!$C$60</f>
         <v>0</v>
       </c>
-      <c r="G24" s="324">
+      <c r="G24" s="323">
         <f>Erg.Fzg._4!$C$60</f>
         <v>0</v>
       </c>
@@ -20320,28 +20317,28 @@
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="416"/>
-      <c r="B25" s="332" t="str">
+      <c r="A25" s="415"/>
+      <c r="B25" s="331" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
       </c>
-      <c r="C25" s="323" t="str">
+      <c r="C25" s="322" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", "EUR")</f>
         <v/>
       </c>
-      <c r="D25" s="324" t="str">
+      <c r="D25" s="323" t="str">
         <f>Erg.Fzg._1!$C$61</f>
         <v/>
       </c>
-      <c r="E25" s="324" t="str">
+      <c r="E25" s="323" t="str">
         <f>Erg.Fzg._2!$C$61</f>
         <v/>
       </c>
-      <c r="F25" s="324" t="str">
+      <c r="F25" s="323" t="str">
         <f>Erg.Fzg._3!$C$61</f>
         <v/>
       </c>
-      <c r="G25" s="324" t="str">
+      <c r="G25" s="323" t="str">
         <f>Erg.Fzg._4!$C$61</f>
         <v/>
       </c>
@@ -20352,28 +20349,28 @@
       <c r="I25" s="6"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="416"/>
-      <c r="B26" s="332" t="str">
+      <c r="A26" s="415"/>
+      <c r="B26" s="331" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
       </c>
-      <c r="C26" s="323" t="str">
+      <c r="C26" s="322" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", "EUR")</f>
         <v/>
       </c>
-      <c r="D26" s="324" t="str">
+      <c r="D26" s="323" t="str">
         <f>Erg.Fzg._1!$C$62</f>
         <v/>
       </c>
-      <c r="E26" s="324" t="str">
+      <c r="E26" s="323" t="str">
         <f>Erg.Fzg._2!$C$62</f>
         <v/>
       </c>
-      <c r="F26" s="324" t="str">
+      <c r="F26" s="323" t="str">
         <f>Erg.Fzg._3!$C$62</f>
         <v/>
       </c>
-      <c r="G26" s="324" t="str">
+      <c r="G26" s="323" t="str">
         <f>Erg.Fzg._4!$C$62</f>
         <v/>
       </c>
@@ -20477,92 +20474,92 @@
       <c r="B30" s="34" t="s">
         <v>104</v>
       </c>
-      <c r="C30" s="316" t="s">
+      <c r="C30" s="315" t="s">
         <v>105</v>
       </c>
-      <c r="D30" s="314">
+      <c r="D30" s="313">
         <f>Erg.Fzg._1!$C$65</f>
         <v>0</v>
       </c>
-      <c r="E30" s="314">
+      <c r="E30" s="313">
         <f>Erg.Fzg._2!$C$65</f>
         <v>0</v>
       </c>
-      <c r="F30" s="314">
+      <c r="F30" s="313">
         <f>Erg.Fzg._3!$C$65</f>
         <v>3.3141818181818179</v>
       </c>
-      <c r="G30" s="314">
+      <c r="G30" s="313">
         <f>Erg.Fzg._4!$C$65</f>
         <v>3.2286545454545457</v>
       </c>
-      <c r="H30" s="315">
+      <c r="H30" s="314">
         <f>Erg.Fzg._5!$C$65</f>
         <v>0.6414545454545455</v>
       </c>
     </row>
     <row r="31" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="309"/>
+      <c r="A31" s="308"/>
       <c r="B31" s="98" t="s">
-        <v>490</v>
-      </c>
-      <c r="C31" s="317" t="s">
+        <v>489</v>
+      </c>
+      <c r="C31" s="316" t="s">
         <v>105</v>
       </c>
-      <c r="D31" s="318">
+      <c r="D31" s="317">
         <f>Erg.Fzg._1!$C$66</f>
         <v>24.3022225152</v>
       </c>
-      <c r="E31" s="318">
+      <c r="E31" s="317">
         <f>Erg.Fzg._2!$C$66</f>
         <v>20.967111363072</v>
       </c>
-      <c r="F31" s="318">
+      <c r="F31" s="317">
         <f>Erg.Fzg._3!$C$66</f>
         <v>6.3146999999999984</v>
       </c>
-      <c r="G31" s="318">
+      <c r="G31" s="317">
         <f>Erg.Fzg._4!$C$66</f>
         <v>6.4776600000000002</v>
       </c>
-      <c r="H31" s="319">
+      <c r="H31" s="318">
         <f>Erg.Fzg._5!$C$66</f>
         <v>10.812315378292841</v>
       </c>
       <c r="I31" s="91"/>
     </row>
     <row r="32" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="309"/>
-      <c r="B32" s="310" t="s">
-        <v>477</v>
-      </c>
-      <c r="C32" s="311" t="s">
+      <c r="A32" s="308"/>
+      <c r="B32" s="309" t="s">
         <v>476</v>
       </c>
-      <c r="D32" s="312">
+      <c r="C32" s="310" t="s">
+        <v>475</v>
+      </c>
+      <c r="D32" s="311">
         <f>SUM(D30:D31)</f>
         <v>24.3022225152</v>
       </c>
-      <c r="E32" s="312">
+      <c r="E32" s="311">
         <f t="shared" ref="E32:H32" si="2">SUM(E30:E31)</f>
         <v>20.967111363072</v>
       </c>
-      <c r="F32" s="312">
+      <c r="F32" s="311">
         <f t="shared" si="2"/>
         <v>9.6288818181818172</v>
       </c>
-      <c r="G32" s="312">
+      <c r="G32" s="311">
         <f t="shared" si="2"/>
         <v>9.7063145454545463</v>
       </c>
-      <c r="H32" s="313">
+      <c r="H32" s="312">
         <f t="shared" si="2"/>
         <v>11.453769923747386</v>
       </c>
       <c r="I32" s="91"/>
     </row>
     <row r="34" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B34" s="293" t="s">
+      <c r="B34" s="292" t="s">
         <v>109</v>
       </c>
       <c r="C34" s="21"/>
@@ -20694,7 +20691,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B1" s="118" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C1" s="118"/>
       <c r="D1" s="118"/>
@@ -20704,11 +20701,11 @@
       <c r="H1" s="119"/>
     </row>
     <row r="2" spans="1:10" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A2" s="320" t="s">
+      <c r="A2" s="319" t="s">
         <v>12</v>
       </c>
       <c r="B2" s="65" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C2" s="227"/>
       <c r="D2" s="230" t="str">
@@ -20751,37 +20748,37 @@
     <row r="6" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="18"/>
       <c r="B6" s="12" t="s">
-        <v>478</v>
-      </c>
-      <c r="C6" s="418" t="str">
+        <v>477</v>
+      </c>
+      <c r="C6" s="417" t="str">
         <f>IF(Projektname=0,"",Projektname)</f>
         <v>Los 1 - Kauf von einem Kompaktklasse-Pkw</v>
       </c>
-      <c r="D6" s="419"/>
-      <c r="E6" s="419"/>
-      <c r="F6" s="419"/>
-      <c r="G6" s="419"/>
-      <c r="H6" s="420"/>
+      <c r="D6" s="418"/>
+      <c r="E6" s="418"/>
+      <c r="F6" s="418"/>
+      <c r="G6" s="418"/>
+      <c r="H6" s="419"/>
     </row>
     <row r="7" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="18"/>
       <c r="B7" s="12"/>
-      <c r="C7" s="421"/>
-      <c r="D7" s="422"/>
-      <c r="E7" s="422"/>
-      <c r="F7" s="422"/>
-      <c r="G7" s="422"/>
-      <c r="H7" s="423"/>
+      <c r="C7" s="420"/>
+      <c r="D7" s="421"/>
+      <c r="E7" s="421"/>
+      <c r="F7" s="421"/>
+      <c r="G7" s="421"/>
+      <c r="H7" s="422"/>
     </row>
     <row r="8" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="18"/>
       <c r="B8" s="12"/>
-      <c r="C8" s="424"/>
-      <c r="D8" s="425"/>
-      <c r="E8" s="425"/>
-      <c r="F8" s="425"/>
-      <c r="G8" s="425"/>
-      <c r="H8" s="426"/>
+      <c r="C8" s="423"/>
+      <c r="D8" s="424"/>
+      <c r="E8" s="424"/>
+      <c r="F8" s="424"/>
+      <c r="G8" s="424"/>
+      <c r="H8" s="425"/>
     </row>
     <row r="9" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A9" s="18"/>
@@ -20818,11 +20815,11 @@
       <c r="B11" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C11" s="414">
+      <c r="C11" s="413">
         <f>IF(Datum=0,"",Datum)</f>
         <v>45588</v>
       </c>
-      <c r="D11" s="415"/>
+      <c r="D11" s="414"/>
       <c r="E11" s="79"/>
       <c r="F11" s="81"/>
       <c r="G11" s="81"/>
@@ -20833,7 +20830,7 @@
       <c r="B12" s="12"/>
       <c r="C12" s="76"/>
       <c r="E12" s="58" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="F12" s="85">
         <f>Fahrleistung</f>
@@ -20872,8 +20869,8 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="18"/>
-      <c r="B15" s="293" t="s">
-        <v>468</v>
+      <c r="B15" s="292" t="s">
+        <v>467</v>
       </c>
       <c r="C15" s="21"/>
       <c r="D15" s="21"/>
@@ -20930,7 +20927,7 @@
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="416" t="s">
+      <c r="A18" s="415" t="s">
         <v>12</v>
       </c>
       <c r="B18" s="27" t="s">
@@ -20961,7 +20958,7 @@
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="416"/>
+      <c r="A19" s="415"/>
       <c r="B19" s="27" t="s">
         <v>108</v>
       </c>
@@ -20990,7 +20987,7 @@
       </c>
     </row>
     <row r="20" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="416"/>
+      <c r="A20" s="415"/>
       <c r="B20" s="27" t="s">
         <v>99</v>
       </c>
@@ -21020,7 +21017,7 @@
       <c r="I20" s="107"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="416"/>
+      <c r="A21" s="415"/>
       <c r="B21" s="29" t="s">
         <v>100</v>
       </c>
@@ -21170,7 +21167,7 @@
     <row r="26" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="33"/>
       <c r="B26" s="98" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C26" s="99" t="s">
         <v>105</v>
@@ -21199,37 +21196,37 @@
     </row>
     <row r="27" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="33"/>
-      <c r="B27" s="310" t="s">
-        <v>477</v>
-      </c>
-      <c r="C27" s="311" t="s">
+      <c r="B27" s="309" t="s">
         <v>476</v>
       </c>
-      <c r="D27" s="312">
+      <c r="C27" s="310" t="s">
+        <v>475</v>
+      </c>
+      <c r="D27" s="311">
         <f>SUM(D25:D26)</f>
         <v>24.3022225152</v>
       </c>
-      <c r="E27" s="312">
+      <c r="E27" s="311">
         <f t="shared" ref="E27:G27" si="2">SUM(E25:E26)</f>
         <v>20.967111363072</v>
       </c>
-      <c r="F27" s="312">
+      <c r="F27" s="311">
         <f t="shared" si="2"/>
         <v>9.6288818181818172</v>
       </c>
-      <c r="G27" s="312">
+      <c r="G27" s="311">
         <f t="shared" si="2"/>
         <v>9.7063145454545463</v>
       </c>
-      <c r="H27" s="313">
+      <c r="H27" s="312">
         <f>SUM(H25:H26)</f>
         <v>11.453769923747386</v>
       </c>
       <c r="I27" s="91"/>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="B29" s="293" t="s">
-        <v>469</v>
+      <c r="B29" s="292" t="s">
+        <v>468</v>
       </c>
       <c r="C29" s="21"/>
       <c r="D29" s="21"/>
@@ -21390,18 +21387,18 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="119"/>
-      <c r="B4" s="293" t="s">
+      <c r="B4" s="292" t="s">
         <v>433</v>
       </c>
-      <c r="C4" s="354"/>
-      <c r="D4" s="354"/>
-      <c r="E4" s="354"/>
-      <c r="F4" s="355"/>
+      <c r="C4" s="353"/>
+      <c r="D4" s="353"/>
+      <c r="E4" s="353"/>
+      <c r="F4" s="354"/>
       <c r="G4" s="190"/>
       <c r="H4" s="119"/>
     </row>
     <row r="5" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="370" t="s">
+      <c r="A5" s="369" t="s">
         <v>12</v>
       </c>
       <c r="B5" s="219"/>
@@ -21411,14 +21408,14 @@
       <c r="F5" s="219"/>
       <c r="G5" s="190"/>
       <c r="H5" s="119"/>
-      <c r="J5" s="427" t="s">
+      <c r="J5" s="426" t="s">
         <v>436</v>
       </c>
-      <c r="K5" s="427"/>
-      <c r="L5" s="427"/>
+      <c r="K5" s="426"/>
+      <c r="L5" s="426"/>
     </row>
     <row r="6" spans="1:12" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A6" s="370"/>
+      <c r="A6" s="369"/>
       <c r="B6" s="220" t="s">
         <v>111</v>
       </c>
@@ -21434,17 +21431,17 @@
       <c r="F6" s="221" t="s">
         <v>114</v>
       </c>
-      <c r="G6" s="306" t="s">
+      <c r="G6" s="305" t="s">
         <v>115</v>
       </c>
       <c r="H6" s="119"/>
-      <c r="J6" s="427"/>
-      <c r="K6" s="427"/>
-      <c r="L6" s="427"/>
+      <c r="J6" s="426"/>
+      <c r="K6" s="426"/>
+      <c r="L6" s="426"/>
     </row>
     <row r="7" spans="1:12" ht="13.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="352"/>
-      <c r="B7" s="428" t="s">
+      <c r="A7" s="351"/>
+      <c r="B7" s="427" t="s">
         <v>116</v>
       </c>
       <c r="C7" s="222" t="s">
@@ -21453,114 +21450,114 @@
       <c r="D7" s="223">
         <v>120</v>
       </c>
-      <c r="E7" s="272"/>
+      <c r="E7" s="271"/>
       <c r="F7" s="222" t="s">
         <v>82</v>
       </c>
-      <c r="G7" s="307">
+      <c r="G7" s="306">
         <f t="shared" ref="G7:G17" si="0">IF(ISBLANK(E7),D7,E7)</f>
         <v>120</v>
       </c>
       <c r="H7" s="119"/>
-      <c r="J7" s="427"/>
-      <c r="K7" s="427"/>
-      <c r="L7" s="427"/>
+      <c r="J7" s="426"/>
+      <c r="K7" s="426"/>
+      <c r="L7" s="426"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="352"/>
-      <c r="B8" s="429"/>
+      <c r="A8" s="351"/>
+      <c r="B8" s="428"/>
       <c r="C8" s="222" t="s">
         <v>117</v>
       </c>
       <c r="D8" s="223">
         <v>130</v>
       </c>
-      <c r="E8" s="272"/>
+      <c r="E8" s="271"/>
       <c r="F8" s="222" t="s">
         <v>82</v>
       </c>
-      <c r="G8" s="307">
+      <c r="G8" s="306">
         <f t="shared" si="0"/>
         <v>130</v>
       </c>
       <c r="H8" s="119"/>
-      <c r="J8" s="427"/>
-      <c r="K8" s="427"/>
-      <c r="L8" s="427"/>
+      <c r="J8" s="426"/>
+      <c r="K8" s="426"/>
+      <c r="L8" s="426"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="352"/>
-      <c r="B9" s="430"/>
+      <c r="A9" s="351"/>
+      <c r="B9" s="429"/>
       <c r="C9" s="222" t="s">
         <v>118</v>
       </c>
       <c r="D9" s="223">
         <v>20</v>
       </c>
-      <c r="E9" s="272"/>
+      <c r="E9" s="271"/>
       <c r="F9" s="222" t="s">
         <v>82</v>
       </c>
-      <c r="G9" s="307">
+      <c r="G9" s="306">
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="H9" s="119"/>
-      <c r="J9" s="427"/>
-      <c r="K9" s="427"/>
-      <c r="L9" s="427"/>
+      <c r="J9" s="426"/>
+      <c r="K9" s="426"/>
+      <c r="L9" s="426"/>
     </row>
     <row r="10" spans="1:12" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A10" s="352"/>
-      <c r="B10" s="356" t="s">
+      <c r="A10" s="351"/>
+      <c r="B10" s="355" t="s">
         <v>119</v>
       </c>
       <c r="C10" s="222" t="s">
         <v>120</v>
       </c>
-      <c r="D10" s="367">
+      <c r="D10" s="366">
         <v>64</v>
       </c>
-      <c r="E10" s="272"/>
+      <c r="E10" s="271"/>
       <c r="F10" s="222" t="s">
         <v>84</v>
       </c>
-      <c r="G10" s="307">
+      <c r="G10" s="306">
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
       <c r="H10" s="119"/>
-      <c r="J10" s="427"/>
-      <c r="K10" s="427"/>
-      <c r="L10" s="427"/>
+      <c r="J10" s="426"/>
+      <c r="K10" s="426"/>
+      <c r="L10" s="426"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="352"/>
-      <c r="B11" s="356" t="s">
+      <c r="A11" s="351"/>
+      <c r="B11" s="355" t="s">
         <v>121</v>
       </c>
       <c r="C11" s="222" t="s">
         <v>120</v>
       </c>
-      <c r="D11" s="367">
+      <c r="D11" s="366">
         <v>3.6</v>
       </c>
-      <c r="E11" s="272"/>
+      <c r="E11" s="271"/>
       <c r="F11" s="222" t="s">
         <v>84</v>
       </c>
-      <c r="G11" s="307">
+      <c r="G11" s="306">
         <f t="shared" si="0"/>
         <v>3.6</v>
       </c>
       <c r="H11" s="119"/>
-      <c r="J11" s="427"/>
-      <c r="K11" s="427"/>
-      <c r="L11" s="427"/>
+      <c r="J11" s="426"/>
+      <c r="K11" s="426"/>
+      <c r="L11" s="426"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="352"/>
-      <c r="B12" s="428" t="s">
+      <c r="A12" s="351"/>
+      <c r="B12" s="427" t="s">
         <v>122</v>
       </c>
       <c r="C12" s="222" t="s">
@@ -21569,112 +21566,112 @@
       <c r="D12" s="223">
         <v>19</v>
       </c>
-      <c r="E12" s="272"/>
+      <c r="E12" s="271"/>
       <c r="F12" s="222" t="s">
         <v>124</v>
       </c>
-      <c r="G12" s="307">
+      <c r="G12" s="306">
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="H12" s="119"/>
-      <c r="J12" s="427"/>
-      <c r="K12" s="427"/>
-      <c r="L12" s="427"/>
+      <c r="J12" s="426"/>
+      <c r="K12" s="426"/>
+      <c r="L12" s="426"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="352"/>
-      <c r="B13" s="429"/>
+      <c r="A13" s="351"/>
+      <c r="B13" s="428"/>
       <c r="C13" s="222" t="s">
         <v>125</v>
       </c>
       <c r="D13" s="223">
         <v>21</v>
       </c>
-      <c r="E13" s="272"/>
+      <c r="E13" s="271"/>
       <c r="F13" s="222" t="s">
         <v>124</v>
       </c>
-      <c r="G13" s="307">
+      <c r="G13" s="306">
         <f>IF(ISBLANK(E13),D13,E13)</f>
         <v>21</v>
       </c>
       <c r="H13" s="119"/>
-      <c r="J13" s="427"/>
-      <c r="K13" s="427"/>
-      <c r="L13" s="427"/>
+      <c r="J13" s="426"/>
+      <c r="K13" s="426"/>
+      <c r="L13" s="426"/>
     </row>
     <row r="14" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="416" t="s">
+      <c r="A14" s="415" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="429"/>
+      <c r="B14" s="428"/>
       <c r="C14" s="222" t="s">
         <v>49</v>
       </c>
       <c r="D14" s="223" t="s">
-        <v>566</v>
-      </c>
-      <c r="E14" s="272"/>
+        <v>565</v>
+      </c>
+      <c r="E14" s="271"/>
       <c r="F14" s="222" t="s">
         <v>79</v>
       </c>
-      <c r="G14" s="307" t="str">
+      <c r="G14" s="306" t="str">
         <f>IF(ISBLANK(E14),"keine",E14)</f>
         <v>keine</v>
       </c>
       <c r="H14" s="119"/>
-      <c r="J14" s="427"/>
-      <c r="K14" s="427"/>
-      <c r="L14" s="427"/>
+      <c r="J14" s="426"/>
+      <c r="K14" s="426"/>
+      <c r="L14" s="426"/>
     </row>
     <row r="15" spans="1:12" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="416"/>
-      <c r="B15" s="429"/>
+      <c r="A15" s="415"/>
+      <c r="B15" s="428"/>
       <c r="C15" s="222" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D15" s="223" t="s">
-        <v>566</v>
-      </c>
-      <c r="E15" s="272"/>
+        <v>565</v>
+      </c>
+      <c r="E15" s="271"/>
       <c r="F15" s="222" t="s">
         <v>79</v>
       </c>
-      <c r="G15" s="307" t="str">
+      <c r="G15" s="306" t="str">
         <f t="shared" ref="G15" si="1">IF(ISBLANK(E15),"keine",E15)</f>
         <v>keine</v>
       </c>
       <c r="H15" s="119"/>
-      <c r="J15" s="427"/>
-      <c r="K15" s="427"/>
-      <c r="L15" s="427"/>
+      <c r="J15" s="426"/>
+      <c r="K15" s="426"/>
+      <c r="L15" s="426"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="416"/>
-      <c r="B16" s="430"/>
+      <c r="A16" s="415"/>
+      <c r="B16" s="429"/>
       <c r="C16" s="222" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="D16" s="223" t="s">
-        <v>566</v>
-      </c>
-      <c r="E16" s="272"/>
+        <v>565</v>
+      </c>
+      <c r="E16" s="271"/>
       <c r="F16" s="222" t="s">
         <v>124</v>
       </c>
-      <c r="G16" s="307" t="str">
+      <c r="G16" s="306" t="str">
         <f>IF(ISBLANK(E16),"keine",E16)</f>
         <v>keine</v>
       </c>
       <c r="H16" s="119"/>
-      <c r="J16" s="427"/>
-      <c r="K16" s="427"/>
-      <c r="L16" s="427"/>
+      <c r="J16" s="426"/>
+      <c r="K16" s="426"/>
+      <c r="L16" s="426"/>
     </row>
     <row r="17" spans="1:12" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.25">
-      <c r="A17" s="353"/>
-      <c r="B17" s="357" t="s">
+      <c r="A17" s="352"/>
+      <c r="B17" s="356" t="s">
         <v>126</v>
       </c>
       <c r="C17" s="225" t="s">
@@ -21683,18 +21680,18 @@
       <c r="D17" s="224">
         <v>60</v>
       </c>
-      <c r="E17" s="273"/>
+      <c r="E17" s="272"/>
       <c r="F17" s="225" t="s">
         <v>87</v>
       </c>
-      <c r="G17" s="307">
+      <c r="G17" s="306">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
       <c r="H17" s="191"/>
-      <c r="J17" s="427"/>
-      <c r="K17" s="427"/>
-      <c r="L17" s="427"/>
+      <c r="J17" s="426"/>
+      <c r="K17" s="426"/>
+      <c r="L17" s="426"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="119"/>
@@ -21744,13 +21741,13 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="196"/>
-      <c r="B23" s="293" t="s">
+      <c r="B23" s="292" t="s">
         <v>432</v>
       </c>
-      <c r="C23" s="339"/>
-      <c r="D23" s="340"/>
-      <c r="E23" s="340"/>
-      <c r="F23" s="341"/>
+      <c r="C23" s="338"/>
+      <c r="D23" s="339"/>
+      <c r="E23" s="339"/>
+      <c r="F23" s="340"/>
       <c r="G23" s="194"/>
       <c r="H23" s="195"/>
       <c r="I23" s="195"/>
@@ -21758,9 +21755,9 @@
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="196"/>
       <c r="B24" s="6"/>
-      <c r="C24" s="327"/>
+      <c r="C24" s="326"/>
       <c r="D24" s="6"/>
-      <c r="E24" s="327"/>
+      <c r="E24" s="326"/>
       <c r="F24" s="208"/>
       <c r="G24" s="194"/>
       <c r="H24" s="195"/>
@@ -21768,15 +21765,15 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="196"/>
-      <c r="B25" s="346" t="s">
+      <c r="B25" s="345" t="s">
         <v>51</v>
       </c>
-      <c r="C25" s="327"/>
-      <c r="D25" s="296" t="s">
+      <c r="C25" s="326"/>
+      <c r="D25" s="295" t="s">
         <v>129</v>
       </c>
-      <c r="E25" s="347"/>
-      <c r="F25" s="295" t="s">
+      <c r="E25" s="346"/>
+      <c r="F25" s="294" t="s">
         <v>114</v>
       </c>
       <c r="G25" s="194"/>
@@ -21786,13 +21783,13 @@
     <row r="26" spans="1:12" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A26" s="196"/>
       <c r="B26" s="6"/>
-      <c r="C26" s="327"/>
+      <c r="C26" s="326"/>
       <c r="D26" s="209"/>
       <c r="E26" s="210" t="s">
         <v>113</v>
       </c>
-      <c r="F26" s="294"/>
-      <c r="G26" s="308" t="s">
+      <c r="F26" s="293"/>
+      <c r="G26" s="307" t="s">
         <v>130</v>
       </c>
       <c r="H26" s="198" t="s">
@@ -21815,12 +21812,12 @@
       <c r="F27" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="G27" s="308">
+      <c r="G27" s="307">
         <f>IF(ISNUMBER(E27),E27,D27)/100</f>
         <v>0.41399999999999998</v>
       </c>
       <c r="H27" s="199" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="I27" s="254"/>
     </row>
@@ -21837,12 +21834,12 @@
       <c r="F28" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="G28" s="308">
+      <c r="G28" s="307">
         <f>IF(ISNUMBER(E28),E28,D28)/100</f>
         <v>0.59</v>
       </c>
       <c r="H28" s="199" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="I28" s="254"/>
     </row>
@@ -21851,11 +21848,11 @@
       <c r="B29" s="216" t="s">
         <v>52</v>
       </c>
-      <c r="C29" s="348"/>
-      <c r="D29" s="349"/>
-      <c r="E29" s="350"/>
+      <c r="C29" s="347"/>
+      <c r="D29" s="348"/>
+      <c r="E29" s="349"/>
       <c r="F29" s="208"/>
-      <c r="G29" s="308">
+      <c r="G29" s="307">
         <f>G27*Input_Beschaffung!J31/100+G28*(1-Input_Beschaffung!J31/100)</f>
         <v>0.502</v>
       </c>
@@ -21863,46 +21860,46 @@
       <c r="I29" s="254"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="433"/>
+      <c r="A30" s="432"/>
       <c r="B30" s="212" t="s">
         <v>53</v>
       </c>
       <c r="C30" s="213"/>
-      <c r="D30" s="271">
+      <c r="D30" s="270">
         <v>1.6719999999999999</v>
       </c>
       <c r="E30" s="243"/>
       <c r="F30" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="G30" s="308">
+      <c r="G30" s="307">
         <f t="shared" ref="G30:G32" si="2">IF(ISNUMBER(E30),E30,D30)</f>
         <v>1.6719999999999999</v>
       </c>
       <c r="H30" s="199" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="I30" s="254"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A31" s="433"/>
+      <c r="A31" s="432"/>
       <c r="B31" s="212" t="s">
         <v>54</v>
       </c>
       <c r="C31" s="213"/>
-      <c r="D31" s="271">
+      <c r="D31" s="270">
         <v>1.788</v>
       </c>
       <c r="E31" s="243"/>
       <c r="F31" s="9" t="s">
         <v>136</v>
       </c>
-      <c r="G31" s="308">
+      <c r="G31" s="307">
         <f t="shared" si="2"/>
         <v>1.788</v>
       </c>
       <c r="H31" s="199" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="I31" s="254"/>
     </row>
@@ -21919,12 +21916,12 @@
       <c r="F32" s="9" t="s">
         <v>138</v>
       </c>
-      <c r="G32" s="308">
+      <c r="G32" s="307">
         <f t="shared" si="2"/>
         <v>1.3</v>
       </c>
       <c r="H32" s="199" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="I32" s="254"/>
     </row>
@@ -21952,27 +21949,27 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="193"/>
-      <c r="B35" s="293" t="s">
+      <c r="B35" s="292" t="s">
         <v>139</v>
       </c>
-      <c r="C35" s="339"/>
-      <c r="D35" s="340"/>
-      <c r="E35" s="340"/>
-      <c r="F35" s="341"/>
+      <c r="C35" s="338"/>
+      <c r="D35" s="339"/>
+      <c r="E35" s="339"/>
+      <c r="F35" s="340"/>
       <c r="G35" s="201"/>
       <c r="H35" s="201"/>
       <c r="I35" s="201"/>
     </row>
     <row r="36" spans="1:9" ht="22.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="193"/>
-      <c r="B36" s="434" t="s">
+      <c r="B36" s="433" t="s">
         <v>140</v>
       </c>
-      <c r="C36" s="435"/>
-      <c r="D36" s="435"/>
-      <c r="E36" s="435"/>
-      <c r="F36" s="436"/>
-      <c r="G36" s="308" t="s">
+      <c r="C36" s="434"/>
+      <c r="D36" s="434"/>
+      <c r="E36" s="434"/>
+      <c r="F36" s="435"/>
+      <c r="G36" s="307" t="s">
         <v>130</v>
       </c>
       <c r="H36" s="202"/>
@@ -21981,15 +21978,15 @@
     <row r="37" spans="1:9" ht="27.6" x14ac:dyDescent="0.25">
       <c r="A37" s="193"/>
       <c r="B37" s="6"/>
-      <c r="C37" s="327"/>
-      <c r="D37" s="327"/>
-      <c r="E37" s="342" t="s">
+      <c r="C37" s="326"/>
+      <c r="D37" s="326"/>
+      <c r="E37" s="341" t="s">
         <v>113</v>
       </c>
-      <c r="F37" s="343" t="s">
+      <c r="F37" s="342" t="s">
         <v>114</v>
       </c>
-      <c r="G37" s="308"/>
+      <c r="G37" s="307"/>
       <c r="H37" s="195"/>
       <c r="I37" s="195"/>
     </row>
@@ -21998,7 +21995,7 @@
       <c r="B38" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="C38" s="327"/>
+      <c r="C38" s="326"/>
       <c r="D38" s="218">
         <f>IF(KostTHGVorgabe="(Niedrig) 250", 250, 860)</f>
         <v>860</v>
@@ -22007,7 +22004,7 @@
       <c r="F38" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="G38" s="308">
+      <c r="G38" s="307">
         <f>IF(ISNUMBER(E38),E38,D38)</f>
         <v>860</v>
       </c>
@@ -22019,11 +22016,11 @@
     <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" s="193"/>
       <c r="B39" s="6"/>
-      <c r="C39" s="327"/>
-      <c r="D39" s="344"/>
-      <c r="E39" s="344"/>
-      <c r="F39" s="345"/>
-      <c r="G39" s="308"/>
+      <c r="C39" s="326"/>
+      <c r="D39" s="343"/>
+      <c r="E39" s="343"/>
+      <c r="F39" s="344"/>
+      <c r="G39" s="307"/>
       <c r="H39" s="195"/>
       <c r="I39" s="195"/>
     </row>
@@ -22032,7 +22029,7 @@
       <c r="B40" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="C40" s="327"/>
+      <c r="C40" s="326"/>
       <c r="D40" s="218">
         <v>0.02</v>
       </c>
@@ -22040,7 +22037,7 @@
       <c r="F40" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G40" s="308">
+      <c r="G40" s="307">
         <f>IF(ISNUMBER(E40),E40,D40)</f>
         <v>0.02</v>
       </c>
@@ -22062,7 +22059,7 @@
       <c r="F41" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="G41" s="308">
+      <c r="G41" s="307">
         <f>IF(ISNUMBER(E41),E41,D41)</f>
         <v>0.15</v>
       </c>
@@ -22078,7 +22075,7 @@
       <c r="D42" s="194"/>
       <c r="E42" s="194"/>
       <c r="F42" s="193"/>
-      <c r="G42" s="308"/>
+      <c r="G42" s="307"/>
       <c r="H42" s="195"/>
       <c r="I42" s="195"/>
     </row>
@@ -22089,29 +22086,29 @@
       <c r="D43" s="193"/>
       <c r="E43" s="193"/>
       <c r="F43" s="193"/>
-      <c r="G43" s="308"/>
+      <c r="G43" s="307"/>
       <c r="H43" s="194"/>
       <c r="I43" s="194"/>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" s="193"/>
-      <c r="B44" s="293" t="s">
+      <c r="B44" s="292" t="s">
         <v>146</v>
       </c>
-      <c r="C44" s="340"/>
-      <c r="D44" s="340"/>
-      <c r="E44" s="340"/>
-      <c r="F44" s="351"/>
-      <c r="G44" s="308"/>
+      <c r="C44" s="339"/>
+      <c r="D44" s="339"/>
+      <c r="E44" s="339"/>
+      <c r="F44" s="350"/>
+      <c r="G44" s="307"/>
       <c r="H44" s="193"/>
       <c r="I44" s="193"/>
     </row>
     <row r="45" spans="1:9" ht="16.2" x14ac:dyDescent="0.35">
       <c r="A45" s="193"/>
-      <c r="B45" s="431" t="s">
+      <c r="B45" s="430" t="s">
         <v>437</v>
       </c>
-      <c r="C45" s="432"/>
+      <c r="C45" s="431"/>
       <c r="D45" s="218">
         <v>84</v>
       </c>
@@ -22119,7 +22116,7 @@
       <c r="F45" s="9" t="s">
         <v>147</v>
       </c>
-      <c r="G45" s="308">
+      <c r="G45" s="307">
         <f>IF(ISNUMBER(E45),E45,D45)</f>
         <v>84</v>
       </c>
@@ -22246,7 +22243,7 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>21</v>
@@ -22389,7 +22386,7 @@
       <c r="B18" s="72" t="s">
         <v>155</v>
       </c>
-      <c r="C18" s="288">
+      <c r="C18" s="287">
         <f>0.0057*(ReichwPHEV1/23)^3-0.0838*(ReichwPHEV1/23)^2+0.4261*(ReichwPHEV1/23)+ 0.1633</f>
         <v>0.1633</v>
       </c>
@@ -22400,7 +22397,7 @@
       <c r="B19" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C19" s="289">
+      <c r="C19" s="288">
         <f>Verbrauch1/(1-0.9*C18)</f>
         <v>5.8614585653494018</v>
       </c>
@@ -22413,7 +22410,7 @@
       <c r="B20" s="72" t="s">
         <v>157</v>
       </c>
-      <c r="C20" s="290">
+      <c r="C20" s="289">
         <f>VerbEl_WLTP1/C18</f>
         <v>0</v>
       </c>
@@ -22426,7 +22423,7 @@
       <c r="B21" s="186" t="s">
         <v>158</v>
       </c>
-      <c r="C21" s="291">
+      <c r="C21" s="290">
         <f>0.0021*(ReichwPHEV1/23)^3-0.0358*(ReichwPHEV1/23)^2+0.2607*(ReichwPHEV1/23)- 0.0267</f>
         <v>-2.6700000000000002E-2</v>
       </c>
@@ -22434,13 +22431,13 @@
       <c r="F21" s="125"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="440" t="s">
+      <c r="A22" s="439" t="s">
         <v>12</v>
       </c>
-      <c r="B22" s="439" t="s">
+      <c r="B22" s="438" t="s">
         <v>159</v>
       </c>
-      <c r="C22" s="292">
+      <c r="C22" s="291">
         <f>C19*(1-0.9*C21)</f>
         <v>6.0023094146747482</v>
       </c>
@@ -22450,9 +22447,9 @@
       <c r="F22" s="125"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="440"/>
-      <c r="B23" s="409"/>
-      <c r="C23" s="292">
+      <c r="A23" s="439"/>
+      <c r="B23" s="408"/>
+      <c r="C23" s="291">
         <f>C20*C21</f>
         <v>0</v>
       </c>
@@ -22489,7 +22486,7 @@
       <c r="B28" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C28" s="279">
+      <c r="C28" s="278">
         <f>IF(Antriebsart1="Vollelektrisch (BEV)",0,IFERROR(VLOOKUP(Energie1,EnKostList,6,FALSE),0)*IF(Antriebsart1="Plug-In-Hybrid (PHEV)",VerbPHEV1,Verbrauch1)/100*Fahrleistung)</f>
         <v>1671.9999999999998</v>
       </c>
@@ -22502,7 +22499,7 @@
       <c r="B29" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C29" s="279">
+      <c r="C29" s="278">
         <f>IF(Antriebsart1="Verbrenner",0,VLOOKUP("Strom",EnKostList,6,FALSE)*IF(Antriebsart1="Plug-In-Hybrid (PHEV)",VerbElPHEV1,VerbEl_WLTP1)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
@@ -22514,7 +22511,7 @@
       <c r="B30" s="64" t="s">
         <v>101</v>
       </c>
-      <c r="C30" s="280">
+      <c r="C30" s="279">
         <f>SUM(C28:C29)</f>
         <v>1671.9999999999998</v>
       </c>
@@ -22541,7 +22538,7 @@
       <c r="B33" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="C33" s="279">
+      <c r="C33" s="278">
         <f>IF(Antriebsart1="Plug-In-Hybrid (PHEV)",VerbPHEV1*VLOOKUP(Energie1,CO2List,2,FALSE)/100,CO2_1)*Fahrleistung/1000000</f>
         <v>2.64</v>
       </c>
@@ -22554,7 +22551,7 @@
       <c r="B34" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C34" s="279">
+      <c r="C34" s="278">
         <f>C33*Kost_THG</f>
         <v>2270.4</v>
       </c>
@@ -22566,7 +22563,7 @@
       <c r="B35" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="C35" s="279">
+      <c r="C35" s="278">
         <f>IF(Energie1="Strom",0,NOX_1*Fahrleistung*Kost_NOX/1000)</f>
         <v>20.32</v>
       </c>
@@ -22578,7 +22575,7 @@
       <c r="B36" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C36" s="279">
+      <c r="C36" s="278">
         <f>IF(Energie1="Strom",0,Partikel1*Fahrleistung*Kost_Partikel/1000)</f>
         <v>1.05</v>
       </c>
@@ -22590,7 +22587,7 @@
       <c r="B37" s="64" t="s">
         <v>101</v>
       </c>
-      <c r="C37" s="280">
+      <c r="C37" s="279">
         <f>SUM(C34:C36)</f>
         <v>2291.7700000000004</v>
       </c>
@@ -22615,7 +22612,7 @@
       <c r="B40" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="C40" s="279">
+      <c r="C40" s="278">
         <f>IFERROR(IF(Antriebsart1="Vollelektrisch (BEV)",VLOOKUP("Strom",CO2List,3,FALSE)*VerbEl_WLTP1/100*Fahrleistung/1000000,IF(Antriebsart1="Verbrenner",VLOOKUP(Energie1,CO2List,3,FALSE)*Verbrauch1/100*Fahrleistung/1000000,VLOOKUP(Energie1,CO2List,3,FALSE)*VerbPHEV1/100*Fahrleistung/1000000+VLOOKUP("Strom",CO2List,3,FALSE)*VerbElPHEV1/100*Fahrleistung/1000000)),0)</f>
         <v>0.83174607360000008</v>
       </c>
@@ -22628,7 +22625,7 @@
       <c r="B41" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C41" s="279">
+      <c r="C41" s="278">
         <f>C40*Kost_THG</f>
         <v>715.30162329600012</v>
       </c>
@@ -22660,13 +22657,13 @@
       <c r="D45" s="62"/>
     </row>
     <row r="46" spans="1:6" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="370" t="s">
+      <c r="A46" s="369" t="s">
         <v>12</v>
       </c>
-      <c r="B46" s="437" t="s">
+      <c r="B46" s="436" t="s">
         <v>164</v>
       </c>
-      <c r="C46" s="281">
+      <c r="C46" s="280">
         <f>IF(OR(Antriebsart1="Vollelektrisch (BEV)",Antriebsart1="Plug-In-Hybrid (PHEV)"),Batterie1*Batterie_THG/1000,0)</f>
         <v>0</v>
       </c>
@@ -22677,9 +22674,9 @@
       <c r="F46" s="107"/>
     </row>
     <row r="47" spans="1:6" ht="16.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="370"/>
-      <c r="B47" s="438"/>
-      <c r="C47" s="281">
+      <c r="A47" s="369"/>
+      <c r="B47" s="437"/>
+      <c r="C47" s="280">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
         <v>0</v>
       </c>
@@ -22693,7 +22690,7 @@
       <c r="B48" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="C48" s="279">
+      <c r="C48" s="278">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Kost_THG, C46/Haltedauer*Kost_THG)</f>
         <v>0</v>
       </c>
@@ -22724,7 +22721,7 @@
       <c r="B54" s="68" t="s">
         <v>176</v>
       </c>
-      <c r="C54" s="282">
+      <c r="C54" s="281">
         <f>IF(FinArt="Kauf",IF(KaufpreisRech="Kaufpreis",Gesamtpreis1,0),Gesamtpreis1*Haltedauer*12+IF(FinArt="Leasing",LeasSondZahl1,0))</f>
         <v>0</v>
       </c>
@@ -22734,13 +22731,13 @@
       <c r="F54" s="58"/>
     </row>
     <row r="55" spans="1:6" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A55" s="305" t="s">
+      <c r="A55" s="304" t="s">
         <v>12</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="C55" s="283">
+        <v>474</v>
+      </c>
+      <c r="C55" s="282">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis1-Gesamtpreis1*(-0.2*LN(Haltedauer)+0.667),0)</f>
         <v>24164.210717478156</v>
       </c>
@@ -22753,7 +22750,7 @@
       <c r="B56" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C56" s="283">
+      <c r="C56" s="282">
         <f>C30*Haltedauer</f>
         <v>11703.999999999998</v>
       </c>
@@ -22766,7 +22763,7 @@
       <c r="B57" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C57" s="283">
+      <c r="C57" s="282">
         <f>C37*Haltedauer</f>
         <v>16042.390000000003</v>
       </c>
@@ -22779,7 +22776,7 @@
       <c r="B58" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C58" s="283">
+      <c r="C58" s="282">
         <f>C41*Haltedauer</f>
         <v>5007.111363072001</v>
       </c>
@@ -22789,63 +22786,63 @@
       <c r="F58" s="58"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B59" s="329" t="s">
+      <c r="B59" s="328" t="s">
         <v>100</v>
       </c>
-      <c r="C59" s="330">
+      <c r="C59" s="329">
         <f>C48*Haltedauer</f>
         <v>0</v>
       </c>
-      <c r="D59" s="329" t="s">
+      <c r="D59" s="328" t="s">
         <v>75</v>
       </c>
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="370" t="s">
+      <c r="A60" s="369" t="s">
         <v>12</v>
       </c>
-      <c r="B60" s="327" t="str">
+      <c r="B60" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", Zusatzangabe_x)</f>
         <v>Kfz-Steuer</v>
       </c>
-      <c r="C60" s="328">
+      <c r="C60" s="327">
         <f>IF(ISBLANK(Zusatzangabe_x), "", Zusatzangabe_x1*Haltedauer)</f>
         <v>1533</v>
       </c>
-      <c r="D60" s="327" t="str">
+      <c r="D60" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", "EUR")</f>
         <v>EUR</v>
       </c>
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="370"/>
-      <c r="B61" s="327" t="str">
+      <c r="A61" s="369"/>
+      <c r="B61" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
       </c>
-      <c r="C61" s="328" t="str">
+      <c r="C61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y1*Haltedauer)</f>
         <v/>
       </c>
-      <c r="D61" s="327" t="str">
+      <c r="D61" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", "EUR")</f>
         <v/>
       </c>
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="370"/>
-      <c r="B62" s="327" t="str">
+      <c r="A62" s="369"/>
+      <c r="B62" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
       </c>
-      <c r="C62" s="328" t="str">
+      <c r="C62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z1*Haltedauer)</f>
         <v/>
       </c>
-      <c r="D62" s="327" t="str">
+      <c r="D62" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", "EUR")</f>
         <v/>
       </c>
@@ -22855,7 +22852,7 @@
       <c r="B63" s="64" t="s">
         <v>101</v>
       </c>
-      <c r="C63" s="284">
+      <c r="C63" s="283">
         <f>SUM(C54:C62)</f>
         <v>58450.712080550154</v>
       </c>
@@ -22871,7 +22868,7 @@
       <c r="B65" s="68" t="s">
         <v>178</v>
       </c>
-      <c r="C65" s="285">
+      <c r="C65" s="284">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Haltedauer, C46)</f>
         <v>0</v>
       </c>
@@ -22883,7 +22880,7 @@
       <c r="B66" s="72" t="s">
         <v>106</v>
       </c>
-      <c r="C66" s="286">
+      <c r="C66" s="285">
         <f>C33*Haltedauer+C40*Haltedauer</f>
         <v>24.3022225152</v>
       </c>
@@ -22938,7 +22935,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>21</v>
@@ -23091,7 +23088,7 @@
       <c r="B18" s="72" t="s">
         <v>155</v>
       </c>
-      <c r="C18" s="288">
+      <c r="C18" s="287">
         <f>0.0057*(ReichwPHEV2/23)^3-0.0838*(ReichwPHEV2/23)^2+0.4261*(ReichwPHEV2/23)+ 0.1633</f>
         <v>0.1633</v>
       </c>
@@ -23103,7 +23100,7 @@
       <c r="B19" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C19" s="289">
+      <c r="C19" s="288">
         <f>Verbrauch2/(1-0.9*C18)</f>
         <v>5.0408543662004854</v>
       </c>
@@ -23117,7 +23114,7 @@
       <c r="B20" s="72" t="s">
         <v>157</v>
       </c>
-      <c r="C20" s="290">
+      <c r="C20" s="289">
         <f>VerbEl_WLTP2/C18</f>
         <v>0</v>
       </c>
@@ -23131,7 +23128,7 @@
       <c r="B21" s="186" t="s">
         <v>158</v>
       </c>
-      <c r="C21" s="291">
+      <c r="C21" s="290">
         <f>0.0021*(ReichwPHEV2/23)^3-0.0358*(ReichwPHEV2/23)^2+0.2607*(ReichwPHEV2/23)- 0.0267</f>
         <v>-2.6700000000000002E-2</v>
       </c>
@@ -23140,13 +23137,13 @@
       <c r="F21" s="125"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="440" t="s">
+      <c r="A22" s="439" t="s">
         <v>12</v>
       </c>
-      <c r="B22" s="439" t="s">
+      <c r="B22" s="438" t="s">
         <v>159</v>
       </c>
-      <c r="C22" s="292">
+      <c r="C22" s="291">
         <f>C19*(1-0.9*C21)</f>
         <v>5.1619860966202831</v>
       </c>
@@ -23157,9 +23154,9 @@
       <c r="F22" s="125"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="440"/>
-      <c r="B23" s="409"/>
-      <c r="C23" s="292">
+      <c r="A23" s="439"/>
+      <c r="B23" s="408"/>
+      <c r="C23" s="291">
         <f>C20*C21</f>
         <v>0</v>
       </c>
@@ -23200,7 +23197,7 @@
       <c r="B28" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C28" s="279">
+      <c r="C28" s="278">
         <f>IF(Antriebsart2="Vollelektrisch (BEV)",0,IFERROR(VLOOKUP(Energie2,EnKostList,6,FALSE),0)*IF(Antriebsart2="Plug-In-Hybrid (PHEV)",VerbPHEV2,Verbrauch2)/100*Fahrleistung)</f>
         <v>1437.92</v>
       </c>
@@ -23214,7 +23211,7 @@
       <c r="B29" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C29" s="279">
+      <c r="C29" s="278">
         <f>IF(Antriebsart2="Verbrenner",0,VLOOKUP("Strom",EnKostList,6,FALSE)*IF(Antriebsart2="Plug-In-Hybrid (PHEV)",VerbElPHEV2,VerbEl_WLTP2)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
@@ -23228,7 +23225,7 @@
       <c r="B30" s="64" t="s">
         <v>101</v>
       </c>
-      <c r="C30" s="280">
+      <c r="C30" s="279">
         <f>SUM(C28:C29)</f>
         <v>1437.92</v>
       </c>
@@ -23260,7 +23257,7 @@
       <c r="B33" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="C33" s="279">
+      <c r="C33" s="278">
         <f>IF(Antriebsart2="Plug-In-Hybrid (PHEV)",VerbPHEV2*VLOOKUP(Energie2,CO2List,2,FALSE)/100,CO2_2)*Fahrleistung/1000000</f>
         <v>2.2799999999999998</v>
       </c>
@@ -23274,7 +23271,7 @@
       <c r="B34" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C34" s="279">
+      <c r="C34" s="278">
         <f>C33*Kost_THG</f>
         <v>1960.7999999999997</v>
       </c>
@@ -23288,7 +23285,7 @@
       <c r="B35" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="C35" s="287">
+      <c r="C35" s="286">
         <f>IF(Energie2="Strom",0,NOX_2*Fahrleistung*Kost_NOX/1000)</f>
         <v>12.24</v>
       </c>
@@ -23302,7 +23299,7 @@
       <c r="B36" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C36" s="287">
+      <c r="C36" s="286">
         <f>IF(Energie2="Strom",0,Partikel2*Fahrleistung*Kost_Partikel/1000)</f>
         <v>1.62</v>
       </c>
@@ -23316,7 +23313,7 @@
       <c r="B37" s="64" t="s">
         <v>101</v>
       </c>
-      <c r="C37" s="280">
+      <c r="C37" s="279">
         <f>SUM(C34:C36)</f>
         <v>1974.6599999999996</v>
       </c>
@@ -23348,7 +23345,7 @@
       <c r="B40" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="C40" s="279">
+      <c r="C40" s="278">
         <f>IFERROR(IF(Antriebsart2="Vollelektrisch (BEV)",VLOOKUP("Strom",CO2List,3,FALSE)*VerbEl_WLTP2/100*Fahrleistung/1000000,IF(Antriebsart2="Verbrenner",VLOOKUP(Energie2,CO2List,3,FALSE)*Verbrauch2/100*Fahrleistung/1000000,VLOOKUP(Energie2,CO2List,3,FALSE)*VerbPHEV2/100*Fahrleistung/1000000+VLOOKUP("Strom",CO2List,3,FALSE)*VerbElPHEV2/100*Fahrleistung/1000000)),0)</f>
         <v>0.71530162329600011</v>
       </c>
@@ -23362,7 +23359,7 @@
       <c r="B41" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C41" s="279">
+      <c r="C41" s="278">
         <f>C40*Kost_THG</f>
         <v>615.15939603456013</v>
       </c>
@@ -23405,13 +23402,13 @@
       <c r="F45" s="125"/>
     </row>
     <row r="46" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A46" s="370" t="s">
+      <c r="A46" s="369" t="s">
         <v>12</v>
       </c>
-      <c r="B46" s="437" t="s">
+      <c r="B46" s="436" t="s">
         <v>164</v>
       </c>
-      <c r="C46" s="281">
+      <c r="C46" s="280">
         <f>IF(OR(Antriebsart2="Vollelektrisch (BEV)",Antriebsart2="Plug-In-Hybrid (PHEV)"),Batterie2*Batterie_THG/1000,0)</f>
         <v>0</v>
       </c>
@@ -23422,9 +23419,9 @@
       <c r="F46" s="125"/>
     </row>
     <row r="47" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A47" s="370"/>
-      <c r="B47" s="438"/>
-      <c r="C47" s="281">
+      <c r="A47" s="369"/>
+      <c r="B47" s="437"/>
+      <c r="C47" s="280">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
         <v>0</v>
       </c>
@@ -23438,7 +23435,7 @@
       <c r="B48" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="C48" s="279">
+      <c r="C48" s="278">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Kost_THG, C46/Haltedauer*Kost_THG)</f>
         <v>0</v>
       </c>
@@ -23475,7 +23472,7 @@
       <c r="B54" s="68" t="s">
         <v>176</v>
       </c>
-      <c r="C54" s="282">
+      <c r="C54" s="281">
         <f>IF(FinArt="Kauf",IF(KaufpreisRech="Kaufpreis",Gesamtpreis2,0),Gesamtpreis2*Haltedauer*12+IF(FinArt="Leasing",LeasSondZahl2,0))</f>
         <v>0</v>
       </c>
@@ -23486,13 +23483,13 @@
       <c r="F54" s="58"/>
     </row>
     <row r="55" spans="1:6" s="71" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A55" s="305" t="s">
+      <c r="A55" s="304" t="s">
         <v>12</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="C55" s="283">
+        <v>474</v>
+      </c>
+      <c r="C55" s="282">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis2-Gesamtpreis2*(-0.2*LN(Haltedauer)+0.667),0)</f>
         <v>26020.218534092586</v>
       </c>
@@ -23506,7 +23503,7 @@
       <c r="B56" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C56" s="283">
+      <c r="C56" s="282">
         <f>C30*Haltedauer</f>
         <v>10065.44</v>
       </c>
@@ -23519,7 +23516,7 @@
       <c r="B57" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C57" s="283">
+      <c r="C57" s="282">
         <f>C37*Haltedauer</f>
         <v>13822.619999999997</v>
       </c>
@@ -23532,7 +23529,7 @@
       <c r="B58" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C58" s="283">
+      <c r="C58" s="282">
         <f>C41*Haltedauer</f>
         <v>4306.1157722419211</v>
       </c>
@@ -23542,63 +23539,63 @@
       <c r="F58" s="58"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B59" s="329" t="s">
+      <c r="B59" s="328" t="s">
         <v>100</v>
       </c>
-      <c r="C59" s="330">
+      <c r="C59" s="329">
         <f>C48*Haltedauer</f>
         <v>0</v>
       </c>
-      <c r="D59" s="329" t="s">
+      <c r="D59" s="328" t="s">
         <v>75</v>
       </c>
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="370" t="s">
+      <c r="A60" s="369" t="s">
         <v>12</v>
       </c>
-      <c r="B60" s="327" t="str">
+      <c r="B60" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", Zusatzangabe_x)</f>
         <v>Kfz-Steuer</v>
       </c>
-      <c r="C60" s="328">
+      <c r="C60" s="327">
         <f>IF(ISBLANK(Zusatzangabe_x), "", Zusatzangabe_x2*Haltedauer)</f>
         <v>1596</v>
       </c>
-      <c r="D60" s="327" t="str">
+      <c r="D60" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", "EUR")</f>
         <v>EUR</v>
       </c>
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="370"/>
-      <c r="B61" s="327" t="str">
+      <c r="A61" s="369"/>
+      <c r="B61" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
       </c>
-      <c r="C61" s="328" t="str">
+      <c r="C61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y2*Haltedauer)</f>
         <v/>
       </c>
-      <c r="D61" s="327" t="str">
+      <c r="D61" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", "EUR")</f>
         <v/>
       </c>
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="370"/>
-      <c r="B62" s="327" t="str">
+      <c r="A62" s="369"/>
+      <c r="B62" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
       </c>
-      <c r="C62" s="328" t="str">
+      <c r="C62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z2*Haltedauer)</f>
         <v/>
       </c>
-      <c r="D62" s="327" t="str">
+      <c r="D62" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", "EUR")</f>
         <v/>
       </c>
@@ -23608,7 +23605,7 @@
       <c r="B63" s="64" t="s">
         <v>101</v>
       </c>
-      <c r="C63" s="284">
+      <c r="C63" s="283">
         <f>SUM(C54:C62)</f>
         <v>55810.394306334507</v>
       </c>
@@ -23630,7 +23627,7 @@
       <c r="B65" s="68" t="s">
         <v>178</v>
       </c>
-      <c r="C65" s="285">
+      <c r="C65" s="284">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Haltedauer, C46)</f>
         <v>0</v>
       </c>
@@ -23642,7 +23639,7 @@
       <c r="B66" s="72" t="s">
         <v>106</v>
       </c>
-      <c r="C66" s="286">
+      <c r="C66" s="285">
         <f>C33*Haltedauer+C40*Haltedauer</f>
         <v>20.967111363072</v>
       </c>
@@ -23698,7 +23695,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="B2" s="2" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E2" s="106" t="s">
         <v>21</v>
@@ -23851,7 +23848,7 @@
       <c r="B18" s="72" t="s">
         <v>155</v>
       </c>
-      <c r="C18" s="288">
+      <c r="C18" s="287">
         <f>0.0057*(ReichwPHEV3/23)^3-0.0838*(ReichwPHEV3/23)^2+0.4261*(ReichwPHEV3/23)+ 0.1633</f>
         <v>0.1633</v>
       </c>
@@ -23863,7 +23860,7 @@
       <c r="B19" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="C19" s="289">
+      <c r="C19" s="288">
         <f>Verbrauch3/(1-0.9*C18)</f>
         <v>0</v>
       </c>
@@ -23877,7 +23874,7 @@
       <c r="B20" s="72" t="s">
         <v>157</v>
       </c>
-      <c r="C20" s="290">
+      <c r="C20" s="289">
         <f>VerbEl_WLTP3/C18</f>
         <v>94.91733006736068</v>
       </c>
@@ -23891,7 +23888,7 @@
       <c r="B21" s="186" t="s">
         <v>158</v>
       </c>
-      <c r="C21" s="291">
+      <c r="C21" s="290">
         <f>0.0021*(ReichwPHEV3/23)^3-0.0358*(ReichwPHEV3/23)^2+0.2607*(ReichwPHEV3/23)- 0.0267</f>
         <v>-2.6700000000000002E-2</v>
       </c>
@@ -23900,13 +23897,13 @@
       <c r="F21" s="125"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="440" t="s">
+      <c r="A22" s="439" t="s">
         <v>12</v>
       </c>
-      <c r="B22" s="439" t="s">
+      <c r="B22" s="438" t="s">
         <v>159</v>
       </c>
-      <c r="C22" s="292">
+      <c r="C22" s="291">
         <f>C19*(1-0.9*C21)</f>
         <v>0</v>
       </c>
@@ -23917,9 +23914,9 @@
       <c r="F22" s="125"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="440"/>
-      <c r="B23" s="409"/>
-      <c r="C23" s="292">
+      <c r="A23" s="439"/>
+      <c r="B23" s="408"/>
+      <c r="C23" s="291">
         <f>C20*C21</f>
         <v>-2.5342927127985302</v>
       </c>
@@ -23960,7 +23957,7 @@
       <c r="B28" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="C28" s="279">
+      <c r="C28" s="278">
         <f>IF(Antriebsart3="Vollelektrisch (BEV)",0,IFERROR(VLOOKUP(Energie3,EnKostList,6,FALSE),0)*IF(Antriebsart3="Plug-In-Hybrid (PHEV)",VerbPHEV3,Verbrauch3)/100*Fahrleistung)</f>
         <v>0</v>
       </c>
@@ -23974,7 +23971,7 @@
       <c r="B29" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C29" s="279">
+      <c r="C29" s="278">
         <f>IF(Antriebsart3="Verbrenner",0,VLOOKUP("Strom",EnKostList,6,FALSE)*IF(Antriebsart3="Plug-In-Hybrid (PHEV)",VerbElPHEV3,VerbEl_WLTP3)/100*Fahrleistung)</f>
         <v>1556.1999999999998</v>
       </c>
@@ -23988,7 +23985,7 @@
       <c r="B30" s="64" t="s">
         <v>101</v>
       </c>
-      <c r="C30" s="280">
+      <c r="C30" s="279">
         <f>SUM(C28:C29)</f>
         <v>1556.1999999999998</v>
       </c>
@@ -24020,7 +24017,7 @@
       <c r="B33" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="C33" s="279">
+      <c r="C33" s="278">
         <f>IF(Antriebsart3="Plug-In-Hybrid (PHEV)",VerbPHEV3*VLOOKUP(Energie3,CO2List,2,FALSE)/100,CO2_3)*Fahrleistung/1000000</f>
         <v>0</v>
       </c>
@@ -24034,7 +24031,7 @@
       <c r="B34" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C34" s="279">
+      <c r="C34" s="278">
         <f>C33*Kost_THG</f>
         <v>0</v>
       </c>
@@ -24048,7 +24045,7 @@
       <c r="B35" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="C35" s="287">
+      <c r="C35" s="286">
         <f>IF(Energie3="Strom",0,NOX_3*Fahrleistung*Kost_NOX/1000)</f>
         <v>0</v>
       </c>
@@ -24062,7 +24059,7 @@
       <c r="B36" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C36" s="287">
+      <c r="C36" s="286">
         <f>IF(Energie3="Strom",0,Partikel3*Fahrleistung*Kost_Partikel/1000)</f>
         <v>0</v>
       </c>
@@ -24076,7 +24073,7 @@
       <c r="B37" s="64" t="s">
         <v>101</v>
       </c>
-      <c r="C37" s="280">
+      <c r="C37" s="279">
         <f>SUM(C34:C36)</f>
         <v>0</v>
       </c>
@@ -24108,7 +24105,7 @@
       <c r="B40" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="C40" s="279">
+      <c r="C40" s="278">
         <f>IFERROR(IF(Antriebsart3="Vollelektrisch (BEV)",VLOOKUP("Strom",CO2List,3,FALSE)*VerbEl_WLTP3/100*Fahrleistung/1000000,IF(Antriebsart3="Verbrenner",VLOOKUP(Energie3,CO2List,3,FALSE)*Verbrauch3/100*Fahrleistung/1000000,VLOOKUP(Energie3,CO2List,3,FALSE)*VerbPHEV3/100*Fahrleistung/1000000+VLOOKUP("Strom",CO2List,3,FALSE)*VerbElPHEV3/100*Fahrleistung/1000000)),0)</f>
         <v>0.90209999999999979</v>
       </c>
@@ -24122,7 +24119,7 @@
       <c r="B41" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C41" s="279">
+      <c r="C41" s="278">
         <f>C40*Kost_THG</f>
         <v>775.80599999999981</v>
       </c>
@@ -24165,13 +24162,13 @@
       <c r="F45" s="125"/>
     </row>
     <row r="46" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A46" s="370" t="s">
+      <c r="A46" s="369" t="s">
         <v>12</v>
       </c>
-      <c r="B46" s="437" t="s">
+      <c r="B46" s="436" t="s">
         <v>164</v>
       </c>
-      <c r="C46" s="281">
+      <c r="C46" s="280">
         <f>IF(OR(Antriebsart3="Vollelektrisch (BEV)",Antriebsart3="Plug-In-Hybrid (PHEV)"),Batterie3*Batterie_THG/1000,0)</f>
         <v>5.2080000000000002</v>
       </c>
@@ -24182,9 +24179,9 @@
       <c r="F46" s="133"/>
     </row>
     <row r="47" spans="1:6" s="67" customFormat="1" ht="16.2" x14ac:dyDescent="0.25">
-      <c r="A47" s="370"/>
-      <c r="B47" s="438"/>
-      <c r="C47" s="281">
+      <c r="A47" s="369"/>
+      <c r="B47" s="437"/>
+      <c r="C47" s="280">
         <f>IF((Fahrleistung*16)&lt;220000,C46*10^6/(Fahrleistung*16),C46*10^6/220000)</f>
         <v>23.672727272727272</v>
       </c>
@@ -24198,7 +24195,7 @@
       <c r="B48" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="C48" s="279">
+      <c r="C48" s="278">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Kost_THG, C46/Haltedauer*Kost_THG)</f>
         <v>407.17090909090905</v>
       </c>
@@ -24235,7 +24232,7 @@
       <c r="B54" s="68" t="s">
         <v>176</v>
       </c>
-      <c r="C54" s="282">
+      <c r="C54" s="281">
         <f>IF(FinArt="Kauf",IF(KaufpreisRech="Kaufpreis",Gesamtpreis3,0),Gesamtpreis3*Haltedauer*12+IF(FinArt="Leasing",LeasSondZahl3,0))</f>
         <v>0</v>
       </c>
@@ -24246,13 +24243,13 @@
       <c r="F54" s="58"/>
     </row>
     <row r="55" spans="1:6" s="71" customFormat="1" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A55" s="305" t="s">
+      <c r="A55" s="304" t="s">
         <v>12</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="C55" s="283">
+        <v>474</v>
+      </c>
+      <c r="C55" s="282">
         <f>IF(AND(KaufpreisRech="Wertminderung",FinArt="Kauf"),Gesamtpreis3-Gesamtpreis3*(-0.2*LN(Haltedauer)+0.667),0)</f>
         <v>28472.026525301146</v>
       </c>
@@ -24266,7 +24263,7 @@
       <c r="B56" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="C56" s="283">
+      <c r="C56" s="282">
         <f>C30*Haltedauer</f>
         <v>10893.399999999998</v>
       </c>
@@ -24279,7 +24276,7 @@
       <c r="B57" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C57" s="283">
+      <c r="C57" s="282">
         <f>C37*Haltedauer</f>
         <v>0</v>
       </c>
@@ -24292,7 +24289,7 @@
       <c r="B58" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="C58" s="283">
+      <c r="C58" s="282">
         <f>C41*Haltedauer</f>
         <v>5430.6419999999989</v>
       </c>
@@ -24302,63 +24299,63 @@
       <c r="F58" s="58"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B59" s="327" t="s">
+      <c r="B59" s="326" t="s">
         <v>100</v>
       </c>
-      <c r="C59" s="328">
+      <c r="C59" s="327">
         <f>C48*Haltedauer</f>
         <v>2850.1963636363635</v>
       </c>
-      <c r="D59" s="327" t="s">
+      <c r="D59" s="326" t="s">
         <v>75</v>
       </c>
       <c r="F59" s="147"/>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="370" t="s">
+      <c r="A60" s="369" t="s">
         <v>12</v>
       </c>
-      <c r="B60" s="327" t="str">
+      <c r="B60" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", Zusatzangabe_x)</f>
         <v>Kfz-Steuer</v>
       </c>
-      <c r="C60" s="328">
+      <c r="C60" s="327">
         <f>IF(ISBLANK(Zusatzangabe_x), "", Zusatzangabe_x3*Haltedauer)</f>
         <v>0</v>
       </c>
-      <c r="D60" s="327" t="str">
+      <c r="D60" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_x), "", "EUR")</f>
         <v>EUR</v>
       </c>
       <c r="F60" s="147"/>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="370"/>
-      <c r="B61" s="327" t="str">
+      <c r="A61" s="369"/>
+      <c r="B61" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y)</f>
         <v/>
       </c>
-      <c r="C61" s="328" t="str">
+      <c r="C61" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", Zusatzangabe_y3*Haltedauer)</f>
         <v/>
       </c>
-      <c r="D61" s="327" t="str">
+      <c r="D61" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_y), "", "EUR")</f>
         <v/>
       </c>
       <c r="F61" s="147"/>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="370"/>
-      <c r="B62" s="327" t="str">
+      <c r="A62" s="369"/>
+      <c r="B62" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z)</f>
         <v/>
       </c>
-      <c r="C62" s="328" t="str">
+      <c r="C62" s="327" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", Zusatzangabe_z3*Haltedauer)</f>
         <v/>
       </c>
-      <c r="D62" s="327" t="str">
+      <c r="D62" s="326" t="str">
         <f>IF(ISBLANK(Zusatzangabe_z), "", "EUR")</f>
         <v/>
       </c>
@@ -24368,7 +24365,7 @@
       <c r="B63" s="64" t="s">
         <v>101</v>
       </c>
-      <c r="C63" s="284">
+      <c r="C63" s="283">
         <f>SUM(C54:C62)</f>
         <v>47646.264888937505</v>
       </c>
@@ -24390,7 +24387,7 @@
       <c r="B65" s="68" t="s">
         <v>178</v>
       </c>
-      <c r="C65" s="285">
+      <c r="C65" s="284">
         <f>IF(C47*Fahrleistung/10^6*Haltedauer&lt;C46, C47*Fahrleistung/10^6*Haltedauer, C46)</f>
         <v>3.3141818181818179</v>
       </c>
@@ -24402,7 +24399,7 @@
       <c r="B66" s="72" t="s">
         <v>106</v>
       </c>
-      <c r="C66" s="286">
+      <c r="C66" s="285">
         <f>C33*Haltedauer+C40*Haltedauer</f>
         <v>6.3146999999999984</v>
       </c>
@@ -24436,17 +24433,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5e4dc333-02c0-4d6f-a03d-d04a548a7be7">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101006A4EC2B1D245C948A7120CE5A36078F8" ma:contentTypeVersion="14" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="4b87026bc8dcc7f3f10cc45b8239b46f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="5e4dc333-02c0-4d6f-a03d-d04a548a7be7" xmlns:ns3="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b7f15f5ac45b0ba6c0c6284d6c06137b" ns2:_="" ns3:_="">
     <xsd:import namespace="5e4dc333-02c0-4d6f-a03d-d04a548a7be7"/>
@@ -24675,7 +24661,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -24684,24 +24670,18 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{651615EB-DE44-4BF4-BD1E-846AB7A3DA36}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="5e4dc333-02c0-4d6f-a03d-d04a548a7be7"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="5e4dc333-02c0-4d6f-a03d-d04a548a7be7">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C82CFA85-B81D-4C7D-99B5-F82C00D97DE4}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -24720,10 +24700,27 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92A2CDCF-36F6-4C30-8F9B-D45880CB8E7E}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{651615EB-DE44-4BF4-BD1E-846AB7A3DA36}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="6998d7be-1ad0-4716-9c60-ba76cfe9b1f3"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="5e4dc333-02c0-4d6f-a03d-d04a548a7be7"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>